--- a/programs/assembly/tage_test_trace.xlsx
+++ b/programs/assembly/tage_test_trace.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\emerald\zaqal\programs\assembly\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEC894FF-9CD4-474C-8DB2-8AAB7E6C1118}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E43C89F1-40F7-491F-AB15-14455A03F64C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11760" yWindow="2565" windowWidth="13455" windowHeight="9045" xr2:uid="{E346031A-6FE0-420F-941A-72680D802F2C}"/>
+    <workbookView xWindow="29220" yWindow="-2580" windowWidth="7830" windowHeight="12300" xr2:uid="{E346031A-6FE0-420F-941A-72680D802F2C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -641,15 +641,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{568F02AD-F3AB-4DFE-A2E8-3F9FAFF7E011}">
-  <dimension ref="A1:AG27"/>
+  <dimension ref="A1:AG28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="3" width="9.140625" style="4"/>
+    <col min="1" max="1" width="6.140625" style="4" customWidth="1"/>
+    <col min="2" max="2" width="4.5703125" style="4" customWidth="1"/>
+    <col min="3" max="3" width="9.140625" style="4"/>
     <col min="4" max="4" width="4.140625" style="4" customWidth="1"/>
-    <col min="5" max="5" width="3.28515625" style="4" customWidth="1"/>
+    <col min="5" max="5" width="2.140625" style="4" customWidth="1"/>
     <col min="6" max="6" width="5.140625" style="4" customWidth="1"/>
     <col min="7" max="7" width="6.140625" style="4" customWidth="1"/>
-    <col min="8" max="8" width="4.5703125" style="4" customWidth="1"/>
+    <col min="8" max="8" width="7.28515625" style="4" customWidth="1"/>
     <col min="9" max="9" width="5.28515625" style="4" customWidth="1"/>
     <col min="10" max="10" width="5" style="4" customWidth="1"/>
     <col min="11" max="11" width="4.7109375" style="4" customWidth="1"/>
@@ -1467,43 +1469,36 @@
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="4">
-        <v>19</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I22" s="1">
-        <v>12</v>
-      </c>
-      <c r="J22" s="1">
-        <v>0</v>
-      </c>
-      <c r="K22" s="1">
-        <v>20</v>
-      </c>
-      <c r="L22" s="1">
-        <v>0</v>
-      </c>
+      <c r="A22" s="3">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3">
+        <v>60</v>
+      </c>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+      <c r="J22" s="1"/>
+      <c r="K22" s="1"/>
+      <c r="L22" s="1"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>59</v>
@@ -1525,54 +1520,75 @@
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" s="3">
-        <v>20.100000000000001</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3">
-        <v>60</v>
-      </c>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
-      <c r="J24" s="3"/>
-      <c r="K24" s="3"/>
-      <c r="L24" s="3"/>
+      <c r="A24" s="4">
+        <v>20</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I24" s="1">
+        <v>12</v>
+      </c>
+      <c r="J24" s="1">
+        <v>0</v>
+      </c>
+      <c r="K24" s="1">
+        <v>20</v>
+      </c>
+      <c r="L24" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" s="4">
-        <v>21</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>28</v>
-      </c>
+      <c r="A25" s="3"/>
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+      <c r="H25" s="3"/>
+      <c r="I25" s="3"/>
+      <c r="J25" s="3"/>
+      <c r="K25" s="3"/>
+      <c r="L25" s="3"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="4">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
+        <v>22</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A28" s="4">
         <v>23</v>
       </c>
-      <c r="B27" s="2"/>
+      <c r="B28" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>

--- a/programs/assembly/tage_test_trace.xlsx
+++ b/programs/assembly/tage_test_trace.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\emerald\zaqal\programs\assembly\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E43C89F1-40F7-491F-AB15-14455A03F64C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D813A1D-4A52-4A1A-9072-12998F417DA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29220" yWindow="-2580" windowWidth="7830" windowHeight="12300" xr2:uid="{E346031A-6FE0-420F-941A-72680D802F2C}"/>
+    <workbookView xWindow="29025" yWindow="3300" windowWidth="7830" windowHeight="12300" xr2:uid="{E346031A-6FE0-420F-941A-72680D802F2C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="61">
   <si>
     <t>order</t>
   </si>
@@ -217,13 +217,16 @@
   </si>
   <si>
     <t>8.x38</t>
+  </si>
+  <si>
+    <t>cycle BRU</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -268,6 +271,13 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF92D050"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -320,13 +330,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -641,7 +652,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{568F02AD-F3AB-4DFE-A2E8-3F9FAFF7E011}">
-  <dimension ref="A1:AG28"/>
+  <dimension ref="A1:AH28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="4" customWidth="1"/>
@@ -649,21 +660,21 @@
     <col min="3" max="3" width="9.140625" style="4"/>
     <col min="4" max="4" width="4.140625" style="4" customWidth="1"/>
     <col min="5" max="5" width="2.140625" style="4" customWidth="1"/>
-    <col min="6" max="6" width="5.140625" style="4" customWidth="1"/>
-    <col min="7" max="7" width="6.140625" style="4" customWidth="1"/>
-    <col min="8" max="8" width="7.28515625" style="4" customWidth="1"/>
-    <col min="9" max="9" width="5.28515625" style="4" customWidth="1"/>
-    <col min="10" max="10" width="5" style="4" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" style="4" customWidth="1"/>
-    <col min="12" max="12" width="5.42578125" style="4" customWidth="1"/>
-    <col min="13" max="14" width="3.140625" style="4" customWidth="1"/>
-    <col min="15" max="19" width="9.140625" style="4"/>
-    <col min="20" max="20" width="3.7109375" style="4" customWidth="1"/>
-    <col min="21" max="21" width="4" style="4" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="4"/>
+    <col min="6" max="7" width="5.140625" style="4" customWidth="1"/>
+    <col min="8" max="8" width="6.140625" style="4" customWidth="1"/>
+    <col min="9" max="9" width="7.28515625" style="4" customWidth="1"/>
+    <col min="10" max="10" width="5.28515625" style="4" customWidth="1"/>
+    <col min="11" max="11" width="5" style="4" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" style="4" customWidth="1"/>
+    <col min="13" max="13" width="5.42578125" style="4" customWidth="1"/>
+    <col min="14" max="15" width="3.140625" style="4" customWidth="1"/>
+    <col min="16" max="20" width="9.140625" style="4"/>
+    <col min="21" max="21" width="3.7109375" style="4" customWidth="1"/>
+    <col min="22" max="22" width="4" style="4" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -675,84 +686,87 @@
         <v>32</v>
       </c>
       <c r="G1" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="H1" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="I1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="J1" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="K1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="L1" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="M1" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="M1" s="5"/>
       <c r="N1" s="5"/>
-      <c r="O1" s="5" t="s">
+      <c r="O1" s="5"/>
+      <c r="P1" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="Q1" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="Q1" s="5" t="s">
+      <c r="R1" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="R1" s="5" t="s">
+      <c r="S1" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="S1" s="5" t="s">
+      <c r="T1" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="T1" s="5" t="s">
+      <c r="U1" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="U1" s="5" t="s">
+      <c r="V1" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="V1" s="5" t="s">
+      <c r="W1" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="W1" s="5" t="s">
+      <c r="X1" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="X1" s="5" t="s">
+      <c r="Y1" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="Y1" s="5" t="s">
+      <c r="Z1" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="Z1" s="5" t="s">
+      <c r="AA1" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="AA1" s="5" t="s">
+      <c r="AB1" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="AB1" s="5" t="s">
+      <c r="AC1" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="AC1" s="5" t="s">
+      <c r="AD1" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="AD1" s="5" t="s">
+      <c r="AE1" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="AE1" s="5" t="s">
+      <c r="AF1" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="AF1" s="5" t="s">
+      <c r="AG1" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="AG1" s="5" t="s">
+      <c r="AH1" s="5" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -767,18 +781,16 @@
       <c r="F2" s="1">
         <v>11</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" s="1"/>
+      <c r="H2" s="1">
         <v>10</v>
       </c>
-      <c r="H2" s="1"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
-      <c r="O2" s="1" t="s">
-        <v>55</v>
-      </c>
+      <c r="N2" s="1"/>
       <c r="P2" s="1" t="s">
         <v>55</v>
       </c>
@@ -791,8 +803,11 @@
       <c r="S2" s="1" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="T2" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -807,20 +822,18 @@
       <c r="F3" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" s="1"/>
+      <c r="H3" s="1">
         <v>10</v>
       </c>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1">
+      <c r="I3" s="1"/>
+      <c r="J3" s="1">
         <v>0</v>
       </c>
-      <c r="J3" s="1"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
-      <c r="O3" s="1" t="s">
-        <v>55</v>
-      </c>
+      <c r="N3" s="1"/>
       <c r="P3" s="1" t="s">
         <v>55</v>
       </c>
@@ -833,8 +846,11 @@
       <c r="S3" s="1" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="T3" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -849,20 +865,18 @@
       <c r="F4" s="1">
         <v>12</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" s="1"/>
+      <c r="H4" s="1">
         <v>10</v>
       </c>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1">
+      <c r="I4" s="1"/>
+      <c r="J4" s="1">
         <v>6</v>
       </c>
-      <c r="J4" s="1"/>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
-      <c r="O4" s="1" t="s">
-        <v>55</v>
-      </c>
+      <c r="N4" s="1"/>
       <c r="P4" s="1" t="s">
         <v>55</v>
       </c>
@@ -875,8 +889,11 @@
       <c r="S4" s="1" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="T4" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="5" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -891,22 +908,20 @@
       <c r="F5" s="1">
         <v>13</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" s="1"/>
+      <c r="H5" s="1">
         <v>10</v>
       </c>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1">
+      <c r="I5" s="1"/>
+      <c r="J5" s="1">
         <v>6</v>
       </c>
-      <c r="J5" s="1">
+      <c r="K5" s="1">
         <v>2</v>
       </c>
-      <c r="K5" s="1"/>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
-      <c r="O5" s="1" t="s">
-        <v>55</v>
-      </c>
+      <c r="N5" s="1"/>
       <c r="P5" s="1" t="s">
         <v>55</v>
       </c>
@@ -919,36 +934,39 @@
       <c r="S5" s="1" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
+      <c r="T5" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="6" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A6" s="6">
         <v>5</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="1"/>
+      <c r="D6" s="6"/>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
       <c r="G6" s="1">
+        <v>12</v>
+      </c>
+      <c r="H6" s="1">
         <v>10</v>
       </c>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1">
+      <c r="I6" s="1"/>
+      <c r="J6" s="1">
         <v>6</v>
       </c>
-      <c r="J6" s="1">
+      <c r="K6" s="1">
         <v>2</v>
       </c>
-      <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
-      <c r="O6" s="1" t="s">
-        <v>55</v>
-      </c>
+      <c r="N6" s="1"/>
       <c r="P6" s="1" t="s">
         <v>55</v>
       </c>
@@ -961,8 +979,11 @@
       <c r="S6" s="1" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="T6" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="7" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -977,23 +998,21 @@
       <c r="F7" s="1">
         <v>13</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" s="1"/>
+      <c r="H7" s="1">
         <v>10</v>
       </c>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1">
+      <c r="I7" s="1"/>
+      <c r="J7" s="1">
         <v>6</v>
       </c>
-      <c r="J7" s="1">
+      <c r="K7" s="1">
         <v>2</v>
       </c>
-      <c r="K7" s="1">
+      <c r="L7" s="1">
         <v>1</v>
       </c>
-      <c r="L7" s="1"/>
-      <c r="O7" s="1" t="s">
-        <v>55</v>
-      </c>
+      <c r="M7" s="1"/>
       <c r="P7" s="1" t="s">
         <v>55</v>
       </c>
@@ -1006,8 +1025,11 @@
       <c r="S7" s="1" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="T7" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1022,25 +1044,23 @@
       <c r="F8" s="1">
         <v>14</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8" s="1"/>
+      <c r="H8" s="1">
         <v>10</v>
       </c>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1">
+      <c r="I8" s="1"/>
+      <c r="J8" s="1">
         <v>6</v>
       </c>
-      <c r="J8" s="1">
+      <c r="K8" s="1">
         <v>2</v>
       </c>
-      <c r="K8" s="1">
+      <c r="L8" s="1">
         <v>1</v>
       </c>
-      <c r="L8" s="1">
+      <c r="M8" s="1">
         <v>8</v>
       </c>
-      <c r="O8" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="P8" s="1" t="s">
         <v>55</v>
       </c>
@@ -1053,43 +1073,46 @@
       <c r="S8" s="1" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
+      <c r="T8" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A9" s="6">
         <v>8</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D9" s="1"/>
+      <c r="D9" s="6"/>
       <c r="E9" s="1"/>
       <c r="F9" s="1">
         <v>15</v>
       </c>
       <c r="G9" s="1">
+        <v>13</v>
+      </c>
+      <c r="H9" s="1">
         <v>10</v>
       </c>
-      <c r="H9" s="1" t="s">
+      <c r="I9" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="I9" s="1">
+      <c r="J9" s="1">
         <v>6</v>
       </c>
-      <c r="J9" s="1">
+      <c r="K9" s="1">
         <v>2</v>
       </c>
-      <c r="K9" s="1">
+      <c r="L9" s="1">
         <v>1</v>
       </c>
-      <c r="L9" s="1">
+      <c r="M9" s="1">
         <v>8</v>
       </c>
-      <c r="O9" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="P9" s="1" t="s">
         <v>55</v>
       </c>
@@ -1102,8 +1125,11 @@
       <c r="S9" s="1" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="T9" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>8.1</v>
       </c>
@@ -1122,12 +1148,13 @@
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
-      <c r="K10" s="3">
+      <c r="K10" s="3"/>
+      <c r="L10" s="3">
         <v>10</v>
       </c>
-      <c r="L10" s="3"/>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="M10" s="3"/>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -1142,60 +1169,64 @@
       <c r="F11" s="1">
         <v>25</v>
       </c>
-      <c r="G11" s="1">
+      <c r="G11" s="1"/>
+      <c r="H11" s="1">
         <v>10</v>
       </c>
-      <c r="H11" s="1" t="s">
+      <c r="I11" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="I11" s="1">
+      <c r="J11" s="1">
         <v>6</v>
       </c>
-      <c r="J11" s="1">
+      <c r="K11" s="1">
         <v>2</v>
       </c>
-      <c r="K11" s="1">
+      <c r="L11" s="1">
         <v>1</v>
       </c>
-      <c r="L11" s="1">
+      <c r="M11" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
+    <row r="12" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A12" s="6">
         <v>10</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D12" s="1"/>
+      <c r="D12" s="6"/>
       <c r="E12" s="1"/>
       <c r="F12" s="1">
         <v>26</v>
       </c>
-      <c r="G12" s="1" t="s">
+      <c r="G12" s="1">
+        <v>24</v>
+      </c>
+      <c r="H12" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="H12" s="1" t="s">
+      <c r="I12" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="I12" s="1">
+      <c r="J12" s="1">
         <v>6</v>
       </c>
-      <c r="J12" s="1">
+      <c r="K12" s="1">
         <v>2</v>
       </c>
-      <c r="K12" s="1">
+      <c r="L12" s="1">
         <v>1</v>
       </c>
-      <c r="L12" s="1">
+      <c r="M12" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -1210,90 +1241,97 @@
       <c r="F13" s="1">
         <v>36</v>
       </c>
-      <c r="G13" s="1" t="s">
+      <c r="G13" s="1"/>
+      <c r="H13" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="H13" s="1" t="s">
+      <c r="I13" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="I13" s="1">
+      <c r="J13" s="1">
         <v>6</v>
       </c>
-      <c r="J13" s="1">
+      <c r="K13" s="1">
         <v>2</v>
       </c>
-      <c r="K13" s="1">
+      <c r="L13" s="1">
         <v>20</v>
       </c>
-      <c r="L13" s="1">
+      <c r="M13" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A14" s="1">
+    <row r="14" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A14" s="6">
         <v>12</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="6" t="s">
         <v>26</v>
       </c>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
-      <c r="G14" s="1" t="s">
+      <c r="G14" s="1">
+        <v>34</v>
+      </c>
+      <c r="H14" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="H14" s="1" t="s">
+      <c r="I14" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="I14" s="1">
+      <c r="J14" s="1">
         <v>6</v>
       </c>
-      <c r="J14" s="1">
+      <c r="K14" s="1">
         <v>2</v>
       </c>
-      <c r="K14" s="1">
+      <c r="L14" s="1">
         <v>20</v>
       </c>
-      <c r="L14" s="1">
+      <c r="M14" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A15" s="1">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A15" s="6">
         <v>13</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D15" s="1"/>
+      <c r="D15" s="6"/>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
-      <c r="G15" s="1" t="s">
+      <c r="G15" s="1">
+        <v>44</v>
+      </c>
+      <c r="H15" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="H15" s="1" t="s">
+      <c r="I15" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="I15" s="1">
+      <c r="J15" s="1">
         <v>6</v>
       </c>
-      <c r="J15" s="1">
+      <c r="K15" s="1">
         <v>2</v>
       </c>
-      <c r="K15" s="1">
+      <c r="L15" s="1">
         <v>20</v>
       </c>
-      <c r="L15" s="1">
+      <c r="M15" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -1308,26 +1346,27 @@
       <c r="F16" s="1">
         <v>56</v>
       </c>
-      <c r="G16" s="1" t="s">
+      <c r="G16" s="1"/>
+      <c r="H16" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="H16" s="1" t="s">
+      <c r="I16" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="I16" s="1">
+      <c r="J16" s="1">
         <v>12</v>
       </c>
-      <c r="J16" s="1">
+      <c r="K16" s="1">
         <v>2</v>
       </c>
-      <c r="K16" s="1">
+      <c r="L16" s="1">
         <v>20</v>
       </c>
-      <c r="L16" s="1">
+      <c r="M16" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -1340,26 +1379,27 @@
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
-      <c r="G17" s="1" t="s">
+      <c r="G17" s="1"/>
+      <c r="H17" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="H17" s="1" t="s">
+      <c r="I17" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="I17" s="1">
+      <c r="J17" s="1">
         <v>12</v>
       </c>
-      <c r="J17" s="1">
+      <c r="K17" s="1">
         <v>0</v>
       </c>
-      <c r="K17" s="1">
+      <c r="L17" s="1">
         <v>20</v>
       </c>
-      <c r="L17" s="1">
+      <c r="M17" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -1372,26 +1412,27 @@
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
-      <c r="G18" s="1" t="s">
+      <c r="G18" s="1"/>
+      <c r="H18" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="H18" s="1" t="s">
+      <c r="I18" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="I18" s="1">
+      <c r="J18" s="1">
         <v>12</v>
       </c>
-      <c r="J18" s="1">
+      <c r="K18" s="1">
         <v>0</v>
       </c>
-      <c r="K18" s="1">
+      <c r="L18" s="1">
         <v>20</v>
       </c>
-      <c r="L18" s="1">
+      <c r="M18" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>16.100000000000001</v>
       </c>
@@ -1406,8 +1447,9 @@
       <c r="F19" s="3">
         <v>57</v>
       </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="G19" s="3"/>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>17</v>
       </c>
@@ -1420,26 +1462,27 @@
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
-      <c r="G20" s="1" t="s">
+      <c r="G20" s="1"/>
+      <c r="H20" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="H20" s="1" t="s">
+      <c r="I20" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="I20" s="1">
+      <c r="J20" s="1">
         <v>12</v>
       </c>
-      <c r="J20" s="1">
+      <c r="K20" s="1">
         <v>0</v>
       </c>
-      <c r="K20" s="1">
+      <c r="L20" s="1">
         <v>20</v>
       </c>
-      <c r="L20" s="1">
+      <c r="M20" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
         <v>18</v>
       </c>
@@ -1449,26 +1492,26 @@
       <c r="C21" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="G21" s="1" t="s">
+      <c r="H21" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="H21" s="1" t="s">
+      <c r="I21" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="I21" s="1">
+      <c r="J21" s="1">
         <v>12</v>
       </c>
-      <c r="J21" s="1">
+      <c r="K21" s="1">
         <v>0</v>
       </c>
-      <c r="K21" s="1">
+      <c r="L21" s="1">
         <v>20</v>
       </c>
-      <c r="L21" s="1">
+      <c r="M21" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <v>18.100000000000001</v>
       </c>
@@ -1483,14 +1526,15 @@
       <c r="F22" s="3">
         <v>60</v>
       </c>
-      <c r="G22" s="1"/>
+      <c r="G22" s="3"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M22" s="1"/>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
         <v>19</v>
       </c>
@@ -1500,26 +1544,26 @@
       <c r="C23" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="G23" s="1" t="s">
+      <c r="H23" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="H23" s="1" t="s">
+      <c r="I23" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="I23" s="1">
+      <c r="J23" s="1">
         <v>12</v>
       </c>
-      <c r="J23" s="1">
+      <c r="K23" s="1">
         <v>0</v>
       </c>
-      <c r="K23" s="1">
+      <c r="L23" s="1">
         <v>20</v>
       </c>
-      <c r="L23" s="1">
+      <c r="M23" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
         <v>20</v>
       </c>
@@ -1529,26 +1573,26 @@
       <c r="C24" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="G24" s="1" t="s">
+      <c r="H24" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="H24" s="1" t="s">
+      <c r="I24" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="I24" s="1">
+      <c r="J24" s="1">
         <v>12</v>
       </c>
-      <c r="J24" s="1">
+      <c r="K24" s="1">
         <v>0</v>
       </c>
-      <c r="K24" s="1">
+      <c r="L24" s="1">
         <v>20</v>
       </c>
-      <c r="L24" s="1">
+      <c r="M24" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="3"/>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
@@ -1561,8 +1605,9 @@
       <c r="J25" s="3"/>
       <c r="K25" s="3"/>
       <c r="L25" s="3"/>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M25" s="3"/>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="4">
         <v>21</v>
       </c>
@@ -1573,7 +1618,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
         <v>22</v>
       </c>
@@ -1584,7 +1629,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="4">
         <v>23</v>
       </c>
@@ -1593,5 +1638,6 @@
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
--- a/programs/assembly/tage_test_trace.xlsx
+++ b/programs/assembly/tage_test_trace.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\emerald\zaqal\programs\assembly\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D813A1D-4A52-4A1A-9072-12998F417DA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33E7BA80-FF6C-45F7-B991-C946CFCDBCE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29025" yWindow="3300" windowWidth="7830" windowHeight="12300" xr2:uid="{E346031A-6FE0-420F-941A-72680D802F2C}"/>
+    <workbookView xWindow="13065" yWindow="150" windowWidth="15735" windowHeight="12300" xr2:uid="{E346031A-6FE0-420F-941A-72680D802F2C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="72">
   <si>
     <t>order</t>
   </si>
@@ -150,9 +150,6 @@
     <t>BPU</t>
   </si>
   <si>
-    <t>FTB</t>
-  </si>
-  <si>
     <t>TAGE</t>
   </si>
   <si>
@@ -220,6 +217,42 @@
   </si>
   <si>
     <t>cycle BRU</t>
+  </si>
+  <si>
+    <t>FTB entry 1</t>
+  </si>
+  <si>
+    <t>FTB entry 2</t>
+  </si>
+  <si>
+    <t>FTB entry 0 source - target</t>
+  </si>
+  <si>
+    <t>1c - 30</t>
+  </si>
+  <si>
+    <t>34 - 28</t>
+  </si>
+  <si>
+    <t>2c - 3c</t>
+  </si>
+  <si>
+    <t>3c - 08</t>
+  </si>
+  <si>
+    <t>x10 - x18</t>
+  </si>
+  <si>
+    <t>x1c - x30</t>
+  </si>
+  <si>
+    <t>x34 - 28</t>
+  </si>
+  <si>
+    <t>GHR</t>
+  </si>
+  <si>
+    <t>PHR</t>
   </si>
 </sst>
 </file>
@@ -330,7 +363,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -338,6 +371,7 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -652,7 +686,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{568F02AD-F3AB-4DFE-A2E8-3F9FAFF7E011}">
-  <dimension ref="A1:AH28"/>
+  <dimension ref="A1:AL28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="4" customWidth="1"/>
@@ -668,13 +702,13 @@
     <col min="12" max="12" width="4.7109375" style="4" customWidth="1"/>
     <col min="13" max="13" width="5.42578125" style="4" customWidth="1"/>
     <col min="14" max="15" width="3.140625" style="4" customWidth="1"/>
-    <col min="16" max="20" width="9.140625" style="4"/>
-    <col min="21" max="21" width="3.7109375" style="4" customWidth="1"/>
-    <col min="22" max="22" width="4" style="4" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="4"/>
+    <col min="16" max="24" width="9.140625" style="4"/>
+    <col min="25" max="25" width="3.7109375" style="4" customWidth="1"/>
+    <col min="26" max="26" width="4" style="4" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -686,7 +720,7 @@
         <v>32</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H1" s="5" t="s">
         <v>31</v>
@@ -712,61 +746,73 @@
         <v>36</v>
       </c>
       <c r="Q1" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="R1" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="S1" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="T1" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="U1" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="R1" s="5" t="s">
+      <c r="V1" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="W1" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="S1" s="5" t="s">
+      <c r="X1" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="T1" s="5" t="s">
+      <c r="Y1" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="U1" s="5" t="s">
+      <c r="Z1" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="V1" s="5" t="s">
+      <c r="AA1" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="W1" s="5" t="s">
+      <c r="AB1" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="X1" s="5" t="s">
+      <c r="AC1" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="Y1" s="5" t="s">
+      <c r="AD1" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="Z1" s="5" t="s">
+      <c r="AE1" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="AA1" s="5" t="s">
+      <c r="AF1" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="AB1" s="5" t="s">
+      <c r="AG1" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="AC1" s="5" t="s">
+      <c r="AH1" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="AD1" s="5" t="s">
+      <c r="AI1" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="AE1" s="5" t="s">
+      <c r="AJ1" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="AF1" s="5" t="s">
+      <c r="AK1" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="AG1" s="5" t="s">
+      <c r="AL1" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="AH1" s="5" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -792,22 +838,26 @@
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
       <c r="P2" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="3" spans="1:34" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="V2" s="1"/>
+      <c r="W2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="X2" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -820,7 +870,7 @@
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G3" s="1"/>
       <c r="H3" s="1">
@@ -835,22 +885,26 @@
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
       <c r="P3" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="R3" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="S3" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="T3" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="4" spans="1:34" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+      <c r="R3" s="1"/>
+      <c r="S3" s="1"/>
+      <c r="T3" s="1"/>
+      <c r="U3" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="V3" s="1"/>
+      <c r="W3" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="X3" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -878,22 +932,26 @@
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
       <c r="P4" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="R4" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="S4" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="T4" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+      <c r="R4" s="1"/>
+      <c r="S4" s="1"/>
+      <c r="T4" s="1"/>
+      <c r="U4" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="V4" s="1"/>
+      <c r="W4" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="X4" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -923,22 +981,26 @@
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
       <c r="P5" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="Q5" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="R5" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="S5" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="T5" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+      <c r="R5" s="1"/>
+      <c r="S5" s="1"/>
+      <c r="T5" s="1"/>
+      <c r="U5" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="V5" s="1"/>
+      <c r="W5" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="X5" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="6" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>5</v>
       </c>
@@ -968,22 +1030,26 @@
       <c r="M6" s="1"/>
       <c r="N6" s="1"/>
       <c r="P6" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="R6" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="S6" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="T6" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+      <c r="R6" s="1"/>
+      <c r="S6" s="1"/>
+      <c r="T6" s="1"/>
+      <c r="U6" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="V6" s="1"/>
+      <c r="W6" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="X6" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="7" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -1014,22 +1080,26 @@
       </c>
       <c r="M7" s="1"/>
       <c r="P7" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="R7" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="S7" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="T7" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+      <c r="R7" s="1"/>
+      <c r="S7" s="1"/>
+      <c r="T7" s="1"/>
+      <c r="U7" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="V7" s="1"/>
+      <c r="W7" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="X7" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="8" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1062,22 +1132,26 @@
         <v>8</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="Q8" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="R8" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="S8" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="T8" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+      <c r="R8" s="1"/>
+      <c r="S8" s="1"/>
+      <c r="T8" s="1"/>
+      <c r="U8" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="V8" s="1"/>
+      <c r="W8" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="X8" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="9" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>8</v>
       </c>
@@ -1099,7 +1173,7 @@
         <v>10</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J9" s="1">
         <v>6</v>
@@ -1114,22 +1188,26 @@
         <v>8</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="Q9" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="R9" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="S9" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="T9" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+      <c r="R9" s="1"/>
+      <c r="S9" s="1"/>
+      <c r="T9" s="1"/>
+      <c r="U9" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="V9" s="1"/>
+      <c r="W9" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="X9" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>8.1</v>
       </c>
@@ -1153,8 +1231,11 @@
         <v>10</v>
       </c>
       <c r="M10" s="3"/>
-    </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="Q10" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -1174,7 +1255,7 @@
         <v>10</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J11" s="1">
         <v>6</v>
@@ -1188,8 +1269,11 @@
       <c r="M11" s="1">
         <v>8</v>
       </c>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="Q11" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="12" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
         <v>10</v>
       </c>
@@ -1208,10 +1292,10 @@
         <v>24</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J12" s="1">
         <v>6</v>
@@ -1225,8 +1309,14 @@
       <c r="M12" s="1">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="Q12" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="R12" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="13" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -1243,10 +1333,10 @@
       </c>
       <c r="G13" s="1"/>
       <c r="H13" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J13" s="1">
         <v>6</v>
@@ -1260,8 +1350,14 @@
       <c r="M13" s="1">
         <v>8</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="Q13" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="R13" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="14" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
         <v>12</v>
       </c>
@@ -1278,10 +1374,10 @@
         <v>34</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J14" s="1">
         <v>6</v>
@@ -1295,8 +1391,14 @@
       <c r="M14" s="1">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="Q14" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="R14" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="15" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
         <v>13</v>
       </c>
@@ -1313,10 +1415,10 @@
         <v>44</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J15" s="1">
         <v>6</v>
@@ -1330,8 +1432,14 @@
       <c r="M15" s="1">
         <v>8</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="Q15" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="R15" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="16" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -1339,7 +1447,7 @@
         <v>3</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
@@ -1348,10 +1456,10 @@
       </c>
       <c r="G16" s="1"/>
       <c r="H16" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J16" s="1">
         <v>12</v>
@@ -1365,8 +1473,14 @@
       <c r="M16" s="1">
         <v>8</v>
       </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="Q16" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="R16" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -1381,10 +1495,10 @@
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
       <c r="H17" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J17" s="1">
         <v>12</v>
@@ -1398,8 +1512,14 @@
       <c r="M17" s="1">
         <v>8</v>
       </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="Q17" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="R17" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -1412,12 +1532,14 @@
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
+      <c r="G18" s="1">
+        <v>56</v>
+      </c>
       <c r="H18" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J18" s="1">
         <v>12</v>
@@ -1431,8 +1553,14 @@
       <c r="M18" s="1">
         <v>8</v>
       </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="Q18" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="R18" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>16.100000000000001</v>
       </c>
@@ -1448,8 +1576,14 @@
         <v>57</v>
       </c>
       <c r="G19" s="3"/>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="Q19" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="R19" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>17</v>
       </c>
@@ -1464,10 +1598,10 @@
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
       <c r="H20" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J20" s="1">
         <v>12</v>
@@ -1481,8 +1615,14 @@
       <c r="M20" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="Q20" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="R20" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
         <v>18</v>
       </c>
@@ -1493,10 +1633,10 @@
         <v>30</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J21" s="1">
         <v>12</v>
@@ -1510,8 +1650,14 @@
       <c r="M21" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="Q21" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="R21" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <v>18.100000000000001</v>
       </c>
@@ -1533,8 +1679,14 @@
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="Q22" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="R22" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
         <v>19</v>
       </c>
@@ -1545,10 +1697,10 @@
         <v>23</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J23" s="1">
         <v>12</v>
@@ -1562,8 +1714,14 @@
       <c r="M23" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="Q23" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="R23" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
         <v>20</v>
       </c>
@@ -1574,10 +1732,10 @@
         <v>24</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J24" s="1">
         <v>12</v>
@@ -1591,8 +1749,14 @@
       <c r="M24" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="Q24" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="R24" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" s="3"/>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
@@ -1607,7 +1771,7 @@
       <c r="L25" s="3"/>
       <c r="M25" s="3"/>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" s="4">
         <v>21</v>
       </c>
@@ -1618,7 +1782,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
         <v>22</v>
       </c>
@@ -1629,7 +1793,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" s="4">
         <v>23</v>
       </c>

--- a/programs/assembly/tage_test_trace.xlsx
+++ b/programs/assembly/tage_test_trace.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\emerald\zaqal\programs\assembly\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33E7BA80-FF6C-45F7-B991-C946CFCDBCE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F281E1E4-7DA8-4357-8615-65F0E7F1264A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13065" yWindow="150" windowWidth="15735" windowHeight="12300" xr2:uid="{E346031A-6FE0-420F-941A-72680D802F2C}"/>
+    <workbookView xWindow="28965" yWindow="-2070" windowWidth="11325" windowHeight="25140" xr2:uid="{E346031A-6FE0-420F-941A-72680D802F2C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1548" uniqueCount="107">
   <si>
     <t>order</t>
   </si>
@@ -150,9 +150,6 @@
     <t>BPU</t>
   </si>
   <si>
-    <t>TAGE</t>
-  </si>
-  <si>
     <t>ITTAGE</t>
   </si>
   <si>
@@ -222,9 +219,6 @@
     <t>FTB entry 1</t>
   </si>
   <si>
-    <t>FTB entry 2</t>
-  </si>
-  <si>
     <t>FTB entry 0 source - target</t>
   </si>
   <si>
@@ -246,13 +240,124 @@
     <t>x1c - x30</t>
   </si>
   <si>
-    <t>x34 - 28</t>
-  </si>
-  <si>
-    <t>GHR</t>
-  </si>
-  <si>
     <t>PHR</t>
+  </si>
+  <si>
+    <t>TAGE (Slot, Tag, US , CTRS)</t>
+  </si>
+  <si>
+    <t>PC</t>
+  </si>
+  <si>
+    <t>Instruction</t>
+  </si>
+  <si>
+    <t>x08</t>
+  </si>
+  <si>
+    <t>x0c</t>
+  </si>
+  <si>
+    <t>0x38</t>
+  </si>
+  <si>
+    <t>T0[32], Tag=0x20, US=0, CTR=4</t>
+  </si>
+  <si>
+    <t>T0[1], Tag=0x1, US=0, CTR=4</t>
+  </si>
+  <si>
+    <t>T0[35], Tag=0x23, US=0, CTR=4</t>
+  </si>
+  <si>
+    <t>No Update</t>
+  </si>
+  <si>
+    <t>T0[46], Tag=0x2E, US=0, CTR=4</t>
+  </si>
+  <si>
+    <t>T0[13], Tag=0xD, US=0, CTR=4</t>
+  </si>
+  <si>
+    <t>T0[43], Tag=0x2B, US=0, CTR=4</t>
+  </si>
+  <si>
+    <t>T0[46], Tag=0x2E, US=1, CTR=5</t>
+  </si>
+  <si>
+    <t>T0[13], Tag=0xD, US=1, CTR=5</t>
+  </si>
+  <si>
+    <t>T0[43], Tag=0x2B, US=1, CTR=5</t>
+  </si>
+  <si>
+    <t>T0[46], Tag=0x2E, US=2, CTR=6</t>
+  </si>
+  <si>
+    <t>T0[13], Tag=0xD, US=2, CTR=6</t>
+  </si>
+  <si>
+    <t>T0[43], Tag=0x2B, US=2, CTR=6</t>
+  </si>
+  <si>
+    <t>T0[46], Tag=0x2E, US=3, CTR=7</t>
+  </si>
+  <si>
+    <t>T0[13], Tag=0xD, US=3, CTR=7</t>
+  </si>
+  <si>
+    <t>T0[43], Tag=0x2B, US=3, CTR=7</t>
+  </si>
+  <si>
+    <t>T0[32], Tag=0x20, Target=0x28, US=0</t>
+  </si>
+  <si>
+    <t>T0[42], Tag=0x2A, Target=0x20, US=0</t>
+  </si>
+  <si>
+    <t>T0[40], Tag=0x28, Target=0x28, US=0</t>
+  </si>
+  <si>
+    <t>T0[42], Tag=0x2A, Target=0x20, US=1</t>
+  </si>
+  <si>
+    <t>T0[40], Tag=0x28, Target=0x28, US=1</t>
+  </si>
+  <si>
+    <t>T0[42], Tag=0x2A, Target=0x20, US=2</t>
+  </si>
+  <si>
+    <t>T0[40], Tag=0x28, Target=0x28, US=2</t>
+  </si>
+  <si>
+    <t>T0[42], Tag=0x2A, Target=0x20, US=3</t>
+  </si>
+  <si>
+    <t>T0[40], Tag=0x28, Target=0x28, US=3</t>
+  </si>
+  <si>
+    <t>x34 - x20</t>
+  </si>
+  <si>
+    <t>x24 - x3c</t>
+  </si>
+  <si>
+    <t>x3c - x08</t>
+  </si>
+  <si>
+    <t>x34 - x28</t>
+  </si>
+  <si>
+    <t>x2c - x3c</t>
+  </si>
+  <si>
+    <t>0x20</t>
+  </si>
+  <si>
+    <t>0x28</t>
+  </si>
+  <si>
+    <t>PRE GHR</t>
   </si>
 </sst>
 </file>
@@ -686,7 +791,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{568F02AD-F3AB-4DFE-A2E8-3F9FAFF7E011}">
-  <dimension ref="A1:AL28"/>
+  <dimension ref="A1:AL206"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="4" customWidth="1"/>
@@ -694,15 +799,14 @@
     <col min="3" max="3" width="9.140625" style="4"/>
     <col min="4" max="4" width="4.140625" style="4" customWidth="1"/>
     <col min="5" max="5" width="2.140625" style="4" customWidth="1"/>
-    <col min="6" max="7" width="5.140625" style="4" customWidth="1"/>
-    <col min="8" max="8" width="6.140625" style="4" customWidth="1"/>
-    <col min="9" max="9" width="7.28515625" style="4" customWidth="1"/>
-    <col min="10" max="10" width="5.28515625" style="4" customWidth="1"/>
-    <col min="11" max="11" width="5" style="4" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" style="4" customWidth="1"/>
-    <col min="13" max="13" width="5.42578125" style="4" customWidth="1"/>
-    <col min="14" max="15" width="3.140625" style="4" customWidth="1"/>
-    <col min="16" max="24" width="9.140625" style="4"/>
+    <col min="6" max="6" width="4.5703125" style="4" customWidth="1"/>
+    <col min="7" max="9" width="5.5703125" style="4" customWidth="1"/>
+    <col min="10" max="13" width="3.5703125" style="4" customWidth="1"/>
+    <col min="14" max="15" width="2.42578125" style="4" customWidth="1"/>
+    <col min="16" max="16" width="5.5703125" style="4" customWidth="1"/>
+    <col min="17" max="18" width="9.140625" style="4"/>
+    <col min="19" max="20" width="5.140625" style="4" customWidth="1"/>
+    <col min="21" max="24" width="9.140625" style="4"/>
     <col min="25" max="25" width="3.7109375" style="4" customWidth="1"/>
     <col min="26" max="26" width="4" style="4" customWidth="1"/>
     <col min="27" max="16384" width="9.140625" style="4"/>
@@ -712,15 +816,19 @@
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
+      <c r="B1" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="D1" s="5"/>
       <c r="E1" s="5"/>
       <c r="F1" s="5" t="s">
         <v>32</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H1" s="5" t="s">
         <v>31</v>
@@ -746,70 +854,68 @@
         <v>36</v>
       </c>
       <c r="Q1" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="R1" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="S1" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="T1" s="5" t="s">
-        <v>70</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="T1" s="5"/>
       <c r="U1" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="V1" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="W1" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="V1" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="W1" s="5" t="s">
+      <c r="X1" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="X1" s="5" t="s">
+      <c r="Y1" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="Y1" s="5" t="s">
+      <c r="Z1" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="Z1" s="5" t="s">
+      <c r="AA1" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="AA1" s="5" t="s">
+      <c r="AB1" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="AB1" s="5" t="s">
+      <c r="AC1" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="AC1" s="5" t="s">
+      <c r="AD1" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="AD1" s="5" t="s">
+      <c r="AE1" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="AE1" s="5" t="s">
+      <c r="AF1" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="AF1" s="5" t="s">
+      <c r="AG1" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="AG1" s="5" t="s">
+      <c r="AH1" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="AH1" s="5" t="s">
+      <c r="AI1" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="AI1" s="5" t="s">
+      <c r="AJ1" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="AJ1" s="5" t="s">
+      <c r="AK1" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="AK1" s="5" t="s">
+      <c r="AL1" s="5" t="s">
         <v>52</v>
-      </c>
-      <c r="AL1" s="5" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:38" x14ac:dyDescent="0.25">
@@ -837,25 +943,15 @@
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
-      <c r="P2" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>54</v>
-      </c>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
       <c r="T2" s="1"/>
-      <c r="U2" s="1" t="s">
-        <v>54</v>
-      </c>
+      <c r="U2" s="1"/>
       <c r="V2" s="1"/>
-      <c r="W2" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="X2" s="1" t="s">
-        <v>54</v>
-      </c>
+      <c r="W2" s="1"/>
+      <c r="X2" s="1"/>
     </row>
     <row r="3" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
@@ -870,7 +966,7 @@
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G3" s="1"/>
       <c r="H3" s="1">
@@ -884,25 +980,15 @@
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
-      <c r="P3" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="Q3" s="1" t="s">
-        <v>54</v>
-      </c>
+      <c r="P3" s="1"/>
+      <c r="Q3" s="1"/>
       <c r="R3" s="1"/>
       <c r="S3" s="1"/>
       <c r="T3" s="1"/>
-      <c r="U3" s="1" t="s">
-        <v>54</v>
-      </c>
+      <c r="U3" s="1"/>
       <c r="V3" s="1"/>
-      <c r="W3" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="X3" s="1" t="s">
-        <v>54</v>
-      </c>
+      <c r="W3" s="1"/>
+      <c r="X3" s="1"/>
     </row>
     <row r="4" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
@@ -931,25 +1017,15 @@
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
-      <c r="P4" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="Q4" s="1" t="s">
-        <v>54</v>
-      </c>
+      <c r="P4" s="1"/>
+      <c r="Q4" s="1"/>
       <c r="R4" s="1"/>
       <c r="S4" s="1"/>
       <c r="T4" s="1"/>
-      <c r="U4" s="1" t="s">
-        <v>54</v>
-      </c>
+      <c r="U4" s="1"/>
       <c r="V4" s="1"/>
-      <c r="W4" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="X4" s="1" t="s">
-        <v>54</v>
-      </c>
+      <c r="W4" s="1"/>
+      <c r="X4" s="1"/>
     </row>
     <row r="5" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
@@ -980,25 +1056,15 @@
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
-      <c r="P5" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="Q5" s="1" t="s">
-        <v>54</v>
-      </c>
+      <c r="P5" s="1"/>
+      <c r="Q5" s="1"/>
       <c r="R5" s="1"/>
       <c r="S5" s="1"/>
       <c r="T5" s="1"/>
-      <c r="U5" s="1" t="s">
-        <v>54</v>
-      </c>
+      <c r="U5" s="1"/>
       <c r="V5" s="1"/>
-      <c r="W5" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="X5" s="1" t="s">
-        <v>54</v>
-      </c>
+      <c r="W5" s="1"/>
+      <c r="X5" s="1"/>
     </row>
     <row r="6" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
@@ -1029,25 +1095,15 @@
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
       <c r="N6" s="1"/>
-      <c r="P6" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="Q6" s="1" t="s">
-        <v>54</v>
-      </c>
+      <c r="P6" s="1"/>
+      <c r="Q6" s="1"/>
       <c r="R6" s="1"/>
       <c r="S6" s="1"/>
       <c r="T6" s="1"/>
-      <c r="U6" s="1" t="s">
-        <v>54</v>
-      </c>
+      <c r="U6" s="1"/>
       <c r="V6" s="1"/>
-      <c r="W6" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="X6" s="1" t="s">
-        <v>54</v>
-      </c>
+      <c r="W6" s="1"/>
+      <c r="X6" s="1"/>
     </row>
     <row r="7" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
@@ -1079,25 +1135,15 @@
         <v>1</v>
       </c>
       <c r="M7" s="1"/>
-      <c r="P7" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="Q7" s="1" t="s">
-        <v>54</v>
-      </c>
+      <c r="P7" s="1"/>
+      <c r="Q7" s="1"/>
       <c r="R7" s="1"/>
       <c r="S7" s="1"/>
       <c r="T7" s="1"/>
-      <c r="U7" s="1" t="s">
-        <v>54</v>
-      </c>
+      <c r="U7" s="1"/>
       <c r="V7" s="1"/>
-      <c r="W7" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="X7" s="1" t="s">
-        <v>54</v>
-      </c>
+      <c r="W7" s="1"/>
+      <c r="X7" s="1"/>
     </row>
     <row r="8" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
@@ -1131,25 +1177,15 @@
       <c r="M8" s="1">
         <v>8</v>
       </c>
-      <c r="P8" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="Q8" s="1" t="s">
-        <v>54</v>
-      </c>
+      <c r="P8" s="1"/>
+      <c r="Q8" s="1"/>
       <c r="R8" s="1"/>
       <c r="S8" s="1"/>
       <c r="T8" s="1"/>
-      <c r="U8" s="1" t="s">
-        <v>54</v>
-      </c>
+      <c r="U8" s="1"/>
       <c r="V8" s="1"/>
-      <c r="W8" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="X8" s="1" t="s">
-        <v>54</v>
-      </c>
+      <c r="W8" s="1"/>
+      <c r="X8" s="1"/>
     </row>
     <row r="9" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
@@ -1173,7 +1209,7 @@
         <v>10</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J9" s="1">
         <v>6</v>
@@ -1187,25 +1223,17 @@
       <c r="M9" s="1">
         <v>8</v>
       </c>
-      <c r="P9" s="1" t="s">
-        <v>54</v>
-      </c>
+      <c r="P9" s="1"/>
       <c r="Q9" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="R9" s="1"/>
       <c r="S9" s="1"/>
       <c r="T9" s="1"/>
-      <c r="U9" s="1" t="s">
-        <v>54</v>
-      </c>
+      <c r="U9" s="1"/>
       <c r="V9" s="1"/>
-      <c r="W9" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="X9" s="1" t="s">
-        <v>54</v>
-      </c>
+      <c r="W9" s="1"/>
+      <c r="X9" s="1"/>
     </row>
     <row r="10" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
@@ -1231,9 +1259,7 @@
         <v>10</v>
       </c>
       <c r="M10" s="3"/>
-      <c r="Q10" s="1" t="s">
-        <v>63</v>
-      </c>
+      <c r="Q10" s="1"/>
     </row>
     <row r="11" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
@@ -1255,7 +1281,7 @@
         <v>10</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J11" s="1">
         <v>6</v>
@@ -1269,9 +1295,7 @@
       <c r="M11" s="1">
         <v>8</v>
       </c>
-      <c r="Q11" s="1" t="s">
-        <v>63</v>
-      </c>
+      <c r="Q11" s="1"/>
     </row>
     <row r="12" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
@@ -1292,10 +1316,10 @@
         <v>24</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J12" s="1">
         <v>6</v>
@@ -1309,11 +1333,12 @@
       <c r="M12" s="1">
         <v>8</v>
       </c>
-      <c r="Q12" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="R12" s="4" t="s">
-        <v>64</v>
+      <c r="Q12" s="1"/>
+      <c r="R12" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="W12" s="1" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="13" spans="1:38" x14ac:dyDescent="0.25">
@@ -1333,10 +1358,10 @@
       </c>
       <c r="G13" s="1"/>
       <c r="H13" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J13" s="1">
         <v>6</v>
@@ -1350,12 +1375,8 @@
       <c r="M13" s="1">
         <v>8</v>
       </c>
-      <c r="Q13" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="R13" s="4" t="s">
-        <v>64</v>
-      </c>
+      <c r="Q13" s="1"/>
+      <c r="R13" s="1"/>
     </row>
     <row r="14" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
@@ -1374,10 +1395,10 @@
         <v>34</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J14" s="1">
         <v>6</v>
@@ -1391,11 +1412,9 @@
       <c r="M14" s="1">
         <v>8</v>
       </c>
-      <c r="Q14" s="1" t="s">
+      <c r="Q14" s="1"/>
+      <c r="R14" s="1" t="s">
         <v>63</v>
-      </c>
-      <c r="R14" s="4" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="15" spans="1:38" x14ac:dyDescent="0.25">
@@ -1415,10 +1434,10 @@
         <v>44</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J15" s="1">
         <v>6</v>
@@ -1432,11 +1451,16 @@
       <c r="M15" s="1">
         <v>8</v>
       </c>
-      <c r="Q15" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="R15" s="4" t="s">
-        <v>66</v>
+      <c r="Q15" s="1"/>
+      <c r="R15" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="S15" s="1">
+        <v>0</v>
+      </c>
+      <c r="T15" s="1"/>
+      <c r="U15" s="1" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="16" spans="1:38" x14ac:dyDescent="0.25">
@@ -1447,7 +1471,7 @@
         <v>3</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
@@ -1456,10 +1480,10 @@
       </c>
       <c r="G16" s="1"/>
       <c r="H16" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J16" s="1">
         <v>12</v>
@@ -1473,14 +1497,10 @@
       <c r="M16" s="1">
         <v>8</v>
       </c>
-      <c r="Q16" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="R16" s="4" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="Q16" s="1"/>
+      <c r="R16" s="1"/>
+    </row>
+    <row r="17" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -1495,10 +1515,10 @@
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
       <c r="H17" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J17" s="1">
         <v>12</v>
@@ -1512,21 +1532,17 @@
       <c r="M17" s="1">
         <v>8</v>
       </c>
-      <c r="Q17" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="R17" s="4" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A18" s="1">
+      <c r="Q17" s="1"/>
+      <c r="R17" s="1"/>
+    </row>
+    <row r="18" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A18" s="6">
         <v>16</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D18" s="1"/>
@@ -1536,10 +1552,10 @@
         <v>56</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J18" s="1">
         <v>12</v>
@@ -1554,13 +1570,18 @@
         <v>8</v>
       </c>
       <c r="Q18" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="R18" s="4" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+      <c r="R18" s="1"/>
+      <c r="S18" s="1">
+        <v>1</v>
+      </c>
+      <c r="T18" s="1"/>
+      <c r="U18" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="19" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>16.100000000000001</v>
       </c>
@@ -1576,14 +1597,13 @@
         <v>57</v>
       </c>
       <c r="G19" s="3"/>
-      <c r="Q19" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="R19" s="4" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="Q19" s="7"/>
+      <c r="R19" s="1"/>
+      <c r="S19" s="1"/>
+      <c r="T19" s="1"/>
+      <c r="U19" s="1"/>
+    </row>
+    <row r="20" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>17</v>
       </c>
@@ -1598,10 +1618,10 @@
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
       <c r="H20" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J20" s="1">
         <v>12</v>
@@ -1615,28 +1635,30 @@
       <c r="M20" s="1">
         <v>0</v>
       </c>
-      <c r="Q20" s="7" t="s">
+      <c r="Q20" s="7"/>
+      <c r="R20" s="1"/>
+      <c r="S20" s="1"/>
+      <c r="T20" s="1"/>
+      <c r="U20" s="1"/>
+    </row>
+    <row r="21" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>18</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G21" s="1">
         <v>67</v>
       </c>
-      <c r="R20" s="4" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A21" s="4">
-        <v>18</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>30</v>
-      </c>
       <c r="H21" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J21" s="1">
         <v>12</v>
@@ -1651,13 +1673,11 @@
         <v>0</v>
       </c>
       <c r="Q21" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="R21" s="4" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+      <c r="R21" s="1"/>
+    </row>
+    <row r="22" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <v>18.100000000000001</v>
       </c>
@@ -1679,28 +1699,24 @@
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
-      <c r="Q22" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="R22" s="4" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A23" s="4">
+      <c r="Q22" s="7"/>
+      <c r="R22" s="1"/>
+    </row>
+    <row r="23" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
         <v>19</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C23" s="1" t="s">
         <v>23</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J23" s="1">
         <v>12</v>
@@ -1714,28 +1730,30 @@
       <c r="M23" s="1">
         <v>0</v>
       </c>
-      <c r="Q23" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="R23" s="4" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A24" s="4">
-        <v>20</v>
-      </c>
-      <c r="B24" s="2" t="s">
+      <c r="Q23" s="7"/>
+      <c r="R23" s="1"/>
+    </row>
+    <row r="24" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>20</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C24" s="1" t="s">
         <v>24</v>
       </c>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1">
+        <v>78</v>
+      </c>
       <c r="H24" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J24" s="1">
         <v>12</v>
@@ -1749,55 +1767,8315 @@
       <c r="M24" s="1">
         <v>0</v>
       </c>
-      <c r="Q24" s="7" t="s">
+      <c r="N24" s="1"/>
+      <c r="O24" s="1"/>
+      <c r="P24" s="1"/>
+      <c r="Q24" s="1"/>
+      <c r="R24" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="S24" s="1"/>
+      <c r="T24" s="1"/>
+      <c r="U24" s="1"/>
+      <c r="V24" s="1"/>
+      <c r="W24" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="X24" s="1"/>
+      <c r="Y24" s="1"/>
+      <c r="Z24" s="1"/>
+      <c r="AA24" s="1"/>
+      <c r="AB24" s="1"/>
+    </row>
+    <row r="25" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>21</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="J25" s="1"/>
+      <c r="K25" s="1"/>
+      <c r="L25" s="1"/>
+      <c r="M25" s="1"/>
+      <c r="N25" s="1"/>
+      <c r="O25" s="1"/>
+      <c r="P25" s="1"/>
+      <c r="Q25" s="1"/>
+      <c r="R25" s="1"/>
+      <c r="S25" s="1"/>
+      <c r="T25" s="1"/>
+      <c r="U25" s="1"/>
+      <c r="V25" s="1"/>
+      <c r="W25" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="X25" s="1"/>
+      <c r="Y25" s="1"/>
+      <c r="Z25" s="1"/>
+      <c r="AA25" s="1"/>
+      <c r="AB25" s="1"/>
+    </row>
+    <row r="26" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
+        <v>22</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1">
+        <v>88</v>
+      </c>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="J26" s="1"/>
+      <c r="K26" s="1"/>
+      <c r="L26" s="1"/>
+      <c r="M26" s="1"/>
+      <c r="N26" s="1"/>
+      <c r="O26" s="1"/>
+      <c r="P26" s="1"/>
+      <c r="Q26" s="1"/>
+      <c r="R26" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="S26" s="1"/>
+      <c r="T26" s="1"/>
+      <c r="U26" s="1"/>
+      <c r="V26" s="1"/>
+      <c r="W26" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="X26" s="1"/>
+      <c r="Y26" s="1"/>
+      <c r="Z26" s="1"/>
+      <c r="AA26" s="1"/>
+      <c r="AB26" s="1"/>
+    </row>
+    <row r="27" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
+        <v>23</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1">
+        <v>98</v>
+      </c>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="J27" s="1"/>
+      <c r="K27" s="1"/>
+      <c r="L27" s="1"/>
+      <c r="M27" s="1"/>
+      <c r="N27" s="1"/>
+      <c r="O27" s="1"/>
+      <c r="P27" s="1"/>
+      <c r="Q27" s="1"/>
+      <c r="R27" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="S27" s="1">
+        <v>3</v>
+      </c>
+      <c r="T27" s="1"/>
+      <c r="U27" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="V27" s="1"/>
+      <c r="W27" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="X27" s="1"/>
+      <c r="Y27" s="1"/>
+      <c r="Z27" s="1"/>
+      <c r="AA27" s="1"/>
+      <c r="AB27" s="1"/>
+    </row>
+    <row r="28" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A28" s="2"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2">
+        <v>112</v>
+      </c>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+      <c r="K28" s="2"/>
+      <c r="L28" s="2"/>
+      <c r="M28" s="2"/>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
+      <c r="P28" s="2"/>
+      <c r="Q28" s="2"/>
+      <c r="R28" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="S28" s="1"/>
+      <c r="T28" s="1"/>
+      <c r="U28" s="1"/>
+      <c r="V28" s="1"/>
+      <c r="W28" s="1"/>
+      <c r="X28" s="1"/>
+      <c r="Y28" s="1"/>
+      <c r="Z28" s="1"/>
+      <c r="AA28" s="1"/>
+      <c r="AB28" s="1"/>
+    </row>
+    <row r="29" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
+        <v>24</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I29" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J29" s="4">
+        <v>18</v>
+      </c>
+      <c r="K29" s="4">
+        <v>0</v>
+      </c>
+      <c r="L29" s="4">
+        <v>10</v>
+      </c>
+      <c r="M29" s="4">
+        <v>0</v>
+      </c>
+      <c r="N29" s="1"/>
+      <c r="O29" s="1"/>
+      <c r="P29" s="1"/>
+      <c r="Q29" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R29" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="S29" s="1"/>
+      <c r="T29" s="1"/>
+      <c r="U29" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W29" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y29" s="1"/>
+      <c r="Z29" s="1"/>
+      <c r="AA29" s="1"/>
+      <c r="AB29" s="1"/>
+    </row>
+    <row r="30" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
+        <v>25</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I30" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J30" s="4">
+        <v>18</v>
+      </c>
+      <c r="K30" s="4">
+        <v>2</v>
+      </c>
+      <c r="L30" s="4">
+        <v>10</v>
+      </c>
+      <c r="M30" s="4">
+        <v>0</v>
+      </c>
+      <c r="N30" s="1"/>
+      <c r="O30" s="1"/>
+      <c r="P30" s="1"/>
+      <c r="Q30" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R30" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="S30" s="1"/>
+      <c r="T30" s="1"/>
+      <c r="U30" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W30" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y30" s="1"/>
+      <c r="Z30" s="1"/>
+      <c r="AA30" s="1"/>
+      <c r="AB30" s="1"/>
+    </row>
+    <row r="31" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
+        <v>26</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I31" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J31" s="4">
+        <v>18</v>
+      </c>
+      <c r="K31" s="4">
+        <v>2</v>
+      </c>
+      <c r="L31" s="4">
+        <v>10</v>
+      </c>
+      <c r="M31" s="4">
+        <v>0</v>
+      </c>
+      <c r="N31" s="1"/>
+      <c r="O31" s="1"/>
+      <c r="P31" s="1"/>
+      <c r="Q31" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R31" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="S31" s="1"/>
+      <c r="T31" s="1"/>
+      <c r="U31" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="W31" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y31" s="1"/>
+      <c r="Z31" s="1"/>
+      <c r="AA31" s="1"/>
+      <c r="AB31" s="1"/>
+    </row>
+    <row r="32" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
+        <v>27</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I32" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J32" s="4">
+        <v>18</v>
+      </c>
+      <c r="K32" s="4">
+        <v>2</v>
+      </c>
+      <c r="L32" s="4">
+        <v>1</v>
+      </c>
+      <c r="M32" s="4">
+        <v>0</v>
+      </c>
+      <c r="N32" s="1"/>
+      <c r="O32" s="1"/>
+      <c r="P32" s="1"/>
+      <c r="Q32" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R32" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="S32" s="1"/>
+      <c r="T32" s="1"/>
+      <c r="U32" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W32" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y32" s="1"/>
+      <c r="Z32" s="1"/>
+      <c r="AA32" s="1"/>
+      <c r="AB32" s="1"/>
+    </row>
+    <row r="33" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
+        <v>28</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I33" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J33" s="4">
+        <v>18</v>
+      </c>
+      <c r="K33" s="4">
+        <v>2</v>
+      </c>
+      <c r="L33" s="4">
+        <v>1</v>
+      </c>
+      <c r="M33" s="4">
+        <v>8</v>
+      </c>
+      <c r="N33" s="1"/>
+      <c r="O33" s="1"/>
+      <c r="P33" s="1"/>
+      <c r="Q33" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R33" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="S33" s="1"/>
+      <c r="T33" s="1"/>
+      <c r="U33" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W33" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y33" s="1"/>
+      <c r="Z33" s="1"/>
+      <c r="AA33" s="1"/>
+      <c r="AB33" s="1"/>
+    </row>
+    <row r="34" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A34" s="1">
+        <v>29</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I34" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J34" s="4">
+        <v>18</v>
+      </c>
+      <c r="K34" s="4">
+        <v>2</v>
+      </c>
+      <c r="L34" s="4">
+        <v>1</v>
+      </c>
+      <c r="M34" s="4">
+        <v>8</v>
+      </c>
+      <c r="N34" s="1"/>
+      <c r="O34" s="1"/>
+      <c r="P34" s="1"/>
+      <c r="Q34" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R34" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="S34" s="1"/>
+      <c r="T34" s="1"/>
+      <c r="U34" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W34" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y34" s="1"/>
+      <c r="Z34" s="1"/>
+      <c r="AA34" s="1"/>
+      <c r="AB34" s="1"/>
+    </row>
+    <row r="35" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A35" s="1">
+        <v>30</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I35" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="J35" s="4">
+        <v>18</v>
+      </c>
+      <c r="K35" s="4">
+        <v>2</v>
+      </c>
+      <c r="L35" s="4">
+        <v>1</v>
+      </c>
+      <c r="M35" s="4">
+        <v>8</v>
+      </c>
+      <c r="N35" s="1"/>
+      <c r="O35" s="1"/>
+      <c r="P35" s="1"/>
+      <c r="Q35" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R35" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="S35" s="1"/>
+      <c r="T35" s="1"/>
+      <c r="U35" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W35" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y35" s="1"/>
+      <c r="Z35" s="1"/>
+      <c r="AA35" s="1"/>
+      <c r="AB35" s="1"/>
+    </row>
+    <row r="36" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A36" s="1">
+        <v>31</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
+      <c r="H36" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I36" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="J36" s="4">
+        <v>18</v>
+      </c>
+      <c r="K36" s="4">
+        <v>2</v>
+      </c>
+      <c r="L36" s="4">
+        <v>1</v>
+      </c>
+      <c r="M36" s="4">
+        <v>8</v>
+      </c>
+      <c r="N36" s="1"/>
+      <c r="O36" s="1"/>
+      <c r="P36" s="1"/>
+      <c r="Q36" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R36" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="S36" s="1"/>
+      <c r="T36" s="1"/>
+      <c r="U36" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W36" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="Y36" s="1"/>
+      <c r="Z36" s="1"/>
+      <c r="AA36" s="1"/>
+      <c r="AB36" s="1"/>
+    </row>
+    <row r="37" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A37" s="1">
+        <v>32</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D37" s="1"/>
+      <c r="E37" s="1"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1"/>
+      <c r="H37" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I37" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="J37" s="4">
+        <v>18</v>
+      </c>
+      <c r="K37" s="4">
+        <v>2</v>
+      </c>
+      <c r="L37" s="4">
+        <v>20</v>
+      </c>
+      <c r="M37" s="4">
+        <v>8</v>
+      </c>
+      <c r="N37" s="1"/>
+      <c r="O37" s="1"/>
+      <c r="P37" s="1"/>
+      <c r="Q37" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R37" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="S37" s="1"/>
+      <c r="T37" s="1"/>
+      <c r="U37" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W37" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y37" s="1"/>
+      <c r="Z37" s="1"/>
+      <c r="AA37" s="1"/>
+      <c r="AB37" s="1"/>
+    </row>
+    <row r="38" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A38" s="1">
+        <v>33</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
+      <c r="H38" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I38" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="J38" s="4">
+        <v>18</v>
+      </c>
+      <c r="K38" s="4">
+        <v>2</v>
+      </c>
+      <c r="L38" s="4">
+        <v>20</v>
+      </c>
+      <c r="M38" s="4">
+        <v>8</v>
+      </c>
+      <c r="N38" s="1"/>
+      <c r="O38" s="1"/>
+      <c r="P38" s="1"/>
+      <c r="Q38" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R38" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="S38" s="1"/>
+      <c r="T38" s="1"/>
+      <c r="U38" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W38" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y38" s="1"/>
+      <c r="Z38" s="1"/>
+      <c r="AA38" s="1"/>
+      <c r="AB38" s="1"/>
+    </row>
+    <row r="39" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A39" s="1">
+        <v>34</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D39" s="1"/>
+      <c r="E39" s="1"/>
+      <c r="F39" s="1"/>
+      <c r="G39" s="1"/>
+      <c r="H39" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I39" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="J39" s="4">
+        <v>18</v>
+      </c>
+      <c r="K39" s="4">
+        <v>2</v>
+      </c>
+      <c r="L39" s="4">
+        <v>20</v>
+      </c>
+      <c r="M39" s="4">
+        <v>8</v>
+      </c>
+      <c r="N39" s="1"/>
+      <c r="O39" s="1"/>
+      <c r="P39" s="1"/>
+      <c r="Q39" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R39" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="S39" s="1">
+        <v>7</v>
+      </c>
+      <c r="T39" s="1"/>
+      <c r="U39" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="W39" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y39" s="1"/>
+      <c r="Z39" s="1"/>
+      <c r="AA39" s="1"/>
+      <c r="AB39" s="1"/>
+    </row>
+    <row r="40" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A40" s="1">
+        <v>35</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D40" s="1"/>
+      <c r="E40" s="1"/>
+      <c r="F40" s="1"/>
+      <c r="G40" s="1"/>
+      <c r="H40" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I40" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="J40" s="4">
+        <v>24</v>
+      </c>
+      <c r="K40" s="4">
+        <v>2</v>
+      </c>
+      <c r="L40" s="4">
+        <v>20</v>
+      </c>
+      <c r="M40" s="4">
+        <v>8</v>
+      </c>
+      <c r="N40" s="1"/>
+      <c r="O40" s="1"/>
+      <c r="P40" s="1"/>
+      <c r="Q40" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R40" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="S40" s="1"/>
+      <c r="T40" s="1"/>
+      <c r="U40" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W40" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y40" s="1"/>
+      <c r="Z40" s="1"/>
+      <c r="AA40" s="1"/>
+      <c r="AB40" s="1"/>
+    </row>
+    <row r="41" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A41" s="1">
+        <v>36</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D41" s="1"/>
+      <c r="E41" s="1"/>
+      <c r="F41" s="1"/>
+      <c r="G41" s="1"/>
+      <c r="H41" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I41" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="J41" s="4">
+        <v>24</v>
+      </c>
+      <c r="K41" s="4">
+        <v>0</v>
+      </c>
+      <c r="L41" s="4">
+        <v>20</v>
+      </c>
+      <c r="M41" s="4">
+        <v>8</v>
+      </c>
+      <c r="N41" s="1"/>
+      <c r="O41" s="1"/>
+      <c r="P41" s="1"/>
+      <c r="Q41" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R41" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="S41" s="1"/>
+      <c r="T41" s="1"/>
+      <c r="U41" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W41" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y41" s="1"/>
+      <c r="Z41" s="1"/>
+      <c r="AA41" s="1"/>
+      <c r="AB41" s="1"/>
+    </row>
+    <row r="42" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A42" s="1">
+        <v>37</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D42" s="1"/>
+      <c r="E42" s="1"/>
+      <c r="F42" s="1"/>
+      <c r="G42" s="1"/>
+      <c r="H42" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I42" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="J42" s="4">
+        <v>24</v>
+      </c>
+      <c r="K42" s="4">
+        <v>0</v>
+      </c>
+      <c r="L42" s="4">
+        <v>20</v>
+      </c>
+      <c r="M42" s="4">
+        <v>8</v>
+      </c>
+      <c r="N42" s="1"/>
+      <c r="O42" s="1"/>
+      <c r="P42" s="1"/>
+      <c r="Q42" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="R42" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="S42" s="1"/>
+      <c r="T42" s="1"/>
+      <c r="U42" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="W42" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y42" s="1"/>
+      <c r="Z42" s="1"/>
+      <c r="AA42" s="1"/>
+      <c r="AB42" s="1"/>
+    </row>
+    <row r="43" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A43" s="1">
+        <v>38</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D43" s="1"/>
+      <c r="E43" s="1"/>
+      <c r="F43" s="1"/>
+      <c r="G43" s="1"/>
+      <c r="H43" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I43" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="J43" s="4">
+        <v>24</v>
+      </c>
+      <c r="K43" s="4">
+        <v>0</v>
+      </c>
+      <c r="L43" s="4">
+        <v>20</v>
+      </c>
+      <c r="M43" s="4">
+        <v>0</v>
+      </c>
+      <c r="N43" s="1"/>
+      <c r="O43" s="1"/>
+      <c r="P43" s="1"/>
+      <c r="Q43" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="R43" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="S43" s="1"/>
+      <c r="T43" s="1"/>
+      <c r="U43" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W43" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y43" s="1"/>
+      <c r="Z43" s="1"/>
+      <c r="AA43" s="1"/>
+      <c r="AB43" s="1"/>
+    </row>
+    <row r="44" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A44" s="1">
+        <v>39</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D44" s="1"/>
+      <c r="E44" s="1"/>
+      <c r="F44" s="1"/>
+      <c r="G44" s="1"/>
+      <c r="H44" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I44" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J44" s="4">
+        <v>24</v>
+      </c>
+      <c r="K44" s="4">
+        <v>0</v>
+      </c>
+      <c r="L44" s="4">
+        <v>20</v>
+      </c>
+      <c r="M44" s="4">
+        <v>0</v>
+      </c>
+      <c r="N44" s="1"/>
+      <c r="O44" s="1"/>
+      <c r="P44" s="1"/>
+      <c r="Q44" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R44" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="S44" s="1"/>
+      <c r="T44" s="1"/>
+      <c r="U44" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W44" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y44" s="1"/>
+      <c r="Z44" s="1"/>
+      <c r="AA44" s="1"/>
+      <c r="AB44" s="1"/>
+    </row>
+    <row r="45" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A45" s="1">
+        <v>40</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D45" s="1"/>
+      <c r="E45" s="1"/>
+      <c r="F45" s="1"/>
+      <c r="G45" s="1"/>
+      <c r="H45" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I45" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J45" s="4">
+        <v>24</v>
+      </c>
+      <c r="K45" s="4">
+        <v>0</v>
+      </c>
+      <c r="L45" s="4">
+        <v>20</v>
+      </c>
+      <c r="M45" s="4">
+        <v>0</v>
+      </c>
+      <c r="N45" s="1"/>
+      <c r="O45" s="1"/>
+      <c r="P45" s="1"/>
+      <c r="Q45" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R45" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="S45" s="1"/>
+      <c r="T45" s="1"/>
+      <c r="U45" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W45" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y45" s="1"/>
+      <c r="Z45" s="1"/>
+      <c r="AA45" s="1"/>
+      <c r="AB45" s="1"/>
+    </row>
+    <row r="46" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A46" s="1">
+        <v>41</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D46" s="1"/>
+      <c r="E46" s="1"/>
+      <c r="F46" s="1"/>
+      <c r="G46" s="1"/>
+      <c r="H46" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I46" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J46" s="4">
+        <v>24</v>
+      </c>
+      <c r="K46" s="4">
+        <v>0</v>
+      </c>
+      <c r="L46" s="4">
+        <v>20</v>
+      </c>
+      <c r="M46" s="4">
+        <v>0</v>
+      </c>
+      <c r="N46" s="1"/>
+      <c r="O46" s="1"/>
+      <c r="P46" s="1"/>
+      <c r="Q46" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R46" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="S46" s="1"/>
+      <c r="T46" s="1"/>
+      <c r="U46" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W46" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="Y46" s="1"/>
+      <c r="Z46" s="1"/>
+      <c r="AA46" s="1"/>
+      <c r="AB46" s="1"/>
+    </row>
+    <row r="47" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A47" s="1">
+        <v>42</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D47" s="1"/>
+      <c r="E47" s="1"/>
+      <c r="F47" s="1"/>
+      <c r="G47" s="1"/>
+      <c r="H47" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I47" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J47" s="4">
+        <v>24</v>
+      </c>
+      <c r="K47" s="4">
+        <v>0</v>
+      </c>
+      <c r="L47" s="4">
+        <v>10</v>
+      </c>
+      <c r="M47" s="4">
+        <v>0</v>
+      </c>
+      <c r="N47" s="1"/>
+      <c r="O47" s="1"/>
+      <c r="P47" s="1"/>
+      <c r="Q47" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R47" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="S47" s="1"/>
+      <c r="T47" s="1"/>
+      <c r="U47" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W47" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y47" s="1"/>
+      <c r="Z47" s="1"/>
+      <c r="AA47" s="1"/>
+      <c r="AB47" s="1"/>
+    </row>
+    <row r="48" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A48" s="1">
+        <v>43</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D48" s="1"/>
+      <c r="E48" s="1"/>
+      <c r="F48" s="1"/>
+      <c r="G48" s="1"/>
+      <c r="H48" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I48" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J48" s="4">
+        <v>24</v>
+      </c>
+      <c r="K48" s="4">
+        <v>0</v>
+      </c>
+      <c r="L48" s="4">
+        <v>10</v>
+      </c>
+      <c r="M48" s="4">
+        <v>0</v>
+      </c>
+      <c r="N48" s="1"/>
+      <c r="O48" s="1"/>
+      <c r="P48" s="1"/>
+      <c r="Q48" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R48" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="S48" s="1"/>
+      <c r="T48" s="1"/>
+      <c r="U48" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W48" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y48" s="1"/>
+      <c r="Z48" s="1"/>
+      <c r="AA48" s="1"/>
+      <c r="AB48" s="1"/>
+    </row>
+    <row r="49" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A49" s="1">
+        <v>44</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D49" s="1"/>
+      <c r="E49" s="1"/>
+      <c r="F49" s="1"/>
+      <c r="G49" s="1"/>
+      <c r="H49" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I49" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J49" s="4">
+        <v>24</v>
+      </c>
+      <c r="K49" s="4">
+        <v>0</v>
+      </c>
+      <c r="L49" s="4">
+        <v>10</v>
+      </c>
+      <c r="M49" s="4">
+        <v>0</v>
+      </c>
+      <c r="N49" s="1"/>
+      <c r="O49" s="1"/>
+      <c r="P49" s="1"/>
+      <c r="Q49" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R49" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="S49" s="1"/>
+      <c r="T49" s="1"/>
+      <c r="U49" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="W49" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y49" s="1"/>
+      <c r="Z49" s="1"/>
+      <c r="AA49" s="1"/>
+      <c r="AB49" s="1"/>
+    </row>
+    <row r="50" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A50" s="1">
+        <v>45</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D50" s="1"/>
+      <c r="E50" s="1"/>
+      <c r="F50" s="1"/>
+      <c r="G50" s="1"/>
+      <c r="H50" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I50" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J50" s="4">
+        <v>30</v>
+      </c>
+      <c r="K50" s="4">
+        <v>0</v>
+      </c>
+      <c r="L50" s="4">
+        <v>10</v>
+      </c>
+      <c r="M50" s="4">
+        <v>0</v>
+      </c>
+      <c r="N50" s="1"/>
+      <c r="O50" s="1"/>
+      <c r="P50" s="1"/>
+      <c r="Q50" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R50" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="S50" s="1"/>
+      <c r="T50" s="1"/>
+      <c r="U50" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W50" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y50" s="1"/>
+      <c r="Z50" s="1"/>
+      <c r="AA50" s="1"/>
+      <c r="AB50" s="1"/>
+    </row>
+    <row r="51" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A51" s="1">
+        <v>46</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D51" s="1"/>
+      <c r="E51" s="1"/>
+      <c r="F51" s="1"/>
+      <c r="G51" s="1"/>
+      <c r="H51" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I51" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J51" s="4">
+        <v>30</v>
+      </c>
+      <c r="K51" s="4">
+        <v>2</v>
+      </c>
+      <c r="L51" s="4">
+        <v>10</v>
+      </c>
+      <c r="M51" s="4">
+        <v>0</v>
+      </c>
+      <c r="N51" s="1"/>
+      <c r="O51" s="1"/>
+      <c r="P51" s="1"/>
+      <c r="Q51" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R51" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="S51" s="1"/>
+      <c r="T51" s="1"/>
+      <c r="U51" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W51" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y51" s="1"/>
+      <c r="Z51" s="1"/>
+      <c r="AA51" s="1"/>
+      <c r="AB51" s="1"/>
+    </row>
+    <row r="52" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A52" s="1">
+        <v>47</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D52" s="1"/>
+      <c r="E52" s="1"/>
+      <c r="F52" s="1"/>
+      <c r="G52" s="1"/>
+      <c r="H52" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I52" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J52" s="4">
+        <v>30</v>
+      </c>
+      <c r="K52" s="4">
+        <v>2</v>
+      </c>
+      <c r="L52" s="4">
+        <v>10</v>
+      </c>
+      <c r="M52" s="4">
+        <v>0</v>
+      </c>
+      <c r="N52" s="1"/>
+      <c r="O52" s="1"/>
+      <c r="P52" s="1"/>
+      <c r="Q52" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R52" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="S52" s="1"/>
+      <c r="T52" s="1"/>
+      <c r="U52" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="W52" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y52" s="1"/>
+      <c r="Z52" s="1"/>
+      <c r="AA52" s="1"/>
+      <c r="AB52" s="1"/>
+    </row>
+    <row r="53" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A53" s="1">
+        <v>48</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D53" s="1"/>
+      <c r="E53" s="1"/>
+      <c r="F53" s="1"/>
+      <c r="G53" s="1"/>
+      <c r="H53" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I53" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J53" s="4">
+        <v>30</v>
+      </c>
+      <c r="K53" s="4">
+        <v>2</v>
+      </c>
+      <c r="L53" s="4">
+        <v>1</v>
+      </c>
+      <c r="M53" s="4">
+        <v>0</v>
+      </c>
+      <c r="N53" s="1"/>
+      <c r="O53" s="1"/>
+      <c r="P53" s="1"/>
+      <c r="Q53" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R53" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="S53" s="1"/>
+      <c r="T53" s="1"/>
+      <c r="U53" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W53" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y53" s="1"/>
+      <c r="Z53" s="1"/>
+      <c r="AA53" s="1"/>
+      <c r="AB53" s="1"/>
+    </row>
+    <row r="54" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A54" s="1">
+        <v>49</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D54" s="1"/>
+      <c r="E54" s="1"/>
+      <c r="F54" s="1"/>
+      <c r="G54" s="1"/>
+      <c r="H54" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I54" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J54" s="4">
+        <v>30</v>
+      </c>
+      <c r="K54" s="4">
+        <v>2</v>
+      </c>
+      <c r="L54" s="4">
+        <v>1</v>
+      </c>
+      <c r="M54" s="4">
+        <v>8</v>
+      </c>
+      <c r="N54" s="1"/>
+      <c r="O54" s="1"/>
+      <c r="P54" s="1"/>
+      <c r="Q54" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R54" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="S54" s="1"/>
+      <c r="T54" s="1"/>
+      <c r="U54" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W54" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y54" s="1"/>
+      <c r="Z54" s="1"/>
+      <c r="AA54" s="1"/>
+      <c r="AB54" s="1"/>
+    </row>
+    <row r="55" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A55" s="1">
+        <v>50</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D55" s="1"/>
+      <c r="E55" s="1"/>
+      <c r="F55" s="1"/>
+      <c r="G55" s="1"/>
+      <c r="H55" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I55" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J55" s="4">
+        <v>30</v>
+      </c>
+      <c r="K55" s="4">
+        <v>2</v>
+      </c>
+      <c r="L55" s="4">
+        <v>1</v>
+      </c>
+      <c r="M55" s="4">
+        <v>8</v>
+      </c>
+      <c r="N55" s="1"/>
+      <c r="O55" s="1"/>
+      <c r="P55" s="1"/>
+      <c r="Q55" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R55" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="S55" s="1"/>
+      <c r="T55" s="1"/>
+      <c r="U55" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W55" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y55" s="1"/>
+      <c r="Z55" s="1"/>
+      <c r="AA55" s="1"/>
+      <c r="AB55" s="1"/>
+    </row>
+    <row r="56" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A56" s="1">
+        <v>51</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D56" s="1"/>
+      <c r="E56" s="1"/>
+      <c r="F56" s="1"/>
+      <c r="G56" s="1"/>
+      <c r="H56" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I56" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="J56" s="4">
+        <v>30</v>
+      </c>
+      <c r="K56" s="4">
+        <v>2</v>
+      </c>
+      <c r="L56" s="4">
+        <v>1</v>
+      </c>
+      <c r="M56" s="4">
+        <v>8</v>
+      </c>
+      <c r="N56" s="1"/>
+      <c r="O56" s="1"/>
+      <c r="P56" s="1"/>
+      <c r="Q56" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R56" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="S56" s="1"/>
+      <c r="T56" s="1"/>
+      <c r="U56" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W56" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y56" s="1"/>
+      <c r="Z56" s="1"/>
+      <c r="AA56" s="1"/>
+      <c r="AB56" s="1"/>
+    </row>
+    <row r="57" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A57" s="1">
+        <v>52</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D57" s="1"/>
+      <c r="E57" s="1"/>
+      <c r="F57" s="1"/>
+      <c r="G57" s="1"/>
+      <c r="H57" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I57" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="J57" s="4">
+        <v>30</v>
+      </c>
+      <c r="K57" s="4">
+        <v>2</v>
+      </c>
+      <c r="L57" s="4">
+        <v>1</v>
+      </c>
+      <c r="M57" s="4">
+        <v>8</v>
+      </c>
+      <c r="N57" s="1"/>
+      <c r="O57" s="1"/>
+      <c r="P57" s="1"/>
+      <c r="Q57" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R57" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="S57" s="1"/>
+      <c r="T57" s="1"/>
+      <c r="U57" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W57" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="Y57" s="1"/>
+      <c r="Z57" s="1"/>
+      <c r="AA57" s="1"/>
+      <c r="AB57" s="1"/>
+    </row>
+    <row r="58" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A58" s="1">
+        <v>53</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D58" s="1"/>
+      <c r="E58" s="1"/>
+      <c r="F58" s="1"/>
+      <c r="G58" s="1"/>
+      <c r="H58" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I58" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="J58" s="4">
+        <v>30</v>
+      </c>
+      <c r="K58" s="4">
+        <v>2</v>
+      </c>
+      <c r="L58" s="4">
+        <v>20</v>
+      </c>
+      <c r="M58" s="4">
+        <v>8</v>
+      </c>
+      <c r="N58" s="1"/>
+      <c r="O58" s="1"/>
+      <c r="P58" s="1"/>
+      <c r="Q58" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R58" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="S58" s="1"/>
+      <c r="T58" s="1"/>
+      <c r="U58" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W58" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y58" s="1"/>
+      <c r="Z58" s="1"/>
+      <c r="AA58" s="1"/>
+      <c r="AB58" s="1"/>
+    </row>
+    <row r="59" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A59" s="1">
+        <v>54</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D59" s="1"/>
+      <c r="E59" s="1"/>
+      <c r="F59" s="1"/>
+      <c r="G59" s="1"/>
+      <c r="H59" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I59" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="J59" s="4">
+        <v>30</v>
+      </c>
+      <c r="K59" s="4">
+        <v>2</v>
+      </c>
+      <c r="L59" s="4">
+        <v>20</v>
+      </c>
+      <c r="M59" s="4">
+        <v>8</v>
+      </c>
+      <c r="N59" s="1"/>
+      <c r="O59" s="1"/>
+      <c r="P59" s="1"/>
+      <c r="Q59" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R59" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="S59" s="1"/>
+      <c r="T59" s="1"/>
+      <c r="U59" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W59" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y59" s="1"/>
+      <c r="Z59" s="1"/>
+      <c r="AA59" s="1"/>
+      <c r="AB59" s="1"/>
+    </row>
+    <row r="60" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A60" s="1">
+        <v>55</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D60" s="1"/>
+      <c r="E60" s="1"/>
+      <c r="F60" s="1"/>
+      <c r="G60" s="1"/>
+      <c r="H60" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I60" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="J60" s="4">
+        <v>30</v>
+      </c>
+      <c r="K60" s="4">
+        <v>2</v>
+      </c>
+      <c r="L60" s="4">
+        <v>20</v>
+      </c>
+      <c r="M60" s="4">
+        <v>8</v>
+      </c>
+      <c r="N60" s="1"/>
+      <c r="O60" s="1"/>
+      <c r="P60" s="1"/>
+      <c r="Q60" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R60" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="S60" s="1"/>
+      <c r="T60" s="1"/>
+      <c r="U60" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="W60" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y60" s="1"/>
+      <c r="Z60" s="1"/>
+      <c r="AA60" s="1"/>
+      <c r="AB60" s="1"/>
+    </row>
+    <row r="61" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A61" s="1">
+        <v>56</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D61" s="1"/>
+      <c r="E61" s="1"/>
+      <c r="F61" s="1"/>
+      <c r="G61" s="1"/>
+      <c r="H61" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I61" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="J61" s="4">
+        <v>36</v>
+      </c>
+      <c r="K61" s="4">
+        <v>2</v>
+      </c>
+      <c r="L61" s="4">
+        <v>20</v>
+      </c>
+      <c r="M61" s="4">
+        <v>8</v>
+      </c>
+      <c r="N61" s="1"/>
+      <c r="O61" s="1"/>
+      <c r="P61" s="1"/>
+      <c r="Q61" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R61" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="S61" s="1"/>
+      <c r="T61" s="1"/>
+      <c r="U61" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W61" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y61" s="1"/>
+      <c r="Z61" s="1"/>
+      <c r="AA61" s="1"/>
+      <c r="AB61" s="1"/>
+    </row>
+    <row r="62" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A62" s="1">
+        <v>57</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I62" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="J62" s="4">
+        <v>36</v>
+      </c>
+      <c r="K62" s="4">
+        <v>0</v>
+      </c>
+      <c r="L62" s="4">
+        <v>20</v>
+      </c>
+      <c r="M62" s="4">
+        <v>8</v>
+      </c>
+      <c r="N62" s="1"/>
+      <c r="O62" s="1"/>
+      <c r="P62" s="1"/>
+      <c r="Q62" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R62" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="S62" s="1"/>
+      <c r="T62" s="1"/>
+      <c r="U62" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W62" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y62" s="1"/>
+      <c r="Z62" s="1"/>
+      <c r="AA62" s="1"/>
+      <c r="AB62" s="1"/>
+    </row>
+    <row r="63" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A63" s="1">
+        <v>58</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D63" s="1"/>
+      <c r="E63" s="1"/>
+      <c r="F63" s="1"/>
+      <c r="G63" s="1"/>
+      <c r="H63" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I63" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="J63" s="4">
+        <v>36</v>
+      </c>
+      <c r="K63" s="4">
+        <v>0</v>
+      </c>
+      <c r="L63" s="4">
+        <v>20</v>
+      </c>
+      <c r="M63" s="4">
+        <v>8</v>
+      </c>
+      <c r="N63" s="1"/>
+      <c r="O63" s="1"/>
+      <c r="P63" s="1"/>
+      <c r="Q63" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="R63" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="S63" s="1"/>
+      <c r="T63" s="1"/>
+      <c r="U63" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="W63" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y63" s="1"/>
+      <c r="Z63" s="1"/>
+      <c r="AA63" s="1"/>
+      <c r="AB63" s="1"/>
+    </row>
+    <row r="64" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A64" s="1">
+        <v>59</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D64" s="1"/>
+      <c r="E64" s="1"/>
+      <c r="F64" s="1"/>
+      <c r="G64" s="1"/>
+      <c r="H64" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I64" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="J64" s="4">
+        <v>36</v>
+      </c>
+      <c r="K64" s="4">
+        <v>0</v>
+      </c>
+      <c r="L64" s="4">
+        <v>20</v>
+      </c>
+      <c r="M64" s="4">
+        <v>0</v>
+      </c>
+      <c r="N64" s="1"/>
+      <c r="O64" s="1"/>
+      <c r="P64" s="1"/>
+      <c r="Q64" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="R64" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="S64" s="1"/>
+      <c r="T64" s="1"/>
+      <c r="U64" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W64" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y64" s="1"/>
+      <c r="Z64" s="1"/>
+      <c r="AA64" s="1"/>
+      <c r="AB64" s="1"/>
+    </row>
+    <row r="65" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A65" s="1">
+        <v>60</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D65" s="1"/>
+      <c r="E65" s="1"/>
+      <c r="F65" s="1"/>
+      <c r="G65" s="1"/>
+      <c r="H65" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I65" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J65" s="4">
+        <v>36</v>
+      </c>
+      <c r="K65" s="4">
+        <v>0</v>
+      </c>
+      <c r="L65" s="4">
+        <v>20</v>
+      </c>
+      <c r="M65" s="4">
+        <v>0</v>
+      </c>
+      <c r="N65" s="1"/>
+      <c r="O65" s="1"/>
+      <c r="P65" s="1"/>
+      <c r="Q65" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R65" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="S65" s="1"/>
+      <c r="T65" s="1"/>
+      <c r="U65" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W65" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y65" s="1"/>
+      <c r="Z65" s="1"/>
+      <c r="AA65" s="1"/>
+      <c r="AB65" s="1"/>
+    </row>
+    <row r="66" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A66" s="1">
+        <v>61</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D66" s="1"/>
+      <c r="E66" s="1"/>
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I66" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J66" s="4">
+        <v>36</v>
+      </c>
+      <c r="K66" s="4">
+        <v>0</v>
+      </c>
+      <c r="L66" s="4">
+        <v>20</v>
+      </c>
+      <c r="M66" s="4">
+        <v>0</v>
+      </c>
+      <c r="N66" s="1"/>
+      <c r="O66" s="1"/>
+      <c r="P66" s="1"/>
+      <c r="Q66" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R66" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="S66" s="1"/>
+      <c r="T66" s="1"/>
+      <c r="U66" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W66" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y66" s="1"/>
+      <c r="Z66" s="1"/>
+      <c r="AA66" s="1"/>
+      <c r="AB66" s="1"/>
+    </row>
+    <row r="67" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A67" s="1">
+        <v>62</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D67" s="1"/>
+      <c r="E67" s="1"/>
+      <c r="F67" s="1"/>
+      <c r="G67" s="1"/>
+      <c r="H67" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I67" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J67" s="4">
+        <v>36</v>
+      </c>
+      <c r="K67" s="4">
+        <v>0</v>
+      </c>
+      <c r="L67" s="4">
+        <v>20</v>
+      </c>
+      <c r="M67" s="4">
+        <v>0</v>
+      </c>
+      <c r="N67" s="1"/>
+      <c r="O67" s="1"/>
+      <c r="P67" s="1"/>
+      <c r="Q67" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R67" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="S67" s="1"/>
+      <c r="T67" s="1"/>
+      <c r="U67" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W67" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="Y67" s="1"/>
+      <c r="Z67" s="1"/>
+      <c r="AA67" s="1"/>
+      <c r="AB67" s="1"/>
+    </row>
+    <row r="68" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A68" s="1">
+        <v>63</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D68" s="1"/>
+      <c r="E68" s="1"/>
+      <c r="F68" s="1"/>
+      <c r="G68" s="1"/>
+      <c r="H68" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I68" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J68" s="4">
+        <v>36</v>
+      </c>
+      <c r="K68" s="4">
+        <v>0</v>
+      </c>
+      <c r="L68" s="4">
+        <v>10</v>
+      </c>
+      <c r="M68" s="4">
+        <v>0</v>
+      </c>
+      <c r="N68" s="1"/>
+      <c r="O68" s="1"/>
+      <c r="P68" s="1"/>
+      <c r="Q68" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R68" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="S68" s="1"/>
+      <c r="T68" s="1"/>
+      <c r="U68" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W68" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y68" s="1"/>
+      <c r="Z68" s="1"/>
+      <c r="AA68" s="1"/>
+      <c r="AB68" s="1"/>
+    </row>
+    <row r="69" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A69" s="1">
+        <v>64</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D69" s="1"/>
+      <c r="E69" s="1"/>
+      <c r="F69" s="1"/>
+      <c r="G69" s="1"/>
+      <c r="H69" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I69" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J69" s="4">
+        <v>36</v>
+      </c>
+      <c r="K69" s="4">
+        <v>0</v>
+      </c>
+      <c r="L69" s="4">
+        <v>10</v>
+      </c>
+      <c r="M69" s="4">
+        <v>0</v>
+      </c>
+      <c r="N69" s="1"/>
+      <c r="O69" s="1"/>
+      <c r="P69" s="1"/>
+      <c r="Q69" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R69" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="S69" s="1"/>
+      <c r="T69" s="1"/>
+      <c r="U69" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W69" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y69" s="1"/>
+      <c r="Z69" s="1"/>
+      <c r="AA69" s="1"/>
+      <c r="AB69" s="1"/>
+    </row>
+    <row r="70" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A70" s="1">
+        <v>65</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D70" s="1"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I70" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J70" s="4">
+        <v>36</v>
+      </c>
+      <c r="K70" s="4">
+        <v>0</v>
+      </c>
+      <c r="L70" s="4">
+        <v>10</v>
+      </c>
+      <c r="M70" s="4">
+        <v>0</v>
+      </c>
+      <c r="N70" s="1"/>
+      <c r="O70" s="1"/>
+      <c r="P70" s="1"/>
+      <c r="Q70" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R70" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="S70" s="1"/>
+      <c r="T70" s="1"/>
+      <c r="U70" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="W70" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y70" s="1"/>
+      <c r="Z70" s="1"/>
+      <c r="AA70" s="1"/>
+      <c r="AB70" s="1"/>
+    </row>
+    <row r="71" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A71" s="1">
+        <v>66</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D71" s="1"/>
+      <c r="E71" s="1"/>
+      <c r="F71" s="1"/>
+      <c r="G71" s="1"/>
+      <c r="H71" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I71" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J71" s="4">
+        <v>42</v>
+      </c>
+      <c r="K71" s="4">
+        <v>0</v>
+      </c>
+      <c r="L71" s="4">
+        <v>10</v>
+      </c>
+      <c r="M71" s="4">
+        <v>0</v>
+      </c>
+      <c r="N71" s="1"/>
+      <c r="O71" s="1"/>
+      <c r="P71" s="1"/>
+      <c r="Q71" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R71" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="S71" s="1"/>
+      <c r="T71" s="1"/>
+      <c r="U71" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W71" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y71" s="1"/>
+      <c r="Z71" s="1"/>
+      <c r="AA71" s="1"/>
+      <c r="AB71" s="1"/>
+    </row>
+    <row r="72" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A72" s="1">
+        <v>67</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D72" s="1"/>
+      <c r="E72" s="1"/>
+      <c r="F72" s="1"/>
+      <c r="G72" s="1"/>
+      <c r="H72" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I72" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J72" s="4">
+        <v>42</v>
+      </c>
+      <c r="K72" s="4">
+        <v>2</v>
+      </c>
+      <c r="L72" s="4">
+        <v>10</v>
+      </c>
+      <c r="M72" s="4">
+        <v>0</v>
+      </c>
+      <c r="N72" s="1"/>
+      <c r="O72" s="1"/>
+      <c r="P72" s="1"/>
+      <c r="Q72" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R72" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="S72" s="1"/>
+      <c r="T72" s="1"/>
+      <c r="U72" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W72" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y72" s="1"/>
+      <c r="Z72" s="1"/>
+      <c r="AA72" s="1"/>
+      <c r="AB72" s="1"/>
+    </row>
+    <row r="73" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A73" s="1">
         <v>68</v>
       </c>
-      <c r="R24" s="2" t="s">
+      <c r="B73" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D73" s="1"/>
+      <c r="E73" s="1"/>
+      <c r="F73" s="1"/>
+      <c r="G73" s="1"/>
+      <c r="H73" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I73" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J73" s="4">
+        <v>42</v>
+      </c>
+      <c r="K73" s="4">
+        <v>2</v>
+      </c>
+      <c r="L73" s="4">
+        <v>10</v>
+      </c>
+      <c r="M73" s="4">
+        <v>0</v>
+      </c>
+      <c r="N73" s="1"/>
+      <c r="O73" s="1"/>
+      <c r="P73" s="1"/>
+      <c r="Q73" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R73" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="S73" s="1"/>
+      <c r="T73" s="1"/>
+      <c r="U73" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="W73" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y73" s="1"/>
+      <c r="Z73" s="1"/>
+      <c r="AA73" s="1"/>
+      <c r="AB73" s="1"/>
+    </row>
+    <row r="74" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A74" s="1">
         <v>69</v>
       </c>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A25" s="3"/>
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
-      <c r="J25" s="3"/>
-      <c r="K25" s="3"/>
-      <c r="L25" s="3"/>
-      <c r="M25" s="3"/>
-    </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A26" s="4">
+      <c r="B74" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C74" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="D74" s="1"/>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I74" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J74" s="4">
+        <v>42</v>
+      </c>
+      <c r="K74" s="4">
+        <v>2</v>
+      </c>
+      <c r="L74" s="4">
+        <v>1</v>
+      </c>
+      <c r="M74" s="4">
+        <v>0</v>
+      </c>
+      <c r="N74" s="1"/>
+      <c r="O74" s="1"/>
+      <c r="P74" s="1"/>
+      <c r="Q74" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R74" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="S74" s="1"/>
+      <c r="T74" s="1"/>
+      <c r="U74" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W74" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y74" s="1"/>
+      <c r="Z74" s="1"/>
+      <c r="AA74" s="1"/>
+      <c r="AB74" s="1"/>
+    </row>
+    <row r="75" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A75" s="1">
+        <v>70</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D75" s="1"/>
+      <c r="E75" s="1"/>
+      <c r="F75" s="1"/>
+      <c r="G75" s="1"/>
+      <c r="H75" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I75" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J75" s="4">
+        <v>42</v>
+      </c>
+      <c r="K75" s="4">
+        <v>2</v>
+      </c>
+      <c r="L75" s="4">
+        <v>1</v>
+      </c>
+      <c r="M75" s="4">
+        <v>8</v>
+      </c>
+      <c r="N75" s="1"/>
+      <c r="O75" s="1"/>
+      <c r="P75" s="1"/>
+      <c r="Q75" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R75" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="S75" s="1"/>
+      <c r="T75" s="1"/>
+      <c r="U75" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W75" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y75" s="1"/>
+      <c r="Z75" s="1"/>
+      <c r="AA75" s="1"/>
+      <c r="AB75" s="1"/>
+    </row>
+    <row r="76" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A76" s="1">
+        <v>71</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D76" s="1"/>
+      <c r="E76" s="1"/>
+      <c r="F76" s="1"/>
+      <c r="G76" s="1"/>
+      <c r="H76" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I76" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J76" s="4">
+        <v>42</v>
+      </c>
+      <c r="K76" s="4">
+        <v>2</v>
+      </c>
+      <c r="L76" s="4">
+        <v>1</v>
+      </c>
+      <c r="M76" s="4">
+        <v>8</v>
+      </c>
+      <c r="N76" s="1"/>
+      <c r="O76" s="1"/>
+      <c r="P76" s="1"/>
+      <c r="Q76" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R76" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="S76" s="1"/>
+      <c r="T76" s="1"/>
+      <c r="U76" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W76" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y76" s="1"/>
+      <c r="Z76" s="1"/>
+      <c r="AA76" s="1"/>
+      <c r="AB76" s="1"/>
+    </row>
+    <row r="77" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A77" s="1">
+        <v>72</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D77" s="1"/>
+      <c r="E77" s="1"/>
+      <c r="F77" s="1"/>
+      <c r="G77" s="1"/>
+      <c r="H77" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I77" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="J77" s="4">
+        <v>42</v>
+      </c>
+      <c r="K77" s="4">
+        <v>2</v>
+      </c>
+      <c r="L77" s="4">
+        <v>1</v>
+      </c>
+      <c r="M77" s="4">
+        <v>8</v>
+      </c>
+      <c r="N77" s="1"/>
+      <c r="O77" s="1"/>
+      <c r="P77" s="1"/>
+      <c r="Q77" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R77" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="S77" s="1"/>
+      <c r="T77" s="1"/>
+      <c r="U77" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W77" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y77" s="1"/>
+      <c r="Z77" s="1"/>
+      <c r="AA77" s="1"/>
+      <c r="AB77" s="1"/>
+    </row>
+    <row r="78" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A78" s="1">
+        <v>73</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D78" s="1"/>
+      <c r="E78" s="1"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I78" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="J78" s="4">
+        <v>42</v>
+      </c>
+      <c r="K78" s="4">
+        <v>2</v>
+      </c>
+      <c r="L78" s="4">
+        <v>1</v>
+      </c>
+      <c r="M78" s="4">
+        <v>8</v>
+      </c>
+      <c r="N78" s="1"/>
+      <c r="O78" s="1"/>
+      <c r="P78" s="1"/>
+      <c r="Q78" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R78" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="S78" s="1"/>
+      <c r="T78" s="1"/>
+      <c r="U78" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W78" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="Y78" s="1"/>
+      <c r="Z78" s="1"/>
+      <c r="AA78" s="1"/>
+      <c r="AB78" s="1"/>
+    </row>
+    <row r="79" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A79" s="1">
+        <v>74</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D79" s="1"/>
+      <c r="E79" s="1"/>
+      <c r="F79" s="1"/>
+      <c r="G79" s="1"/>
+      <c r="H79" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I79" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="J79" s="4">
+        <v>42</v>
+      </c>
+      <c r="K79" s="4">
+        <v>2</v>
+      </c>
+      <c r="L79" s="4">
+        <v>20</v>
+      </c>
+      <c r="M79" s="4">
+        <v>8</v>
+      </c>
+      <c r="N79" s="1"/>
+      <c r="O79" s="1"/>
+      <c r="P79" s="1"/>
+      <c r="Q79" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R79" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="S79" s="1"/>
+      <c r="T79" s="1"/>
+      <c r="U79" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W79" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y79" s="1"/>
+      <c r="Z79" s="1"/>
+      <c r="AA79" s="1"/>
+      <c r="AB79" s="1"/>
+    </row>
+    <row r="80" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A80" s="1">
+        <v>75</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D80" s="1"/>
+      <c r="E80" s="1"/>
+      <c r="F80" s="1"/>
+      <c r="G80" s="1"/>
+      <c r="H80" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I80" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="J80" s="4">
+        <v>42</v>
+      </c>
+      <c r="K80" s="4">
+        <v>2</v>
+      </c>
+      <c r="L80" s="4">
+        <v>20</v>
+      </c>
+      <c r="M80" s="4">
+        <v>8</v>
+      </c>
+      <c r="N80" s="1"/>
+      <c r="O80" s="1"/>
+      <c r="P80" s="1"/>
+      <c r="Q80" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R80" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="S80" s="1"/>
+      <c r="T80" s="1"/>
+      <c r="U80" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W80" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y80" s="1"/>
+      <c r="Z80" s="1"/>
+      <c r="AA80" s="1"/>
+      <c r="AB80" s="1"/>
+    </row>
+    <row r="81" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A81" s="1">
+        <v>76</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D81" s="1"/>
+      <c r="E81" s="1"/>
+      <c r="F81" s="1"/>
+      <c r="G81" s="1"/>
+      <c r="H81" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I81" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="J81" s="4">
+        <v>42</v>
+      </c>
+      <c r="K81" s="4">
+        <v>2</v>
+      </c>
+      <c r="L81" s="4">
+        <v>20</v>
+      </c>
+      <c r="M81" s="4">
+        <v>8</v>
+      </c>
+      <c r="N81" s="1"/>
+      <c r="O81" s="1"/>
+      <c r="P81" s="1"/>
+      <c r="Q81" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R81" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="S81" s="1"/>
+      <c r="T81" s="1"/>
+      <c r="U81" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="W81" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y81" s="1"/>
+      <c r="Z81" s="1"/>
+      <c r="AA81" s="1"/>
+      <c r="AB81" s="1"/>
+    </row>
+    <row r="82" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A82" s="1">
+        <v>77</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D82" s="1"/>
+      <c r="E82" s="1"/>
+      <c r="F82" s="1"/>
+      <c r="G82" s="1"/>
+      <c r="H82" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I82" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="J82" s="4">
+        <v>48</v>
+      </c>
+      <c r="K82" s="4">
+        <v>2</v>
+      </c>
+      <c r="L82" s="4">
+        <v>20</v>
+      </c>
+      <c r="M82" s="4">
+        <v>8</v>
+      </c>
+      <c r="N82" s="1"/>
+      <c r="O82" s="1"/>
+      <c r="P82" s="1"/>
+      <c r="Q82" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R82" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="S82" s="1"/>
+      <c r="T82" s="1"/>
+      <c r="U82" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W82" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y82" s="1"/>
+      <c r="Z82" s="1"/>
+      <c r="AA82" s="1"/>
+      <c r="AB82" s="1"/>
+    </row>
+    <row r="83" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A83" s="1">
+        <v>78</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D83" s="1"/>
+      <c r="E83" s="1"/>
+      <c r="F83" s="1"/>
+      <c r="G83" s="1"/>
+      <c r="H83" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I83" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="J83" s="4">
+        <v>48</v>
+      </c>
+      <c r="K83" s="4">
+        <v>0</v>
+      </c>
+      <c r="L83" s="4">
+        <v>20</v>
+      </c>
+      <c r="M83" s="4">
+        <v>8</v>
+      </c>
+      <c r="N83" s="1"/>
+      <c r="O83" s="1"/>
+      <c r="P83" s="1"/>
+      <c r="Q83" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R83" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="S83" s="1"/>
+      <c r="T83" s="1"/>
+      <c r="U83" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W83" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y83" s="1"/>
+      <c r="Z83" s="1"/>
+      <c r="AA83" s="1"/>
+      <c r="AB83" s="1"/>
+    </row>
+    <row r="84" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A84" s="1">
+        <v>79</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D84" s="1"/>
+      <c r="E84" s="1"/>
+      <c r="F84" s="1"/>
+      <c r="G84" s="1"/>
+      <c r="H84" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I84" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="J84" s="4">
+        <v>48</v>
+      </c>
+      <c r="K84" s="4">
+        <v>0</v>
+      </c>
+      <c r="L84" s="4">
+        <v>20</v>
+      </c>
+      <c r="M84" s="4">
+        <v>8</v>
+      </c>
+      <c r="N84" s="1"/>
+      <c r="O84" s="1"/>
+      <c r="P84" s="1"/>
+      <c r="Q84" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="R84" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="S84" s="1"/>
+      <c r="T84" s="1"/>
+      <c r="U84" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="W84" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y84" s="1"/>
+      <c r="Z84" s="1"/>
+      <c r="AA84" s="1"/>
+      <c r="AB84" s="1"/>
+    </row>
+    <row r="85" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A85" s="1">
+        <v>80</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D85" s="1"/>
+      <c r="E85" s="1"/>
+      <c r="F85" s="1"/>
+      <c r="G85" s="1"/>
+      <c r="H85" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I85" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="J85" s="4">
+        <v>48</v>
+      </c>
+      <c r="K85" s="4">
+        <v>0</v>
+      </c>
+      <c r="L85" s="4">
+        <v>20</v>
+      </c>
+      <c r="M85" s="4">
+        <v>0</v>
+      </c>
+      <c r="N85" s="1"/>
+      <c r="O85" s="1"/>
+      <c r="P85" s="1"/>
+      <c r="Q85" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="R85" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="S85" s="1"/>
+      <c r="T85" s="1"/>
+      <c r="U85" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W85" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y85" s="1"/>
+      <c r="Z85" s="1"/>
+      <c r="AA85" s="1"/>
+      <c r="AB85" s="1"/>
+    </row>
+    <row r="86" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A86" s="1">
+        <v>81</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D86" s="1"/>
+      <c r="E86" s="1"/>
+      <c r="F86" s="1"/>
+      <c r="G86" s="1"/>
+      <c r="H86" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I86" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J86" s="4">
+        <v>48</v>
+      </c>
+      <c r="K86" s="4">
+        <v>0</v>
+      </c>
+      <c r="L86" s="4">
+        <v>20</v>
+      </c>
+      <c r="M86" s="4">
+        <v>0</v>
+      </c>
+      <c r="N86" s="1"/>
+      <c r="O86" s="1"/>
+      <c r="P86" s="1"/>
+      <c r="Q86" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R86" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="S86" s="1"/>
+      <c r="T86" s="1"/>
+      <c r="U86" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W86" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y86" s="1"/>
+      <c r="Z86" s="1"/>
+      <c r="AA86" s="1"/>
+      <c r="AB86" s="1"/>
+    </row>
+    <row r="87" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A87" s="1">
+        <v>82</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D87" s="1"/>
+      <c r="E87" s="1"/>
+      <c r="F87" s="1"/>
+      <c r="G87" s="1"/>
+      <c r="H87" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I87" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J87" s="4">
+        <v>48</v>
+      </c>
+      <c r="K87" s="4">
+        <v>0</v>
+      </c>
+      <c r="L87" s="4">
+        <v>20</v>
+      </c>
+      <c r="M87" s="4">
+        <v>0</v>
+      </c>
+      <c r="N87" s="1"/>
+      <c r="O87" s="1"/>
+      <c r="P87" s="1"/>
+      <c r="Q87" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R87" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="S87" s="1"/>
+      <c r="T87" s="1"/>
+      <c r="U87" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W87" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y87" s="1"/>
+      <c r="Z87" s="1"/>
+      <c r="AA87" s="1"/>
+      <c r="AB87" s="1"/>
+    </row>
+    <row r="88" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A88" s="1">
+        <v>83</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D88" s="1"/>
+      <c r="E88" s="1"/>
+      <c r="F88" s="1"/>
+      <c r="G88" s="1"/>
+      <c r="H88" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I88" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J88" s="4">
+        <v>48</v>
+      </c>
+      <c r="K88" s="4">
+        <v>0</v>
+      </c>
+      <c r="L88" s="4">
+        <v>20</v>
+      </c>
+      <c r="M88" s="4">
+        <v>0</v>
+      </c>
+      <c r="N88" s="1"/>
+      <c r="O88" s="1"/>
+      <c r="P88" s="1"/>
+      <c r="Q88" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R88" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="S88" s="1"/>
+      <c r="T88" s="1"/>
+      <c r="U88" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W88" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="Y88" s="1"/>
+      <c r="Z88" s="1"/>
+      <c r="AA88" s="1"/>
+      <c r="AB88" s="1"/>
+    </row>
+    <row r="89" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A89" s="1">
+        <v>84</v>
+      </c>
+      <c r="B89" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="C89" s="1" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A27" s="4">
+      <c r="D89" s="1"/>
+      <c r="E89" s="1"/>
+      <c r="F89" s="1"/>
+      <c r="G89" s="1"/>
+      <c r="H89" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I89" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J89" s="4">
+        <v>48</v>
+      </c>
+      <c r="K89" s="4">
+        <v>0</v>
+      </c>
+      <c r="L89" s="4">
+        <v>10</v>
+      </c>
+      <c r="M89" s="4">
+        <v>0</v>
+      </c>
+      <c r="N89" s="1"/>
+      <c r="O89" s="1"/>
+      <c r="P89" s="1"/>
+      <c r="Q89" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R89" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="S89" s="1"/>
+      <c r="T89" s="1"/>
+      <c r="U89" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W89" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y89" s="1"/>
+      <c r="Z89" s="1"/>
+      <c r="AA89" s="1"/>
+      <c r="AB89" s="1"/>
+    </row>
+    <row r="90" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A90" s="1">
+        <v>85</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D90" s="1"/>
+      <c r="E90" s="1"/>
+      <c r="F90" s="1"/>
+      <c r="G90" s="1"/>
+      <c r="H90" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I90" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J90" s="4">
+        <v>48</v>
+      </c>
+      <c r="K90" s="4">
+        <v>0</v>
+      </c>
+      <c r="L90" s="4">
+        <v>10</v>
+      </c>
+      <c r="M90" s="4">
+        <v>0</v>
+      </c>
+      <c r="N90" s="1"/>
+      <c r="O90" s="1"/>
+      <c r="P90" s="1"/>
+      <c r="Q90" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R90" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="S90" s="1"/>
+      <c r="T90" s="1"/>
+      <c r="U90" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W90" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y90" s="1"/>
+      <c r="Z90" s="1"/>
+      <c r="AA90" s="1"/>
+      <c r="AB90" s="1"/>
+    </row>
+    <row r="91" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A91" s="1">
+        <v>86</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D91" s="1"/>
+      <c r="E91" s="1"/>
+      <c r="F91" s="1"/>
+      <c r="G91" s="1"/>
+      <c r="H91" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I91" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J91" s="4">
+        <v>48</v>
+      </c>
+      <c r="K91" s="4">
+        <v>0</v>
+      </c>
+      <c r="L91" s="4">
+        <v>10</v>
+      </c>
+      <c r="M91" s="4">
+        <v>0</v>
+      </c>
+      <c r="N91" s="1"/>
+      <c r="O91" s="1"/>
+      <c r="P91" s="1"/>
+      <c r="Q91" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R91" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="S91" s="1"/>
+      <c r="T91" s="1"/>
+      <c r="U91" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="W91" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y91" s="1"/>
+      <c r="Z91" s="1"/>
+      <c r="AA91" s="1"/>
+      <c r="AB91" s="1"/>
+    </row>
+    <row r="92" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A92" s="1">
+        <v>87</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D92" s="1"/>
+      <c r="E92" s="1"/>
+      <c r="F92" s="1"/>
+      <c r="G92" s="1"/>
+      <c r="H92" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I92" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J92" s="4">
+        <v>54</v>
+      </c>
+      <c r="K92" s="4">
+        <v>0</v>
+      </c>
+      <c r="L92" s="4">
+        <v>10</v>
+      </c>
+      <c r="M92" s="4">
+        <v>0</v>
+      </c>
+      <c r="N92" s="1"/>
+      <c r="O92" s="1"/>
+      <c r="P92" s="1"/>
+      <c r="Q92" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R92" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="S92" s="1"/>
+      <c r="T92" s="1"/>
+      <c r="U92" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W92" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y92" s="1"/>
+      <c r="Z92" s="1"/>
+      <c r="AA92" s="1"/>
+      <c r="AB92" s="1"/>
+    </row>
+    <row r="93" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A93" s="1">
+        <v>88</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D93" s="1"/>
+      <c r="E93" s="1"/>
+      <c r="F93" s="1"/>
+      <c r="G93" s="1"/>
+      <c r="H93" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I93" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J93" s="4">
+        <v>54</v>
+      </c>
+      <c r="K93" s="4">
+        <v>2</v>
+      </c>
+      <c r="L93" s="4">
+        <v>10</v>
+      </c>
+      <c r="M93" s="4">
+        <v>0</v>
+      </c>
+      <c r="N93" s="1"/>
+      <c r="O93" s="1"/>
+      <c r="P93" s="1"/>
+      <c r="Q93" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R93" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="S93" s="1"/>
+      <c r="T93" s="1"/>
+      <c r="U93" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W93" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y93" s="1"/>
+      <c r="Z93" s="1"/>
+      <c r="AA93" s="1"/>
+      <c r="AB93" s="1"/>
+    </row>
+    <row r="94" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A94" s="1">
+        <v>89</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D94" s="1"/>
+      <c r="E94" s="1"/>
+      <c r="F94" s="1"/>
+      <c r="G94" s="1"/>
+      <c r="H94" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I94" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J94" s="4">
+        <v>54</v>
+      </c>
+      <c r="K94" s="4">
+        <v>2</v>
+      </c>
+      <c r="L94" s="4">
+        <v>10</v>
+      </c>
+      <c r="M94" s="4">
+        <v>0</v>
+      </c>
+      <c r="N94" s="1"/>
+      <c r="O94" s="1"/>
+      <c r="P94" s="1"/>
+      <c r="Q94" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R94" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="S94" s="1"/>
+      <c r="T94" s="1"/>
+      <c r="U94" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="W94" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y94" s="1"/>
+      <c r="Z94" s="1"/>
+      <c r="AA94" s="1"/>
+      <c r="AB94" s="1"/>
+    </row>
+    <row r="95" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A95" s="1">
+        <v>90</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H95" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I95" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J95" s="4">
+        <v>54</v>
+      </c>
+      <c r="K95" s="4">
+        <v>2</v>
+      </c>
+      <c r="L95" s="4">
+        <v>1</v>
+      </c>
+      <c r="M95" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q95" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R95" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="U95" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W95" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="96" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A96" s="1">
+        <v>91</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C96" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="H96" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I96" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J96" s="4">
+        <v>54</v>
+      </c>
+      <c r="K96" s="4">
+        <v>2</v>
+      </c>
+      <c r="L96" s="4">
+        <v>1</v>
+      </c>
+      <c r="M96" s="4">
+        <v>8</v>
+      </c>
+      <c r="Q96" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R96" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="U96" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W96" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="97" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A97" s="1">
+        <v>92</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H97" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I97" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J97" s="4">
+        <v>54</v>
+      </c>
+      <c r="K97" s="4">
+        <v>2</v>
+      </c>
+      <c r="L97" s="4">
+        <v>1</v>
+      </c>
+      <c r="M97" s="4">
+        <v>8</v>
+      </c>
+      <c r="Q97" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R97" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="U97" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W97" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="98" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A98" s="1">
+        <v>93</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H98" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I98" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="J98" s="4">
+        <v>54</v>
+      </c>
+      <c r="K98" s="4">
+        <v>2</v>
+      </c>
+      <c r="L98" s="4">
+        <v>1</v>
+      </c>
+      <c r="M98" s="4">
+        <v>8</v>
+      </c>
+      <c r="Q98" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R98" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="U98" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W98" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="99" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A99" s="1">
+        <v>94</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H99" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I99" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="J99" s="4">
+        <v>54</v>
+      </c>
+      <c r="K99" s="4">
+        <v>2</v>
+      </c>
+      <c r="L99" s="4">
+        <v>1</v>
+      </c>
+      <c r="M99" s="4">
+        <v>8</v>
+      </c>
+      <c r="Q99" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R99" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="U99" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W99" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="100" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A100" s="1">
+        <v>95</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H100" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I100" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="J100" s="4">
+        <v>54</v>
+      </c>
+      <c r="K100" s="4">
+        <v>2</v>
+      </c>
+      <c r="L100" s="4">
+        <v>20</v>
+      </c>
+      <c r="M100" s="4">
+        <v>8</v>
+      </c>
+      <c r="Q100" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R100" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="U100" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W100" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="101" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A101" s="1">
+        <v>96</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H101" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I101" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="J101" s="4">
+        <v>54</v>
+      </c>
+      <c r="K101" s="4">
+        <v>2</v>
+      </c>
+      <c r="L101" s="4">
+        <v>20</v>
+      </c>
+      <c r="M101" s="4">
+        <v>8</v>
+      </c>
+      <c r="Q101" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R101" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="U101" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W101" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="102" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A102" s="1">
+        <v>97</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H102" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I102" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="J102" s="4">
+        <v>54</v>
+      </c>
+      <c r="K102" s="4">
+        <v>2</v>
+      </c>
+      <c r="L102" s="4">
+        <v>20</v>
+      </c>
+      <c r="M102" s="4">
+        <v>8</v>
+      </c>
+      <c r="Q102" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R102" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="U102" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="W102" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="103" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A103" s="1">
+        <v>98</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H103" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I103" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="J103" s="4">
+        <v>60</v>
+      </c>
+      <c r="K103" s="4">
+        <v>2</v>
+      </c>
+      <c r="L103" s="4">
+        <v>20</v>
+      </c>
+      <c r="M103" s="4">
+        <v>8</v>
+      </c>
+      <c r="Q103" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R103" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="U103" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W103" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="104" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A104" s="1">
+        <v>99</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H104" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I104" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="J104" s="4">
+        <v>60</v>
+      </c>
+      <c r="K104" s="4">
+        <v>0</v>
+      </c>
+      <c r="L104" s="4">
+        <v>20</v>
+      </c>
+      <c r="M104" s="4">
+        <v>8</v>
+      </c>
+      <c r="Q104" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R104" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="U104" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W104" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="105" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A105" s="1">
+        <v>100</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H105" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I105" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="J105" s="4">
+        <v>60</v>
+      </c>
+      <c r="K105" s="4">
+        <v>0</v>
+      </c>
+      <c r="L105" s="4">
+        <v>20</v>
+      </c>
+      <c r="M105" s="4">
+        <v>8</v>
+      </c>
+      <c r="Q105" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="R105" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="U105" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="W105" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="106" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A106" s="1">
+        <v>101</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H106" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I106" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="J106" s="4">
+        <v>60</v>
+      </c>
+      <c r="K106" s="4">
+        <v>0</v>
+      </c>
+      <c r="L106" s="4">
+        <v>20</v>
+      </c>
+      <c r="M106" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q106" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="R106" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="U106" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W106" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="107" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A107" s="1">
+        <v>102</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H107" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I107" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J107" s="4">
+        <v>60</v>
+      </c>
+      <c r="K107" s="4">
+        <v>0</v>
+      </c>
+      <c r="L107" s="4">
+        <v>20</v>
+      </c>
+      <c r="M107" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q107" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R107" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="U107" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W107" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="108" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A108" s="1">
+        <v>103</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H108" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I108" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J108" s="4">
+        <v>60</v>
+      </c>
+      <c r="K108" s="4">
+        <v>0</v>
+      </c>
+      <c r="L108" s="4">
+        <v>20</v>
+      </c>
+      <c r="M108" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q108" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R108" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="U108" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W108" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="109" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A109" s="1">
+        <v>104</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H109" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I109" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J109" s="4">
+        <v>60</v>
+      </c>
+      <c r="K109" s="4">
+        <v>0</v>
+      </c>
+      <c r="L109" s="4">
+        <v>20</v>
+      </c>
+      <c r="M109" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q109" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R109" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="U109" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W109" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="110" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A110" s="1">
+        <v>105</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H110" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I110" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J110" s="4">
+        <v>60</v>
+      </c>
+      <c r="K110" s="4">
+        <v>0</v>
+      </c>
+      <c r="L110" s="4">
+        <v>10</v>
+      </c>
+      <c r="M110" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q110" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R110" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="U110" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W110" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="111" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A111" s="1">
+        <v>106</v>
+      </c>
+      <c r="B111" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="C111" s="1" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A28" s="4">
+      <c r="H111" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I111" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J111" s="4">
+        <v>60</v>
+      </c>
+      <c r="K111" s="4">
+        <v>0</v>
+      </c>
+      <c r="L111" s="4">
+        <v>10</v>
+      </c>
+      <c r="M111" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q111" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R111" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="U111" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W111" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="112" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A112" s="1">
+        <v>107</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H112" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I112" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J112" s="4">
+        <v>60</v>
+      </c>
+      <c r="K112" s="4">
+        <v>0</v>
+      </c>
+      <c r="L112" s="4">
+        <v>10</v>
+      </c>
+      <c r="M112" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q112" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R112" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="U112" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="W112" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="113" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A113" s="1">
+        <v>108</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H113" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I113" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J113" s="4">
+        <v>66</v>
+      </c>
+      <c r="K113" s="4">
+        <v>0</v>
+      </c>
+      <c r="L113" s="4">
+        <v>10</v>
+      </c>
+      <c r="M113" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q113" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R113" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="U113" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W113" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="114" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A114" s="1">
+        <v>109</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H114" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I114" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J114" s="4">
+        <v>66</v>
+      </c>
+      <c r="K114" s="4">
+        <v>2</v>
+      </c>
+      <c r="L114" s="4">
+        <v>10</v>
+      </c>
+      <c r="M114" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q114" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R114" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="U114" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W114" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="115" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A115" s="1">
+        <v>110</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H115" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I115" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J115" s="4">
+        <v>66</v>
+      </c>
+      <c r="K115" s="4">
+        <v>2</v>
+      </c>
+      <c r="L115" s="4">
+        <v>10</v>
+      </c>
+      <c r="M115" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q115" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R115" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="U115" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="W115" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="116" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A116" s="1">
+        <v>111</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H116" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I116" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J116" s="4">
+        <v>66</v>
+      </c>
+      <c r="K116" s="4">
+        <v>2</v>
+      </c>
+      <c r="L116" s="4">
+        <v>1</v>
+      </c>
+      <c r="M116" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q116" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R116" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="U116" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W116" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="117" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A117" s="1">
+        <v>112</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H117" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I117" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J117" s="4">
+        <v>66</v>
+      </c>
+      <c r="K117" s="4">
+        <v>2</v>
+      </c>
+      <c r="L117" s="4">
+        <v>1</v>
+      </c>
+      <c r="M117" s="4">
+        <v>8</v>
+      </c>
+      <c r="Q117" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R117" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="U117" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W117" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="118" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A118" s="1">
+        <v>113</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H118" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I118" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J118" s="4">
+        <v>66</v>
+      </c>
+      <c r="K118" s="4">
+        <v>2</v>
+      </c>
+      <c r="L118" s="4">
+        <v>1</v>
+      </c>
+      <c r="M118" s="4">
+        <v>8</v>
+      </c>
+      <c r="Q118" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R118" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="U118" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W118" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="119" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A119" s="1">
+        <v>114</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C119" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B28" s="2"/>
+      <c r="H119" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I119" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="J119" s="4">
+        <v>66</v>
+      </c>
+      <c r="K119" s="4">
+        <v>2</v>
+      </c>
+      <c r="L119" s="4">
+        <v>1</v>
+      </c>
+      <c r="M119" s="4">
+        <v>8</v>
+      </c>
+      <c r="Q119" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R119" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="U119" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W119" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="120" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A120" s="1">
+        <v>115</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H120" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I120" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="J120" s="4">
+        <v>66</v>
+      </c>
+      <c r="K120" s="4">
+        <v>2</v>
+      </c>
+      <c r="L120" s="4">
+        <v>1</v>
+      </c>
+      <c r="M120" s="4">
+        <v>8</v>
+      </c>
+      <c r="Q120" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R120" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="U120" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W120" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="121" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A121" s="1">
+        <v>116</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H121" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I121" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="J121" s="4">
+        <v>66</v>
+      </c>
+      <c r="K121" s="4">
+        <v>2</v>
+      </c>
+      <c r="L121" s="4">
+        <v>20</v>
+      </c>
+      <c r="M121" s="4">
+        <v>8</v>
+      </c>
+      <c r="Q121" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R121" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="U121" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W121" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="122" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A122" s="1">
+        <v>117</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H122" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I122" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="J122" s="4">
+        <v>66</v>
+      </c>
+      <c r="K122" s="4">
+        <v>2</v>
+      </c>
+      <c r="L122" s="4">
+        <v>20</v>
+      </c>
+      <c r="M122" s="4">
+        <v>8</v>
+      </c>
+      <c r="Q122" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R122" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="U122" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W122" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="123" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A123" s="1">
+        <v>118</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H123" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I123" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="J123" s="4">
+        <v>66</v>
+      </c>
+      <c r="K123" s="4">
+        <v>2</v>
+      </c>
+      <c r="L123" s="4">
+        <v>20</v>
+      </c>
+      <c r="M123" s="4">
+        <v>8</v>
+      </c>
+      <c r="Q123" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R123" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="U123" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="W123" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="124" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A124" s="1">
+        <v>119</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H124" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I124" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="J124" s="4">
+        <v>72</v>
+      </c>
+      <c r="K124" s="4">
+        <v>2</v>
+      </c>
+      <c r="L124" s="4">
+        <v>20</v>
+      </c>
+      <c r="M124" s="4">
+        <v>8</v>
+      </c>
+      <c r="Q124" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R124" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="U124" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W124" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="125" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A125" s="1">
+        <v>120</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H125" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I125" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="J125" s="4">
+        <v>72</v>
+      </c>
+      <c r="K125" s="4">
+        <v>0</v>
+      </c>
+      <c r="L125" s="4">
+        <v>20</v>
+      </c>
+      <c r="M125" s="4">
+        <v>8</v>
+      </c>
+      <c r="Q125" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R125" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="U125" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W125" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="126" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A126" s="1">
+        <v>121</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H126" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I126" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="J126" s="4">
+        <v>72</v>
+      </c>
+      <c r="K126" s="4">
+        <v>0</v>
+      </c>
+      <c r="L126" s="4">
+        <v>20</v>
+      </c>
+      <c r="M126" s="4">
+        <v>8</v>
+      </c>
+      <c r="Q126" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="R126" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="U126" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="W126" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="127" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A127" s="1">
+        <v>122</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H127" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I127" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="J127" s="4">
+        <v>72</v>
+      </c>
+      <c r="K127" s="4">
+        <v>0</v>
+      </c>
+      <c r="L127" s="4">
+        <v>20</v>
+      </c>
+      <c r="M127" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q127" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="R127" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="U127" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W127" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="128" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A128" s="1">
+        <v>123</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H128" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I128" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J128" s="4">
+        <v>72</v>
+      </c>
+      <c r="K128" s="4">
+        <v>0</v>
+      </c>
+      <c r="L128" s="4">
+        <v>20</v>
+      </c>
+      <c r="M128" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q128" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R128" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="U128" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W128" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="129" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A129" s="1">
+        <v>124</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H129" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I129" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J129" s="4">
+        <v>72</v>
+      </c>
+      <c r="K129" s="4">
+        <v>0</v>
+      </c>
+      <c r="L129" s="4">
+        <v>20</v>
+      </c>
+      <c r="M129" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q129" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R129" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="U129" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W129" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="130" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A130" s="1">
+        <v>125</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H130" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I130" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J130" s="4">
+        <v>72</v>
+      </c>
+      <c r="K130" s="4">
+        <v>0</v>
+      </c>
+      <c r="L130" s="4">
+        <v>20</v>
+      </c>
+      <c r="M130" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q130" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R130" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="U130" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W130" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="131" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A131" s="1">
+        <v>126</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H131" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I131" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J131" s="4">
+        <v>72</v>
+      </c>
+      <c r="K131" s="4">
+        <v>0</v>
+      </c>
+      <c r="L131" s="4">
+        <v>10</v>
+      </c>
+      <c r="M131" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q131" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R131" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="U131" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W131" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="132" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A132" s="1">
+        <v>127</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H132" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I132" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J132" s="4">
+        <v>72</v>
+      </c>
+      <c r="K132" s="4">
+        <v>0</v>
+      </c>
+      <c r="L132" s="4">
+        <v>10</v>
+      </c>
+      <c r="M132" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q132" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R132" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="U132" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W132" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="133" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A133" s="1">
+        <v>128</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H133" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I133" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J133" s="4">
+        <v>72</v>
+      </c>
+      <c r="K133" s="4">
+        <v>0</v>
+      </c>
+      <c r="L133" s="4">
+        <v>10</v>
+      </c>
+      <c r="M133" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q133" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R133" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="U133" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="W133" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="134" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A134" s="1">
+        <v>129</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H134" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I134" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J134" s="4">
+        <v>78</v>
+      </c>
+      <c r="K134" s="4">
+        <v>0</v>
+      </c>
+      <c r="L134" s="4">
+        <v>10</v>
+      </c>
+      <c r="M134" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q134" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R134" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="U134" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W134" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="135" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A135" s="1">
+        <v>130</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H135" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I135" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J135" s="4">
+        <v>78</v>
+      </c>
+      <c r="K135" s="4">
+        <v>2</v>
+      </c>
+      <c r="L135" s="4">
+        <v>10</v>
+      </c>
+      <c r="M135" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q135" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R135" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="U135" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W135" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="136" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A136" s="1">
+        <v>131</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H136" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I136" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J136" s="4">
+        <v>78</v>
+      </c>
+      <c r="K136" s="4">
+        <v>2</v>
+      </c>
+      <c r="L136" s="4">
+        <v>10</v>
+      </c>
+      <c r="M136" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q136" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R136" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="U136" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="W136" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="137" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A137" s="1">
+        <v>132</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H137" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I137" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J137" s="4">
+        <v>78</v>
+      </c>
+      <c r="K137" s="4">
+        <v>2</v>
+      </c>
+      <c r="L137" s="4">
+        <v>1</v>
+      </c>
+      <c r="M137" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q137" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R137" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="U137" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W137" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="138" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A138" s="1">
+        <v>133</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H138" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I138" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J138" s="4">
+        <v>78</v>
+      </c>
+      <c r="K138" s="4">
+        <v>2</v>
+      </c>
+      <c r="L138" s="4">
+        <v>1</v>
+      </c>
+      <c r="M138" s="4">
+        <v>8</v>
+      </c>
+      <c r="Q138" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R138" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="U138" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W138" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="139" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A139" s="1">
+        <v>134</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H139" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I139" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J139" s="4">
+        <v>78</v>
+      </c>
+      <c r="K139" s="4">
+        <v>2</v>
+      </c>
+      <c r="L139" s="4">
+        <v>1</v>
+      </c>
+      <c r="M139" s="4">
+        <v>8</v>
+      </c>
+      <c r="Q139" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R139" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="U139" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W139" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="140" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A140" s="1">
+        <v>135</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H140" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I140" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="J140" s="4">
+        <v>78</v>
+      </c>
+      <c r="K140" s="4">
+        <v>2</v>
+      </c>
+      <c r="L140" s="4">
+        <v>1</v>
+      </c>
+      <c r="M140" s="4">
+        <v>8</v>
+      </c>
+      <c r="Q140" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R140" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="U140" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W140" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="141" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A141" s="1">
+        <v>136</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H141" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I141" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="J141" s="4">
+        <v>78</v>
+      </c>
+      <c r="K141" s="4">
+        <v>2</v>
+      </c>
+      <c r="L141" s="4">
+        <v>1</v>
+      </c>
+      <c r="M141" s="4">
+        <v>8</v>
+      </c>
+      <c r="Q141" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R141" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="U141" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W141" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="142" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A142" s="1">
+        <v>137</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H142" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I142" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="J142" s="4">
+        <v>78</v>
+      </c>
+      <c r="K142" s="4">
+        <v>2</v>
+      </c>
+      <c r="L142" s="4">
+        <v>20</v>
+      </c>
+      <c r="M142" s="4">
+        <v>8</v>
+      </c>
+      <c r="Q142" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R142" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="U142" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W142" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="143" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A143" s="1">
+        <v>138</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H143" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I143" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="J143" s="4">
+        <v>78</v>
+      </c>
+      <c r="K143" s="4">
+        <v>2</v>
+      </c>
+      <c r="L143" s="4">
+        <v>20</v>
+      </c>
+      <c r="M143" s="4">
+        <v>8</v>
+      </c>
+      <c r="Q143" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R143" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="U143" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W143" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="144" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A144" s="1">
+        <v>139</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H144" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I144" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="J144" s="4">
+        <v>78</v>
+      </c>
+      <c r="K144" s="4">
+        <v>2</v>
+      </c>
+      <c r="L144" s="4">
+        <v>20</v>
+      </c>
+      <c r="M144" s="4">
+        <v>8</v>
+      </c>
+      <c r="Q144" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R144" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="U144" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="W144" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="145" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A145" s="1">
+        <v>140</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H145" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I145" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="J145" s="4">
+        <v>84</v>
+      </c>
+      <c r="K145" s="4">
+        <v>2</v>
+      </c>
+      <c r="L145" s="4">
+        <v>20</v>
+      </c>
+      <c r="M145" s="4">
+        <v>8</v>
+      </c>
+      <c r="Q145" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R145" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="U145" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W145" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="146" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A146" s="1">
+        <v>141</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H146" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I146" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="J146" s="4">
+        <v>84</v>
+      </c>
+      <c r="K146" s="4">
+        <v>0</v>
+      </c>
+      <c r="L146" s="4">
+        <v>20</v>
+      </c>
+      <c r="M146" s="4">
+        <v>8</v>
+      </c>
+      <c r="Q146" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R146" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="U146" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W146" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="147" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A147" s="1">
+        <v>142</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H147" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I147" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="J147" s="4">
+        <v>84</v>
+      </c>
+      <c r="K147" s="4">
+        <v>0</v>
+      </c>
+      <c r="L147" s="4">
+        <v>20</v>
+      </c>
+      <c r="M147" s="4">
+        <v>8</v>
+      </c>
+      <c r="Q147" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="R147" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="U147" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="W147" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="148" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A148" s="1">
+        <v>143</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H148" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I148" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="J148" s="4">
+        <v>84</v>
+      </c>
+      <c r="K148" s="4">
+        <v>0</v>
+      </c>
+      <c r="L148" s="4">
+        <v>20</v>
+      </c>
+      <c r="M148" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q148" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="R148" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="U148" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W148" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="149" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A149" s="1">
+        <v>144</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H149" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I149" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J149" s="4">
+        <v>84</v>
+      </c>
+      <c r="K149" s="4">
+        <v>0</v>
+      </c>
+      <c r="L149" s="4">
+        <v>20</v>
+      </c>
+      <c r="M149" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q149" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R149" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="U149" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W149" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="150" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A150" s="1">
+        <v>145</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H150" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I150" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J150" s="4">
+        <v>84</v>
+      </c>
+      <c r="K150" s="4">
+        <v>0</v>
+      </c>
+      <c r="L150" s="4">
+        <v>20</v>
+      </c>
+      <c r="M150" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q150" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R150" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="U150" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W150" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="151" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A151" s="1">
+        <v>146</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H151" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I151" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J151" s="4">
+        <v>84</v>
+      </c>
+      <c r="K151" s="4">
+        <v>0</v>
+      </c>
+      <c r="L151" s="4">
+        <v>20</v>
+      </c>
+      <c r="M151" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q151" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R151" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="U151" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W151" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="152" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A152" s="1">
+        <v>147</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H152" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I152" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J152" s="4">
+        <v>84</v>
+      </c>
+      <c r="K152" s="4">
+        <v>0</v>
+      </c>
+      <c r="L152" s="4">
+        <v>10</v>
+      </c>
+      <c r="M152" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q152" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R152" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="U152" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W152" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="153" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A153" s="1">
+        <v>148</v>
+      </c>
+      <c r="B153" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C153" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H153" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I153" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J153" s="4">
+        <v>84</v>
+      </c>
+      <c r="K153" s="4">
+        <v>0</v>
+      </c>
+      <c r="L153" s="4">
+        <v>10</v>
+      </c>
+      <c r="M153" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q153" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R153" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="U153" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W153" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="154" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A154" s="1">
+        <v>149</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H154" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I154" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J154" s="4">
+        <v>84</v>
+      </c>
+      <c r="K154" s="4">
+        <v>0</v>
+      </c>
+      <c r="L154" s="4">
+        <v>10</v>
+      </c>
+      <c r="M154" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q154" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R154" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="U154" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="W154" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="155" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A155" s="1">
+        <v>150</v>
+      </c>
+      <c r="B155" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H155" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I155" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J155" s="4">
+        <v>90</v>
+      </c>
+      <c r="K155" s="4">
+        <v>0</v>
+      </c>
+      <c r="L155" s="4">
+        <v>10</v>
+      </c>
+      <c r="M155" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q155" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R155" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="U155" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W155" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="156" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A156" s="1">
+        <v>151</v>
+      </c>
+      <c r="B156" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H156" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I156" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J156" s="4">
+        <v>90</v>
+      </c>
+      <c r="K156" s="4">
+        <v>2</v>
+      </c>
+      <c r="L156" s="4">
+        <v>10</v>
+      </c>
+      <c r="M156" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q156" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R156" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="U156" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W156" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="157" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A157" s="1">
+        <v>152</v>
+      </c>
+      <c r="B157" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C157" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H157" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I157" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J157" s="4">
+        <v>90</v>
+      </c>
+      <c r="K157" s="4">
+        <v>2</v>
+      </c>
+      <c r="L157" s="4">
+        <v>10</v>
+      </c>
+      <c r="M157" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q157" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R157" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="U157" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="W157" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="158" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A158" s="1">
+        <v>153</v>
+      </c>
+      <c r="B158" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H158" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I158" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J158" s="4">
+        <v>90</v>
+      </c>
+      <c r="K158" s="4">
+        <v>2</v>
+      </c>
+      <c r="L158" s="4">
+        <v>1</v>
+      </c>
+      <c r="M158" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q158" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R158" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="U158" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W158" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="159" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A159" s="1">
+        <v>154</v>
+      </c>
+      <c r="B159" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H159" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I159" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J159" s="4">
+        <v>90</v>
+      </c>
+      <c r="K159" s="4">
+        <v>2</v>
+      </c>
+      <c r="L159" s="4">
+        <v>1</v>
+      </c>
+      <c r="M159" s="4">
+        <v>8</v>
+      </c>
+      <c r="Q159" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R159" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="U159" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W159" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="160" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A160" s="1">
+        <v>155</v>
+      </c>
+      <c r="B160" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H160" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I160" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J160" s="4">
+        <v>90</v>
+      </c>
+      <c r="K160" s="4">
+        <v>2</v>
+      </c>
+      <c r="L160" s="4">
+        <v>1</v>
+      </c>
+      <c r="M160" s="4">
+        <v>8</v>
+      </c>
+      <c r="Q160" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R160" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="U160" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W160" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="161" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A161" s="1">
+        <v>156</v>
+      </c>
+      <c r="B161" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C161" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H161" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I161" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="J161" s="4">
+        <v>90</v>
+      </c>
+      <c r="K161" s="4">
+        <v>2</v>
+      </c>
+      <c r="L161" s="4">
+        <v>1</v>
+      </c>
+      <c r="M161" s="4">
+        <v>8</v>
+      </c>
+      <c r="Q161" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R161" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="U161" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W161" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="162" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A162" s="1">
+        <v>157</v>
+      </c>
+      <c r="B162" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C162" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H162" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I162" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="J162" s="4">
+        <v>90</v>
+      </c>
+      <c r="K162" s="4">
+        <v>2</v>
+      </c>
+      <c r="L162" s="4">
+        <v>1</v>
+      </c>
+      <c r="M162" s="4">
+        <v>8</v>
+      </c>
+      <c r="Q162" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R162" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="U162" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W162" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="163" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A163" s="1">
+        <v>158</v>
+      </c>
+      <c r="B163" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H163" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I163" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="J163" s="4">
+        <v>90</v>
+      </c>
+      <c r="K163" s="4">
+        <v>2</v>
+      </c>
+      <c r="L163" s="4">
+        <v>20</v>
+      </c>
+      <c r="M163" s="4">
+        <v>8</v>
+      </c>
+      <c r="Q163" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R163" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="U163" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W163" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="164" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A164" s="1">
+        <v>159</v>
+      </c>
+      <c r="B164" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C164" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H164" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I164" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="J164" s="4">
+        <v>90</v>
+      </c>
+      <c r="K164" s="4">
+        <v>2</v>
+      </c>
+      <c r="L164" s="4">
+        <v>20</v>
+      </c>
+      <c r="M164" s="4">
+        <v>8</v>
+      </c>
+      <c r="Q164" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R164" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="U164" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W164" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="165" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A165" s="1">
+        <v>160</v>
+      </c>
+      <c r="B165" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C165" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H165" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I165" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="J165" s="4">
+        <v>90</v>
+      </c>
+      <c r="K165" s="4">
+        <v>2</v>
+      </c>
+      <c r="L165" s="4">
+        <v>20</v>
+      </c>
+      <c r="M165" s="4">
+        <v>8</v>
+      </c>
+      <c r="Q165" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R165" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="U165" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="W165" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="166" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A166" s="1">
+        <v>161</v>
+      </c>
+      <c r="B166" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C166" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H166" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I166" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="J166" s="4">
+        <v>96</v>
+      </c>
+      <c r="K166" s="4">
+        <v>2</v>
+      </c>
+      <c r="L166" s="4">
+        <v>20</v>
+      </c>
+      <c r="M166" s="4">
+        <v>8</v>
+      </c>
+      <c r="Q166" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R166" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="U166" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W166" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="167" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A167" s="1">
+        <v>162</v>
+      </c>
+      <c r="B167" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C167" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H167" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I167" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="J167" s="4">
+        <v>96</v>
+      </c>
+      <c r="K167" s="4">
+        <v>0</v>
+      </c>
+      <c r="L167" s="4">
+        <v>20</v>
+      </c>
+      <c r="M167" s="4">
+        <v>8</v>
+      </c>
+      <c r="Q167" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R167" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="U167" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W167" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="168" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A168" s="1">
+        <v>163</v>
+      </c>
+      <c r="B168" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C168" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H168" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I168" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="J168" s="4">
+        <v>96</v>
+      </c>
+      <c r="K168" s="4">
+        <v>0</v>
+      </c>
+      <c r="L168" s="4">
+        <v>20</v>
+      </c>
+      <c r="M168" s="4">
+        <v>8</v>
+      </c>
+      <c r="Q168" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="R168" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="U168" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="W168" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="169" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A169" s="1">
+        <v>164</v>
+      </c>
+      <c r="B169" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C169" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H169" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I169" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="J169" s="4">
+        <v>96</v>
+      </c>
+      <c r="K169" s="4">
+        <v>0</v>
+      </c>
+      <c r="L169" s="4">
+        <v>20</v>
+      </c>
+      <c r="M169" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q169" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="R169" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="U169" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W169" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="170" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A170" s="1">
+        <v>165</v>
+      </c>
+      <c r="B170" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C170" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H170" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I170" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J170" s="4">
+        <v>96</v>
+      </c>
+      <c r="K170" s="4">
+        <v>0</v>
+      </c>
+      <c r="L170" s="4">
+        <v>20</v>
+      </c>
+      <c r="M170" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q170" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R170" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="U170" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W170" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="171" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A171" s="1">
+        <v>166</v>
+      </c>
+      <c r="B171" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C171" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H171" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I171" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J171" s="4">
+        <v>96</v>
+      </c>
+      <c r="K171" s="4">
+        <v>0</v>
+      </c>
+      <c r="L171" s="4">
+        <v>20</v>
+      </c>
+      <c r="M171" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q171" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R171" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="U171" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W171" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="172" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A172" s="1">
+        <v>167</v>
+      </c>
+      <c r="B172" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C172" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H172" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I172" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J172" s="4">
+        <v>96</v>
+      </c>
+      <c r="K172" s="4">
+        <v>0</v>
+      </c>
+      <c r="L172" s="4">
+        <v>20</v>
+      </c>
+      <c r="M172" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q172" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R172" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="U172" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W172" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="173" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A173" s="1">
+        <v>168</v>
+      </c>
+      <c r="B173" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C173" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H173" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I173" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J173" s="4">
+        <v>96</v>
+      </c>
+      <c r="K173" s="4">
+        <v>0</v>
+      </c>
+      <c r="L173" s="4">
+        <v>10</v>
+      </c>
+      <c r="M173" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q173" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R173" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="U173" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W173" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="174" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A174" s="1">
+        <v>169</v>
+      </c>
+      <c r="B174" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C174" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H174" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I174" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J174" s="4">
+        <v>96</v>
+      </c>
+      <c r="K174" s="4">
+        <v>0</v>
+      </c>
+      <c r="L174" s="4">
+        <v>10</v>
+      </c>
+      <c r="M174" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q174" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R174" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="U174" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W174" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="175" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A175" s="1">
+        <v>170</v>
+      </c>
+      <c r="B175" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C175" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H175" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I175" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J175" s="4">
+        <v>96</v>
+      </c>
+      <c r="K175" s="4">
+        <v>0</v>
+      </c>
+      <c r="L175" s="4">
+        <v>10</v>
+      </c>
+      <c r="M175" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q175" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R175" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="U175" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="W175" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="176" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A176" s="1">
+        <v>171</v>
+      </c>
+      <c r="B176" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C176" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H176" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I176" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J176" s="4">
+        <v>102</v>
+      </c>
+      <c r="K176" s="4">
+        <v>0</v>
+      </c>
+      <c r="L176" s="4">
+        <v>10</v>
+      </c>
+      <c r="M176" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q176" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R176" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="U176" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W176" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="177" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A177" s="1">
+        <v>172</v>
+      </c>
+      <c r="B177" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C177" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H177" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I177" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J177" s="4">
+        <v>102</v>
+      </c>
+      <c r="K177" s="4">
+        <v>2</v>
+      </c>
+      <c r="L177" s="4">
+        <v>10</v>
+      </c>
+      <c r="M177" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q177" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R177" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="U177" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W177" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="178" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A178" s="1">
+        <v>173</v>
+      </c>
+      <c r="B178" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C178" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H178" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I178" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J178" s="4">
+        <v>102</v>
+      </c>
+      <c r="K178" s="4">
+        <v>2</v>
+      </c>
+      <c r="L178" s="4">
+        <v>10</v>
+      </c>
+      <c r="M178" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q178" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R178" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="U178" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="W178" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="179" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A179" s="1">
+        <v>174</v>
+      </c>
+      <c r="B179" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C179" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H179" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I179" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J179" s="4">
+        <v>102</v>
+      </c>
+      <c r="K179" s="4">
+        <v>2</v>
+      </c>
+      <c r="L179" s="4">
+        <v>1</v>
+      </c>
+      <c r="M179" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q179" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R179" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="U179" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W179" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="180" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A180" s="1">
+        <v>175</v>
+      </c>
+      <c r="B180" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C180" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H180" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I180" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J180" s="4">
+        <v>102</v>
+      </c>
+      <c r="K180" s="4">
+        <v>2</v>
+      </c>
+      <c r="L180" s="4">
+        <v>1</v>
+      </c>
+      <c r="M180" s="4">
+        <v>8</v>
+      </c>
+      <c r="Q180" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R180" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="U180" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W180" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="181" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A181" s="1">
+        <v>176</v>
+      </c>
+      <c r="B181" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C181" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H181" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I181" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J181" s="4">
+        <v>102</v>
+      </c>
+      <c r="K181" s="4">
+        <v>2</v>
+      </c>
+      <c r="L181" s="4">
+        <v>1</v>
+      </c>
+      <c r="M181" s="4">
+        <v>8</v>
+      </c>
+      <c r="Q181" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R181" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="U181" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W181" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="182" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A182" s="1">
+        <v>177</v>
+      </c>
+      <c r="B182" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C182" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H182" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I182" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="J182" s="4">
+        <v>102</v>
+      </c>
+      <c r="K182" s="4">
+        <v>2</v>
+      </c>
+      <c r="L182" s="4">
+        <v>1</v>
+      </c>
+      <c r="M182" s="4">
+        <v>8</v>
+      </c>
+      <c r="Q182" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R182" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="U182" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W182" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="183" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A183" s="1">
+        <v>178</v>
+      </c>
+      <c r="B183" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C183" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H183" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I183" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="J183" s="4">
+        <v>102</v>
+      </c>
+      <c r="K183" s="4">
+        <v>2</v>
+      </c>
+      <c r="L183" s="4">
+        <v>1</v>
+      </c>
+      <c r="M183" s="4">
+        <v>8</v>
+      </c>
+      <c r="Q183" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R183" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="U183" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W183" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="184" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A184" s="1">
+        <v>179</v>
+      </c>
+      <c r="B184" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C184" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H184" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I184" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="J184" s="4">
+        <v>102</v>
+      </c>
+      <c r="K184" s="4">
+        <v>2</v>
+      </c>
+      <c r="L184" s="4">
+        <v>20</v>
+      </c>
+      <c r="M184" s="4">
+        <v>8</v>
+      </c>
+      <c r="Q184" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R184" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="U184" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W184" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="185" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A185" s="1">
+        <v>180</v>
+      </c>
+      <c r="B185" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C185" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H185" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I185" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="J185" s="4">
+        <v>102</v>
+      </c>
+      <c r="K185" s="4">
+        <v>2</v>
+      </c>
+      <c r="L185" s="4">
+        <v>20</v>
+      </c>
+      <c r="M185" s="4">
+        <v>8</v>
+      </c>
+      <c r="Q185" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R185" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="U185" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W185" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="186" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A186" s="1">
+        <v>181</v>
+      </c>
+      <c r="B186" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C186" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H186" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I186" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="J186" s="4">
+        <v>102</v>
+      </c>
+      <c r="K186" s="4">
+        <v>2</v>
+      </c>
+      <c r="L186" s="4">
+        <v>20</v>
+      </c>
+      <c r="M186" s="4">
+        <v>8</v>
+      </c>
+      <c r="Q186" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R186" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="U186" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="W186" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="187" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A187" s="1">
+        <v>182</v>
+      </c>
+      <c r="B187" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C187" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H187" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I187" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="J187" s="4">
+        <v>108</v>
+      </c>
+      <c r="K187" s="4">
+        <v>2</v>
+      </c>
+      <c r="L187" s="4">
+        <v>20</v>
+      </c>
+      <c r="M187" s="4">
+        <v>8</v>
+      </c>
+      <c r="Q187" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R187" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="U187" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W187" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="188" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A188" s="1">
+        <v>183</v>
+      </c>
+      <c r="B188" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C188" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H188" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I188" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="J188" s="4">
+        <v>108</v>
+      </c>
+      <c r="K188" s="4">
+        <v>0</v>
+      </c>
+      <c r="L188" s="4">
+        <v>20</v>
+      </c>
+      <c r="M188" s="4">
+        <v>8</v>
+      </c>
+      <c r="Q188" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R188" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="U188" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W188" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="189" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A189" s="1">
+        <v>184</v>
+      </c>
+      <c r="B189" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C189" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H189" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I189" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="J189" s="4">
+        <v>108</v>
+      </c>
+      <c r="K189" s="4">
+        <v>0</v>
+      </c>
+      <c r="L189" s="4">
+        <v>20</v>
+      </c>
+      <c r="M189" s="4">
+        <v>8</v>
+      </c>
+      <c r="Q189" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="R189" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="U189" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="W189" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="190" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A190" s="1">
+        <v>185</v>
+      </c>
+      <c r="B190" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C190" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H190" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I190" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="J190" s="4">
+        <v>108</v>
+      </c>
+      <c r="K190" s="4">
+        <v>0</v>
+      </c>
+      <c r="L190" s="4">
+        <v>20</v>
+      </c>
+      <c r="M190" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q190" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="R190" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="U190" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W190" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="191" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A191" s="1">
+        <v>186</v>
+      </c>
+      <c r="B191" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C191" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H191" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I191" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J191" s="4">
+        <v>108</v>
+      </c>
+      <c r="K191" s="4">
+        <v>0</v>
+      </c>
+      <c r="L191" s="4">
+        <v>20</v>
+      </c>
+      <c r="M191" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q191" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R191" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="U191" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W191" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="192" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A192" s="1">
+        <v>187</v>
+      </c>
+      <c r="B192" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C192" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H192" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I192" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J192" s="4">
+        <v>108</v>
+      </c>
+      <c r="K192" s="4">
+        <v>0</v>
+      </c>
+      <c r="L192" s="4">
+        <v>20</v>
+      </c>
+      <c r="M192" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q192" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R192" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="U192" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W192" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="193" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A193" s="1">
+        <v>188</v>
+      </c>
+      <c r="B193" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C193" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H193" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I193" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J193" s="4">
+        <v>108</v>
+      </c>
+      <c r="K193" s="4">
+        <v>0</v>
+      </c>
+      <c r="L193" s="4">
+        <v>20</v>
+      </c>
+      <c r="M193" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q193" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R193" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="U193" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W193" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="194" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A194" s="1">
+        <v>189</v>
+      </c>
+      <c r="B194" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C194" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H194" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I194" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J194" s="4">
+        <v>108</v>
+      </c>
+      <c r="K194" s="4">
+        <v>0</v>
+      </c>
+      <c r="L194" s="4">
+        <v>10</v>
+      </c>
+      <c r="M194" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q194" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R194" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="U194" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W194" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="195" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A195" s="1">
+        <v>190</v>
+      </c>
+      <c r="B195" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C195" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H195" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I195" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J195" s="4">
+        <v>108</v>
+      </c>
+      <c r="K195" s="4">
+        <v>0</v>
+      </c>
+      <c r="L195" s="4">
+        <v>10</v>
+      </c>
+      <c r="M195" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q195" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R195" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="U195" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W195" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="196" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A196" s="1">
+        <v>191</v>
+      </c>
+      <c r="B196" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C196" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H196" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I196" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J196" s="4">
+        <v>108</v>
+      </c>
+      <c r="K196" s="4">
+        <v>0</v>
+      </c>
+      <c r="L196" s="4">
+        <v>10</v>
+      </c>
+      <c r="M196" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q196" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R196" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="U196" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="W196" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="197" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A197" s="1">
+        <v>192</v>
+      </c>
+      <c r="B197" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C197" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H197" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I197" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J197" s="4">
+        <v>114</v>
+      </c>
+      <c r="K197" s="4">
+        <v>0</v>
+      </c>
+      <c r="L197" s="4">
+        <v>10</v>
+      </c>
+      <c r="M197" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q197" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R197" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="U197" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W197" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="198" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A198" s="1">
+        <v>193</v>
+      </c>
+      <c r="B198" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C198" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H198" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I198" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J198" s="4">
+        <v>114</v>
+      </c>
+      <c r="K198" s="4">
+        <v>2</v>
+      </c>
+      <c r="L198" s="4">
+        <v>10</v>
+      </c>
+      <c r="M198" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q198" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R198" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="U198" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W198" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="199" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A199" s="1">
+        <v>194</v>
+      </c>
+      <c r="B199" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C199" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H199" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I199" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J199" s="4">
+        <v>114</v>
+      </c>
+      <c r="K199" s="4">
+        <v>2</v>
+      </c>
+      <c r="L199" s="4">
+        <v>10</v>
+      </c>
+      <c r="M199" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q199" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R199" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="U199" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="W199" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="200" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A200" s="1">
+        <v>195</v>
+      </c>
+      <c r="B200" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C200" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H200" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I200" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J200" s="4">
+        <v>114</v>
+      </c>
+      <c r="K200" s="4">
+        <v>2</v>
+      </c>
+      <c r="L200" s="4">
+        <v>1</v>
+      </c>
+      <c r="M200" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q200" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R200" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="U200" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W200" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="201" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A201" s="1">
+        <v>196</v>
+      </c>
+      <c r="B201" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C201" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H201" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I201" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J201" s="4">
+        <v>114</v>
+      </c>
+      <c r="K201" s="4">
+        <v>2</v>
+      </c>
+      <c r="L201" s="4">
+        <v>1</v>
+      </c>
+      <c r="M201" s="4">
+        <v>8</v>
+      </c>
+      <c r="Q201" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R201" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="U201" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W201" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="202" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A202" s="1">
+        <v>197</v>
+      </c>
+      <c r="B202" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C202" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H202" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I202" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J202" s="4">
+        <v>114</v>
+      </c>
+      <c r="K202" s="4">
+        <v>2</v>
+      </c>
+      <c r="L202" s="4">
+        <v>1</v>
+      </c>
+      <c r="M202" s="4">
+        <v>8</v>
+      </c>
+      <c r="Q202" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R202" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="U202" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W202" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="203" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A203" s="1">
+        <v>198</v>
+      </c>
+      <c r="B203" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C203" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H203" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I203" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="J203" s="4">
+        <v>114</v>
+      </c>
+      <c r="K203" s="4">
+        <v>2</v>
+      </c>
+      <c r="L203" s="4">
+        <v>1</v>
+      </c>
+      <c r="M203" s="4">
+        <v>8</v>
+      </c>
+      <c r="Q203" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R203" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="U203" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W203" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="204" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A204" s="1">
+        <v>199</v>
+      </c>
+      <c r="B204" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C204" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H204" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I204" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="J204" s="4">
+        <v>114</v>
+      </c>
+      <c r="K204" s="4">
+        <v>2</v>
+      </c>
+      <c r="L204" s="4">
+        <v>1</v>
+      </c>
+      <c r="M204" s="4">
+        <v>8</v>
+      </c>
+      <c r="Q204" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R204" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="U204" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W204" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="205" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A205" s="1">
+        <v>200</v>
+      </c>
+      <c r="B205" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C205" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H205" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I205" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="J205" s="4">
+        <v>114</v>
+      </c>
+      <c r="K205" s="4">
+        <v>2</v>
+      </c>
+      <c r="L205" s="4">
+        <v>20</v>
+      </c>
+      <c r="M205" s="4">
+        <v>8</v>
+      </c>
+      <c r="Q205" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R205" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="U205" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W205" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="206" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A206" s="1"/>
+      <c r="B206" s="1"/>
+      <c r="C206" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>

--- a/programs/assembly/tage_test_trace.xlsx
+++ b/programs/assembly/tage_test_trace.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\emerald\zaqal\programs\assembly\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F281E1E4-7DA8-4357-8615-65F0E7F1264A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89C6D24C-DBCF-43AD-A9F4-4BC21CA979FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28965" yWindow="-2070" windowWidth="11325" windowHeight="25140" xr2:uid="{E346031A-6FE0-420F-941A-72680D802F2C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{E346031A-6FE0-420F-941A-72680D802F2C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1548" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1549" uniqueCount="108">
   <si>
     <t>order</t>
   </si>
@@ -358,6 +358,9 @@
   </si>
   <si>
     <t>PRE GHR</t>
+  </si>
+  <si>
+    <t>Post GHR</t>
   </si>
 </sst>
 </file>
@@ -862,7 +865,9 @@
       <c r="S1" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="T1" s="5"/>
+      <c r="T1" s="5" t="s">
+        <v>107</v>
+      </c>
       <c r="U1" s="5" t="s">
         <v>68</v>
       </c>
@@ -1458,7 +1463,9 @@
       <c r="S15" s="1">
         <v>0</v>
       </c>
-      <c r="T15" s="1"/>
+      <c r="T15" s="1">
+        <v>1</v>
+      </c>
       <c r="U15" s="1" t="s">
         <v>74</v>
       </c>
@@ -1576,7 +1583,9 @@
       <c r="S18" s="1">
         <v>1</v>
       </c>
-      <c r="T18" s="1"/>
+      <c r="T18" s="1">
+        <v>3</v>
+      </c>
       <c r="U18" s="1" t="s">
         <v>75</v>
       </c>
@@ -1905,7 +1914,9 @@
       <c r="S27" s="1">
         <v>3</v>
       </c>
-      <c r="T27" s="1"/>
+      <c r="T27" s="1">
+        <v>7</v>
+      </c>
       <c r="U27" s="1" t="s">
         <v>76</v>
       </c>
@@ -2076,7 +2087,9 @@
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
-      <c r="G31" s="1"/>
+      <c r="G31" s="1">
+        <v>121</v>
+      </c>
       <c r="H31" s="4" t="s">
         <v>73</v>
       </c>
@@ -2104,7 +2117,9 @@
       <c r="R31" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="S31" s="1"/>
+      <c r="S31" s="1">
+        <v>7</v>
+      </c>
       <c r="T31" s="1"/>
       <c r="U31" s="4" t="s">
         <v>77</v>

--- a/programs/assembly/tage_test_trace.xlsx
+++ b/programs/assembly/tage_test_trace.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\emerald\zaqal\programs\assembly\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{961CC340-19F2-49AD-B45B-45052EA9E55A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE488C8C-7C69-499B-ABF6-52FE5CFF3E9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="915" yWindow="675" windowWidth="10125" windowHeight="17415" xr2:uid="{E346031A-6FE0-420F-941A-72680D802F2C}"/>
+    <workbookView xWindow="30855" yWindow="780" windowWidth="12360" windowHeight="15150" xr2:uid="{E346031A-6FE0-420F-941A-72680D802F2C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2312" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2335" uniqueCount="159">
   <si>
     <t>order</t>
   </si>
@@ -309,6 +309,12 @@
     <t>T0[32], Tag=0x20, Target=0x28, US=0</t>
   </si>
   <si>
+    <t>T0[42], Tag=0x2A, Target=0x20, US=0</t>
+  </si>
+  <si>
+    <t>T0[40], Tag=0x28, Target=0x28, US=0</t>
+  </si>
+  <si>
     <t>x34 - x20</t>
   </si>
   <si>
@@ -441,51 +447,9 @@
     <t>0b0</t>
   </si>
   <si>
-    <t>0b1000</t>
-  </si>
-  <si>
-    <t>0b10000000</t>
-  </si>
-  <si>
     <t>T0[40], Tag=0x28, Target=0x20, US=0</t>
   </si>
   <si>
-    <t>0b100000001000</t>
-  </si>
-  <si>
-    <t>0b1000000010000000</t>
-  </si>
-  <si>
-    <t>0b10000000100000001000</t>
-  </si>
-  <si>
-    <t>0b100000001000000010000000</t>
-  </si>
-  <si>
-    <t>0b1000000010000000100000001000</t>
-  </si>
-  <si>
-    <t>0b10000000100000001000000010000000</t>
-  </si>
-  <si>
-    <t>0b100000001000000010000000100000001000</t>
-  </si>
-  <si>
-    <t>0b1000000010000000100000001000000010000000</t>
-  </si>
-  <si>
-    <t>0b10000000100000001000000010000000100000001000</t>
-  </si>
-  <si>
-    <t>0b100000001000000010000000100000001000000010000000</t>
-  </si>
-  <si>
-    <t>0b1000000010000000100000001000000010000000100000001000</t>
-  </si>
-  <si>
-    <t>0b10000000100000001000000010000000100000001000000010000000</t>
-  </si>
-  <si>
     <t>0b100000001000000010000000100000001000000010000000100000001000</t>
   </si>
   <si>
@@ -498,9 +462,6 @@
     <t>actual</t>
   </si>
   <si>
-    <t xml:space="preserve"> (T0[7], Tag=x7,US=0, CTR=3)</t>
-  </si>
-  <si>
     <t>x10 - x14</t>
   </si>
   <si>
@@ -529,6 +490,30 @@
   </si>
   <si>
     <t>0180006f</t>
+  </si>
+  <si>
+    <t>ftb predicts correctly</t>
+  </si>
+  <si>
+    <t>0b1010</t>
+  </si>
+  <si>
+    <t>0b1010001000</t>
+  </si>
+  <si>
+    <t>0b1010001000001010</t>
+  </si>
+  <si>
+    <t>0b1010001000001010001000</t>
+  </si>
+  <si>
+    <t>0b1010001000001010001000001010</t>
+  </si>
+  <si>
+    <t>0b10001000001010001000001010001000</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> (T0[7], Tag=x7,US=0, CTR=3) </t>
   </si>
 </sst>
 </file>
@@ -593,13 +578,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="7" tint="0.39997558519241921"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="0" tint="-4.9989318521683403E-2"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -649,19 +627,24 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF0070C0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF00B050"/>
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFFFF00"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF00B050"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -680,8 +663,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor rgb="FFF9F9FB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -704,11 +699,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE5E5E5"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE5E5E5"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE5E5E5"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE5E5E5"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -721,16 +731,27 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1046,7 +1067,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{568F02AD-F3AB-4DFE-A2E8-3F9FAFF7E011}">
-  <dimension ref="A1:AO206"/>
+  <dimension ref="A1:AO208"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="4" customWidth="1"/>
@@ -1083,13 +1104,13 @@
       </c>
       <c r="D1" s="5"/>
       <c r="E1" s="5" t="s">
-        <v>155</v>
+        <v>142</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="H1" s="5" t="s">
         <v>32</v>
@@ -1127,19 +1148,19 @@
         <v>59</v>
       </c>
       <c r="U1" s="5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="V1" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="W1" s="5" t="s">
         <v>67</v>
       </c>
       <c r="X1" s="17" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="Y1" s="17" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="Z1" s="17" t="s">
         <v>37</v>
@@ -1202,7 +1223,7 @@
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
@@ -1225,13 +1246,13 @@
       <c r="U2" s="1"/>
       <c r="V2" s="1"/>
       <c r="W2" s="1"/>
-      <c r="X2" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="Y2" s="18" t="s">
-        <v>133</v>
-      </c>
-      <c r="Z2" s="18" t="s">
+      <c r="X2" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="Y2" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="Z2" s="16" t="s">
         <v>53</v>
       </c>
       <c r="AA2" s="1"/>
@@ -1247,7 +1268,7 @@
         <v>17</v>
       </c>
       <c r="D3" s="1"/>
-      <c r="E3" s="20">
+      <c r="E3" s="19">
         <v>293</v>
       </c>
       <c r="F3" s="1"/>
@@ -1273,13 +1294,13 @@
       <c r="U3" s="1"/>
       <c r="V3" s="1"/>
       <c r="W3" s="1"/>
-      <c r="X3" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="Y3" s="18" t="s">
-        <v>133</v>
-      </c>
-      <c r="Z3" s="18" t="s">
+      <c r="X3" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="Y3" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="Z3" s="16" t="s">
         <v>53</v>
       </c>
       <c r="AA3" s="1"/>
@@ -1295,7 +1316,7 @@
         <v>18</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="20">
+      <c r="E4" s="19">
         <v>628293</v>
       </c>
       <c r="F4" s="1"/>
@@ -1321,13 +1342,13 @@
       <c r="U4" s="1"/>
       <c r="V4" s="1"/>
       <c r="W4" s="1"/>
-      <c r="X4" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="Y4" s="18" t="s">
-        <v>133</v>
-      </c>
-      <c r="Z4" s="18" t="s">
+      <c r="X4" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="Y4" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="Z4" s="16" t="s">
         <v>53</v>
       </c>
       <c r="AA4" s="1"/>
@@ -1343,8 +1364,8 @@
         <v>19</v>
       </c>
       <c r="D5" s="1"/>
-      <c r="E5" s="20" t="s">
-        <v>157</v>
+      <c r="E5" s="19" t="s">
+        <v>144</v>
       </c>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
@@ -1371,13 +1392,13 @@
       <c r="U5" s="1"/>
       <c r="V5" s="1"/>
       <c r="W5" s="1"/>
-      <c r="X5" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="Y5" s="18" t="s">
-        <v>133</v>
-      </c>
-      <c r="Z5" s="18" t="s">
+      <c r="X5" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="Y5" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="Z5" s="16" t="s">
         <v>53</v>
       </c>
       <c r="AA5" s="1"/>
@@ -1386,14 +1407,14 @@
       <c r="A6" s="6">
         <v>5</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="8" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D6" s="6"/>
-      <c r="E6" s="20">
+      <c r="E6" s="19">
         <v>70463</v>
       </c>
       <c r="F6" s="6">
@@ -1425,13 +1446,13 @@
       <c r="U6" s="1"/>
       <c r="V6" s="1"/>
       <c r="W6" s="1"/>
-      <c r="X6" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="Y6" s="18" t="s">
-        <v>133</v>
-      </c>
-      <c r="Z6" s="18" t="s">
+      <c r="X6" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="Y6" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="Z6" s="16" t="s">
         <v>53</v>
       </c>
       <c r="AA6" s="1"/>
@@ -1447,7 +1468,7 @@
         <v>21</v>
       </c>
       <c r="D7" s="1"/>
-      <c r="E7" s="20">
+      <c r="E7" s="19">
         <v>100793</v>
       </c>
       <c r="F7" s="1"/>
@@ -1476,13 +1497,13 @@
       <c r="U7" s="1"/>
       <c r="V7" s="1"/>
       <c r="W7" s="1"/>
-      <c r="X7" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="Y7" s="18" t="s">
-        <v>133</v>
-      </c>
-      <c r="Z7" s="18" t="s">
+      <c r="X7" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="Y7" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="Z7" s="16" t="s">
         <v>53</v>
       </c>
       <c r="AA7" s="1"/>
@@ -1498,7 +1519,7 @@
         <v>22</v>
       </c>
       <c r="D8" s="1"/>
-      <c r="E8" s="20">
+      <c r="E8" s="19">
         <v>271893</v>
       </c>
       <c r="F8" s="1"/>
@@ -1529,13 +1550,13 @@
       <c r="U8" s="1"/>
       <c r="V8" s="1"/>
       <c r="W8" s="1"/>
-      <c r="X8" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="Y8" s="18" t="s">
-        <v>133</v>
-      </c>
-      <c r="Z8" s="18" t="s">
+      <c r="X8" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="Y8" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="Z8" s="16" t="s">
         <v>53</v>
       </c>
       <c r="AA8" s="1"/>
@@ -1544,15 +1565,15 @@
       <c r="A9" s="6">
         <v>8</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="9" t="s">
         <v>8</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>30</v>
       </c>
       <c r="D9" s="6"/>
-      <c r="E9" s="20" t="s">
-        <v>158</v>
+      <c r="E9" s="19" t="s">
+        <v>145</v>
       </c>
       <c r="F9" s="6">
         <v>0</v>
@@ -1592,13 +1613,13 @@
       <c r="U9" s="1"/>
       <c r="V9" s="1"/>
       <c r="W9" s="1"/>
-      <c r="X9" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="Y9" s="18" t="s">
-        <v>133</v>
-      </c>
-      <c r="Z9" s="18" t="s">
+      <c r="X9" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="Y9" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="Z9" s="16" t="s">
         <v>53</v>
       </c>
       <c r="AA9" s="1"/>
@@ -1614,8 +1635,8 @@
         <v>28</v>
       </c>
       <c r="D10" s="3"/>
-      <c r="E10" s="20" t="s">
-        <v>159</v>
+      <c r="E10" s="19" t="s">
+        <v>146</v>
       </c>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
@@ -1632,8 +1653,9 @@
       </c>
       <c r="O10" s="3"/>
       <c r="S10" s="1"/>
-      <c r="Y10" s="18"/>
-      <c r="Z10" s="18"/>
+      <c r="X10" s="1"/>
+      <c r="Y10" s="16"/>
+      <c r="Z10" s="16"/>
     </row>
     <row r="11" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
@@ -1646,7 +1668,7 @@
         <v>23</v>
       </c>
       <c r="D11" s="1"/>
-      <c r="E11" s="20">
+      <c r="E11" s="19">
         <v>1120233</v>
       </c>
       <c r="F11" s="1"/>
@@ -1674,13 +1696,13 @@
         <v>8</v>
       </c>
       <c r="S11" s="1"/>
-      <c r="X11" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="Y11" s="18" t="s">
-        <v>133</v>
-      </c>
-      <c r="Z11" s="18" t="s">
+      <c r="X11" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="Y11" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="Z11" s="16" t="s">
         <v>53</v>
       </c>
     </row>
@@ -1688,15 +1710,15 @@
       <c r="A12" s="6">
         <v>10</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="10" t="s">
         <v>10</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D12" s="6"/>
-      <c r="E12" s="20" t="s">
-        <v>160</v>
+      <c r="E12" s="19" t="s">
+        <v>147</v>
       </c>
       <c r="F12" s="6">
         <v>0</v>
@@ -1732,13 +1754,13 @@
       <c r="T12" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="X12" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="Y12" s="18" t="s">
-        <v>134</v>
-      </c>
-      <c r="Z12" s="18" t="s">
+      <c r="X12" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="Y12" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="Z12" s="16" t="s">
         <v>89</v>
       </c>
     </row>
@@ -1753,7 +1775,7 @@
         <v>25</v>
       </c>
       <c r="D13" s="1"/>
-      <c r="E13" s="20">
+      <c r="E13" s="19">
         <v>1400793</v>
       </c>
       <c r="F13" s="1"/>
@@ -1782,13 +1804,13 @@
       </c>
       <c r="S13" s="1"/>
       <c r="T13" s="1"/>
-      <c r="X13" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="Y13" s="18" t="s">
-        <v>134</v>
-      </c>
-      <c r="Z13" s="18" t="s">
+      <c r="X13" s="23" t="s">
+        <v>152</v>
+      </c>
+      <c r="Y13" s="23" t="s">
+        <v>152</v>
+      </c>
+      <c r="Z13" s="16" t="s">
         <v>53</v>
       </c>
     </row>
@@ -1796,15 +1818,15 @@
       <c r="A14" s="6">
         <v>12</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="15" t="s">
         <v>12</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>26</v>
       </c>
       <c r="D14" s="1"/>
-      <c r="E14" s="20" t="s">
-        <v>161</v>
+      <c r="E14" s="19" t="s">
+        <v>148</v>
       </c>
       <c r="F14" s="1">
         <v>0</v>
@@ -1838,13 +1860,13 @@
       <c r="T14" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="X14" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="Y14" s="18" t="s">
-        <v>134</v>
-      </c>
-      <c r="Z14" s="18" t="s">
+      <c r="X14" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="Y14" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="Z14" s="16" t="s">
         <v>53</v>
       </c>
     </row>
@@ -1852,15 +1874,15 @@
       <c r="A15" s="6">
         <v>13</v>
       </c>
-      <c r="B15" s="12" t="s">
+      <c r="B15" s="11" t="s">
         <v>13</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>27</v>
       </c>
       <c r="D15" s="6"/>
-      <c r="E15" s="20" t="s">
-        <v>162</v>
+      <c r="E15" s="19" t="s">
+        <v>149</v>
       </c>
       <c r="F15" s="6">
         <v>0</v>
@@ -1903,13 +1925,13 @@
       <c r="W15" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="X15" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="Y15" s="18" t="s">
-        <v>134</v>
-      </c>
-      <c r="Z15" s="18" t="s">
+      <c r="X15" s="23" t="s">
+        <v>152</v>
+      </c>
+      <c r="Y15" s="23" t="s">
+        <v>152</v>
+      </c>
+      <c r="Z15" s="16" t="s">
         <v>53</v>
       </c>
     </row>
@@ -1924,7 +1946,7 @@
         <v>54</v>
       </c>
       <c r="D16" s="1"/>
-      <c r="E16" s="20">
+      <c r="E16" s="19">
         <v>628293</v>
       </c>
       <c r="F16" s="1"/>
@@ -1953,13 +1975,13 @@
       </c>
       <c r="S16" s="1"/>
       <c r="T16" s="1"/>
-      <c r="X16" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="Y16" s="18" t="s">
-        <v>134</v>
-      </c>
-      <c r="Z16" s="18" t="s">
+      <c r="X16" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="Y16" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="Z16" s="16" t="s">
         <v>53</v>
       </c>
     </row>
@@ -1974,8 +1996,8 @@
         <v>19</v>
       </c>
       <c r="D17" s="1"/>
-      <c r="E17" s="20" t="s">
-        <v>157</v>
+      <c r="E17" s="19" t="s">
+        <v>144</v>
       </c>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
@@ -2001,13 +2023,13 @@
       </c>
       <c r="S17" s="1"/>
       <c r="T17" s="1"/>
-      <c r="X17" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="Y17" s="18" t="s">
-        <v>134</v>
-      </c>
-      <c r="Z17" s="18" t="s">
+      <c r="X17" s="23" t="s">
+        <v>152</v>
+      </c>
+      <c r="Y17" s="23" t="s">
+        <v>152</v>
+      </c>
+      <c r="Z17" s="16" t="s">
         <v>53</v>
       </c>
     </row>
@@ -2015,14 +2037,14 @@
       <c r="A18" s="6">
         <v>16</v>
       </c>
-      <c r="B18" s="13" t="s">
+      <c r="B18" s="12" t="s">
         <v>5</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D18" s="1"/>
-      <c r="E18" s="20">
+      <c r="E18" s="19">
         <v>70463</v>
       </c>
       <c r="F18" s="1">
@@ -2066,13 +2088,13 @@
       <c r="W18" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="X18" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="Y18" s="18" t="s">
-        <v>134</v>
-      </c>
-      <c r="Z18" s="18" t="s">
+      <c r="X18" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="Y18" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="Z18" s="16" t="s">
         <v>53</v>
       </c>
     </row>
@@ -2087,7 +2109,7 @@
         <v>21</v>
       </c>
       <c r="D19" s="3"/>
-      <c r="E19" s="20">
+      <c r="E19" s="19">
         <v>100793</v>
       </c>
       <c r="F19" s="3"/>
@@ -2101,8 +2123,9 @@
       <c r="U19" s="1"/>
       <c r="V19" s="1"/>
       <c r="W19" s="1"/>
-      <c r="Y19" s="18"/>
-      <c r="Z19" s="18"/>
+      <c r="X19" s="22"/>
+      <c r="Y19" s="22"/>
+      <c r="Z19" s="16"/>
     </row>
     <row r="20" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
@@ -2115,7 +2138,7 @@
         <v>22</v>
       </c>
       <c r="D20" s="1"/>
-      <c r="E20" s="20">
+      <c r="E20" s="19">
         <v>271893</v>
       </c>
       <c r="F20" s="1"/>
@@ -2145,13 +2168,13 @@
       <c r="U20" s="1"/>
       <c r="V20" s="1"/>
       <c r="W20" s="1"/>
-      <c r="X20" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="Y20" s="18" t="s">
-        <v>134</v>
-      </c>
-      <c r="Z20" s="18" t="s">
+      <c r="X20" s="23" t="s">
+        <v>152</v>
+      </c>
+      <c r="Y20" s="23" t="s">
+        <v>152</v>
+      </c>
+      <c r="Z20" s="16" t="s">
         <v>53</v>
       </c>
     </row>
@@ -2159,14 +2182,14 @@
       <c r="A21" s="1">
         <v>18</v>
       </c>
-      <c r="B21" s="10" t="s">
+      <c r="B21" s="9" t="s">
         <v>8</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="E21" s="20" t="s">
-        <v>158</v>
+      <c r="E21" s="19" t="s">
+        <v>145</v>
       </c>
       <c r="F21" s="4">
         <v>0</v>
@@ -2175,7 +2198,7 @@
         <v>1</v>
       </c>
       <c r="I21" s="1">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J21" s="1" t="s">
         <v>57</v>
@@ -2199,13 +2222,13 @@
         <v>66</v>
       </c>
       <c r="T21" s="1"/>
-      <c r="X21" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="Y21" s="18" t="s">
-        <v>134</v>
-      </c>
-      <c r="Z21" s="18" t="s">
+      <c r="X21" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="Y21" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="Z21" s="16" t="s">
         <v>53</v>
       </c>
     </row>
@@ -2220,8 +2243,8 @@
         <v>25</v>
       </c>
       <c r="D22" s="3"/>
-      <c r="E22" s="20" t="s">
-        <v>159</v>
+      <c r="E22" s="19" t="s">
+        <v>146</v>
       </c>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
@@ -2237,8 +2260,9 @@
       <c r="O22" s="1"/>
       <c r="S22" s="7"/>
       <c r="T22" s="1"/>
-      <c r="Y22" s="18"/>
-      <c r="Z22" s="18"/>
+      <c r="X22" s="22"/>
+      <c r="Y22" s="22"/>
+      <c r="Z22" s="16"/>
     </row>
     <row r="23" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
@@ -2250,7 +2274,7 @@
       <c r="C23" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E23" s="20">
+      <c r="E23" s="19">
         <v>1120233</v>
       </c>
       <c r="J23" s="1" t="s">
@@ -2271,17 +2295,15 @@
       <c r="O23" s="1">
         <v>0</v>
       </c>
-      <c r="S23" s="7" t="s">
-        <v>66</v>
-      </c>
+      <c r="S23" s="7"/>
       <c r="T23" s="1"/>
-      <c r="X23" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="Y23" s="18" t="s">
-        <v>134</v>
-      </c>
-      <c r="Z23" s="18" t="s">
+      <c r="X23" s="23" t="s">
+        <v>152</v>
+      </c>
+      <c r="Y23" s="23" t="s">
+        <v>152</v>
+      </c>
+      <c r="Z23" s="16" t="s">
         <v>53</v>
       </c>
     </row>
@@ -2289,15 +2311,15 @@
       <c r="A24" s="1">
         <v>20</v>
       </c>
-      <c r="B24" s="11" t="s">
+      <c r="B24" s="10" t="s">
         <v>10</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D24" s="1"/>
-      <c r="E24" s="20" t="s">
-        <v>160</v>
+      <c r="E24" s="19" t="s">
+        <v>147</v>
       </c>
       <c r="F24" s="1">
         <v>0</v>
@@ -2309,7 +2331,7 @@
         <v>79</v>
       </c>
       <c r="I24" s="1">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J24" s="1" t="s">
         <v>57</v>
@@ -2332,23 +2354,21 @@
       <c r="P24" s="1"/>
       <c r="Q24" s="1"/>
       <c r="R24" s="1"/>
-      <c r="S24" s="7" t="s">
-        <v>66</v>
-      </c>
+      <c r="S24" s="7"/>
       <c r="T24" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="U24" s="1"/>
       <c r="V24" s="1"/>
       <c r="W24" s="1"/>
-      <c r="X24" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="Y24" s="18" t="s">
-        <v>135</v>
-      </c>
-      <c r="Z24" s="18" t="s">
-        <v>136</v>
+      <c r="X24" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="Y24" s="22" t="s">
+        <v>153</v>
+      </c>
+      <c r="Z24" s="16" t="s">
+        <v>90</v>
       </c>
       <c r="AA24" s="1"/>
       <c r="AB24" s="1"/>
@@ -2367,8 +2387,8 @@
         <v>28</v>
       </c>
       <c r="D25" s="1"/>
-      <c r="E25" s="20" t="s">
-        <v>159</v>
+      <c r="E25" s="19" t="s">
+        <v>146</v>
       </c>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
@@ -2378,7 +2398,7 @@
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
       <c r="K25" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L25" s="1">
         <v>12</v>
@@ -2395,20 +2415,18 @@
       <c r="P25" s="1"/>
       <c r="Q25" s="1"/>
       <c r="R25" s="1"/>
-      <c r="S25" s="7" t="s">
-        <v>66</v>
-      </c>
+      <c r="S25" s="7"/>
       <c r="T25" s="1"/>
       <c r="U25" s="1"/>
       <c r="V25" s="1"/>
       <c r="W25" s="1"/>
-      <c r="X25" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="Y25" s="18" t="s">
-        <v>135</v>
-      </c>
-      <c r="Z25" s="18" t="s">
+      <c r="X25" s="23" t="s">
+        <v>153</v>
+      </c>
+      <c r="Y25" s="23" t="s">
+        <v>153</v>
+      </c>
+      <c r="Z25" s="16" t="s">
         <v>53</v>
       </c>
       <c r="AA25" s="1"/>
@@ -2421,15 +2439,15 @@
       <c r="A26" s="1">
         <v>22</v>
       </c>
-      <c r="B26" s="14" t="s">
+      <c r="B26" s="13" t="s">
         <v>15</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D26" s="1"/>
-      <c r="E26" s="20" t="s">
-        <v>163</v>
+      <c r="E26" s="19" t="s">
+        <v>150</v>
       </c>
       <c r="F26" s="1">
         <v>0</v>
@@ -2439,13 +2457,13 @@
       </c>
       <c r="H26" s="1"/>
       <c r="I26" s="1">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J26" s="1" t="s">
         <v>57</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L26" s="1">
         <v>12</v>
@@ -2462,22 +2480,20 @@
       <c r="P26" s="1"/>
       <c r="Q26" s="1"/>
       <c r="R26" s="1"/>
-      <c r="S26" s="7" t="s">
-        <v>66</v>
-      </c>
+      <c r="S26" s="7"/>
       <c r="T26" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="U26" s="1"/>
       <c r="V26" s="1"/>
       <c r="W26" s="1"/>
-      <c r="X26" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="Y26" s="18" t="s">
-        <v>135</v>
-      </c>
-      <c r="Z26" s="18" t="s">
+      <c r="X26" s="22" t="s">
+        <v>153</v>
+      </c>
+      <c r="Y26" s="22" t="s">
+        <v>153</v>
+      </c>
+      <c r="Z26" s="16" t="s">
         <v>53</v>
       </c>
       <c r="AA26" s="1"/>
@@ -2490,14 +2506,14 @@
       <c r="A27" s="1">
         <v>23</v>
       </c>
-      <c r="B27" s="15" t="s">
+      <c r="B27" s="14" t="s">
         <v>13</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>27</v>
       </c>
       <c r="D27" s="1"/>
-      <c r="E27" s="20">
+      <c r="E27" s="19">
         <v>1400793</v>
       </c>
       <c r="F27" s="1">
@@ -2508,13 +2524,13 @@
       </c>
       <c r="H27" s="1"/>
       <c r="I27" s="1">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J27" s="1" t="s">
         <v>57</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L27" s="1">
         <v>12</v>
@@ -2531,11 +2547,9 @@
       <c r="P27" s="1"/>
       <c r="Q27" s="1"/>
       <c r="R27" s="1"/>
-      <c r="S27" s="7" t="s">
-        <v>66</v>
-      </c>
+      <c r="S27" s="7"/>
       <c r="T27" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U27" s="1">
         <v>3</v>
@@ -2546,13 +2560,13 @@
       <c r="W27" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="X27" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="Y27" s="18" t="s">
-        <v>135</v>
-      </c>
-      <c r="Z27" s="18" t="s">
+      <c r="X27" s="23" t="s">
+        <v>153</v>
+      </c>
+      <c r="Y27" s="23" t="s">
+        <v>153</v>
+      </c>
+      <c r="Z27" s="16" t="s">
         <v>53</v>
       </c>
       <c r="AA27" s="1"/>
@@ -2563,15 +2577,15 @@
     </row>
     <row r="28" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A28" s="2"/>
-      <c r="B28" s="10" t="s">
+      <c r="B28" s="9" t="s">
         <v>8</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>29</v>
       </c>
       <c r="D28" s="2"/>
-      <c r="E28" s="20" t="s">
-        <v>158</v>
+      <c r="E28" s="19" t="s">
+        <v>145</v>
       </c>
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
@@ -2588,17 +2602,16 @@
       <c r="P28" s="2"/>
       <c r="Q28" s="2"/>
       <c r="R28" s="2"/>
-      <c r="S28" s="7" t="s">
-        <v>66</v>
-      </c>
+      <c r="S28" s="7"/>
       <c r="T28" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="U28" s="1"/>
       <c r="V28" s="1"/>
       <c r="W28" s="1"/>
-      <c r="Y28" s="18"/>
-      <c r="Z28" s="18"/>
+      <c r="X28" s="23"/>
+      <c r="Y28" s="23"/>
+      <c r="Z28" s="16"/>
       <c r="AA28" s="1"/>
       <c r="AB28" s="1"/>
       <c r="AC28" s="1"/>
@@ -2616,7 +2629,7 @@
         <v>54</v>
       </c>
       <c r="D29" s="1"/>
-      <c r="E29" s="20">
+      <c r="E29" s="19">
         <v>628293</v>
       </c>
       <c r="F29" s="1"/>
@@ -2629,7 +2642,7 @@
         <v>72</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L29" s="1">
         <v>18</v>
@@ -2646,24 +2659,22 @@
       <c r="P29" s="1"/>
       <c r="Q29" s="1"/>
       <c r="R29" s="1"/>
-      <c r="S29" s="1" t="s">
-        <v>66</v>
-      </c>
+      <c r="S29" s="1"/>
       <c r="T29" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U29" s="1"/>
       <c r="V29" s="1"/>
       <c r="W29" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X29" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="Y29" s="18" t="s">
-        <v>135</v>
-      </c>
-      <c r="Z29" s="18" t="s">
+      <c r="X29" s="22" t="s">
+        <v>153</v>
+      </c>
+      <c r="Y29" s="22" t="s">
+        <v>153</v>
+      </c>
+      <c r="Z29" s="16" t="s">
         <v>53</v>
       </c>
       <c r="AB29" s="1"/>
@@ -2682,20 +2693,20 @@
         <v>19</v>
       </c>
       <c r="D30" s="1"/>
-      <c r="E30" s="20" t="s">
-        <v>157</v>
-      </c>
-      <c r="F30" s="1">
+      <c r="E30" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1">
         <v>110</v>
       </c>
-      <c r="G30" s="1"/>
-      <c r="H30" s="1"/>
       <c r="I30" s="1"/>
       <c r="J30" s="1" t="s">
         <v>72</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L30" s="1">
         <v>18</v>
@@ -2712,22 +2723,20 @@
       <c r="P30" s="1"/>
       <c r="Q30" s="1"/>
       <c r="R30" s="1"/>
-      <c r="S30" s="1" t="s">
-        <v>66</v>
-      </c>
+      <c r="S30" s="1"/>
       <c r="T30" s="1"/>
       <c r="U30" s="1"/>
       <c r="V30" s="1"/>
       <c r="W30" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X30" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="Y30" s="18" t="s">
-        <v>135</v>
-      </c>
-      <c r="Z30" s="18" t="s">
+      <c r="X30" s="23" t="s">
+        <v>153</v>
+      </c>
+      <c r="Y30" s="23" t="s">
+        <v>153</v>
+      </c>
+      <c r="Z30" s="16" t="s">
         <v>53</v>
       </c>
       <c r="AB30" s="1"/>
@@ -2739,14 +2748,14 @@
       <c r="A31" s="1">
         <v>26</v>
       </c>
-      <c r="B31" s="13" t="s">
+      <c r="B31" s="12" t="s">
         <v>5</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D31" s="1"/>
-      <c r="E31" s="20">
+      <c r="E31" s="19">
         <v>70463</v>
       </c>
       <c r="F31" s="1">
@@ -2763,7 +2772,7 @@
         <v>72</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L31" s="1">
         <v>18</v>
@@ -2781,7 +2790,7 @@
       <c r="Q31" s="1"/>
       <c r="R31" s="1"/>
       <c r="S31" s="1" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="T31" s="1"/>
       <c r="U31" s="1">
@@ -2790,16 +2799,16 @@
       <c r="V31" s="1">
         <v>14</v>
       </c>
-      <c r="W31" s="19" t="s">
+      <c r="W31" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="X31" s="22" t="s">
         <v>153</v>
       </c>
-      <c r="X31" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="Y31" s="18" t="s">
-        <v>135</v>
-      </c>
-      <c r="Z31" s="18" t="s">
+      <c r="Y31" s="22" t="s">
+        <v>153</v>
+      </c>
+      <c r="Z31" s="16" t="s">
         <v>53</v>
       </c>
       <c r="AB31" s="1"/>
@@ -2818,53 +2827,55 @@
         <v>21</v>
       </c>
       <c r="D32" s="1"/>
-      <c r="E32" s="20">
+      <c r="E32" s="19">
         <v>100793</v>
       </c>
-      <c r="F32" s="1">
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1">
         <v>110</v>
       </c>
-      <c r="G32" s="1"/>
-      <c r="H32" s="1"/>
       <c r="I32" s="1"/>
-      <c r="J32" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="K32" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="L32" s="4">
+      <c r="J32" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="L32" s="1">
         <v>18</v>
       </c>
-      <c r="M32" s="4">
+      <c r="M32" s="1">
         <v>2</v>
       </c>
-      <c r="N32" s="4">
+      <c r="N32" s="1">
         <v>1</v>
       </c>
-      <c r="O32" s="4">
+      <c r="O32" s="1">
         <v>0</v>
       </c>
       <c r="P32" s="1"/>
       <c r="Q32" s="1"/>
       <c r="R32" s="1"/>
-      <c r="S32" s="4" t="s">
-        <v>66</v>
-      </c>
+      <c r="S32" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="T32" s="1"/>
       <c r="U32" s="1"/>
       <c r="V32" s="1"/>
-      <c r="W32" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="X32" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="Y32" s="18" t="s">
-        <v>135</v>
-      </c>
-      <c r="Z32" s="18" t="s">
-        <v>53</v>
-      </c>
+      <c r="W32" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="X32" s="23" t="s">
+        <v>153</v>
+      </c>
+      <c r="Y32" s="23" t="s">
+        <v>153</v>
+      </c>
+      <c r="Z32" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="AA32" s="1"/>
       <c r="AB32" s="1"/>
       <c r="AC32" s="1"/>
       <c r="AD32" s="1"/>
@@ -2881,53 +2892,55 @@
         <v>22</v>
       </c>
       <c r="D33" s="1"/>
-      <c r="E33" s="20">
+      <c r="E33" s="19">
         <v>271893</v>
       </c>
-      <c r="F33" s="1">
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1">
         <v>111</v>
       </c>
-      <c r="G33" s="1"/>
-      <c r="H33" s="1"/>
       <c r="I33" s="1"/>
-      <c r="J33" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="K33" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="L33" s="4">
+      <c r="J33" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="L33" s="1">
         <v>18</v>
       </c>
-      <c r="M33" s="4">
+      <c r="M33" s="1">
         <v>2</v>
       </c>
-      <c r="N33" s="4">
+      <c r="N33" s="1">
         <v>1</v>
       </c>
-      <c r="O33" s="4">
+      <c r="O33" s="1">
         <v>8</v>
       </c>
       <c r="P33" s="1"/>
       <c r="Q33" s="1"/>
       <c r="R33" s="1"/>
-      <c r="S33" s="4" t="s">
-        <v>66</v>
-      </c>
+      <c r="S33" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="T33" s="1"/>
       <c r="U33" s="1"/>
       <c r="V33" s="1"/>
-      <c r="W33" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="X33" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="Y33" s="18" t="s">
-        <v>135</v>
-      </c>
-      <c r="Z33" s="18" t="s">
-        <v>53</v>
-      </c>
+      <c r="W33" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="X33" s="22" t="s">
+        <v>153</v>
+      </c>
+      <c r="Y33" s="22" t="s">
+        <v>153</v>
+      </c>
+      <c r="Z33" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="AA33" s="1"/>
       <c r="AB33" s="1"/>
       <c r="AC33" s="1"/>
       <c r="AD33" s="1"/>
@@ -2937,58 +2950,68 @@
       <c r="A34" s="1">
         <v>29</v>
       </c>
-      <c r="B34" s="10" t="s">
+      <c r="B34" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C34" s="6" t="s">
         <v>30</v>
       </c>
       <c r="D34" s="1"/>
-      <c r="E34" s="20" t="s">
-        <v>158</v>
-      </c>
-      <c r="F34" s="1"/>
-      <c r="G34" s="1"/>
+      <c r="E34" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="F34" s="1">
+        <v>1</v>
+      </c>
+      <c r="G34" s="1">
+        <v>1</v>
+      </c>
       <c r="H34" s="1"/>
-      <c r="I34" s="1"/>
-      <c r="J34" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="K34" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="L34" s="4">
+      <c r="I34" s="1">
+        <v>110</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="L34" s="1">
         <v>18</v>
       </c>
-      <c r="M34" s="4">
+      <c r="M34" s="1">
         <v>2</v>
       </c>
-      <c r="N34" s="4">
+      <c r="N34" s="1">
         <v>1</v>
       </c>
-      <c r="O34" s="4">
+      <c r="O34" s="1">
         <v>8</v>
       </c>
       <c r="P34" s="1"/>
-      <c r="Q34" s="1"/>
+      <c r="Q34" s="1" t="s">
+        <v>151</v>
+      </c>
       <c r="R34" s="1"/>
-      <c r="S34" s="4" t="s">
-        <v>66</v>
-      </c>
+      <c r="S34" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="T34" s="1"/>
       <c r="U34" s="1"/>
       <c r="V34" s="1"/>
-      <c r="W34" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="X34" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="Y34" s="18" t="s">
-        <v>135</v>
-      </c>
-      <c r="Z34" s="18" t="s">
-        <v>53</v>
-      </c>
+      <c r="W34" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="X34" s="23" t="s">
+        <v>153</v>
+      </c>
+      <c r="Y34" s="23" t="s">
+        <v>153</v>
+      </c>
+      <c r="Z34" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="AA34" s="1"/>
       <c r="AB34" s="1"/>
       <c r="AC34" s="1"/>
       <c r="AD34" s="1"/>
@@ -3005,51 +3028,53 @@
         <v>23</v>
       </c>
       <c r="D35" s="1"/>
-      <c r="E35" s="20">
+      <c r="E35" s="19">
         <v>1120233</v>
       </c>
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
-      <c r="J35" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="K35" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="L35" s="4">
+      <c r="J35" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="L35" s="1">
         <v>18</v>
       </c>
-      <c r="M35" s="4">
+      <c r="M35" s="1">
         <v>2</v>
       </c>
-      <c r="N35" s="4">
+      <c r="N35" s="1">
         <v>1</v>
       </c>
-      <c r="O35" s="4">
+      <c r="O35" s="1">
         <v>8</v>
       </c>
       <c r="P35" s="1"/>
       <c r="Q35" s="1"/>
       <c r="R35" s="1"/>
-      <c r="S35" s="4" t="s">
-        <v>66</v>
-      </c>
+      <c r="S35" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="T35" s="1"/>
       <c r="U35" s="1"/>
       <c r="V35" s="1"/>
-      <c r="W35" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="X35" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="Y35" s="18" t="s">
-        <v>135</v>
-      </c>
-      <c r="Z35" s="18" t="s">
-        <v>53</v>
-      </c>
+      <c r="W35" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="X35" s="22" t="s">
+        <v>153</v>
+      </c>
+      <c r="Y35" s="22" t="s">
+        <v>153</v>
+      </c>
+      <c r="Z35" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="AA35" s="1"/>
       <c r="AB35" s="1"/>
       <c r="AC35" s="1"/>
       <c r="AD35" s="1"/>
@@ -3059,61 +3084,68 @@
       <c r="A36" s="1">
         <v>31</v>
       </c>
-      <c r="B36" s="11" t="s">
+      <c r="B36" s="10" t="s">
         <v>10</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D36" s="1"/>
-      <c r="E36" s="20" t="s">
-        <v>160</v>
-      </c>
-      <c r="F36" s="1"/>
-      <c r="G36" s="1"/>
+      <c r="E36" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="F36" s="1">
+        <v>0</v>
+      </c>
+      <c r="G36" s="1">
+        <v>1</v>
+      </c>
       <c r="H36" s="1"/>
-      <c r="I36" s="1"/>
-      <c r="J36" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="K36" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="L36" s="4">
+      <c r="I36" s="1">
+        <v>112</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="L36" s="1">
         <v>18</v>
       </c>
-      <c r="M36" s="4">
+      <c r="M36" s="1">
         <v>2</v>
       </c>
-      <c r="N36" s="4">
+      <c r="N36" s="1">
         <v>1</v>
       </c>
-      <c r="O36" s="4">
+      <c r="O36" s="1">
         <v>8</v>
       </c>
       <c r="P36" s="1"/>
       <c r="Q36" s="1"/>
       <c r="R36" s="1"/>
-      <c r="S36" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="T36" s="4" t="s">
-        <v>93</v>
+      <c r="S36" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="T36" s="1" t="s">
+        <v>95</v>
       </c>
       <c r="U36" s="1"/>
       <c r="V36" s="1"/>
-      <c r="W36" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="X36" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="Y36" s="18" t="s">
-        <v>137</v>
-      </c>
-      <c r="Z36" s="18" t="s">
-        <v>89</v>
-      </c>
+      <c r="W36" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="X36" s="23" t="s">
+        <v>153</v>
+      </c>
+      <c r="Y36" s="23" t="s">
+        <v>154</v>
+      </c>
+      <c r="Z36" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="AA36" s="1"/>
       <c r="AB36" s="1"/>
       <c r="AC36" s="1"/>
       <c r="AD36" s="1"/>
@@ -3130,54 +3162,57 @@
         <v>25</v>
       </c>
       <c r="D37" s="1"/>
-      <c r="E37" s="20">
+      <c r="E37" s="19">
         <v>1400793</v>
       </c>
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
-      <c r="H37" s="1"/>
+      <c r="H37" s="1">
+        <v>124</v>
+      </c>
       <c r="I37" s="1"/>
-      <c r="J37" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="K37" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="L37" s="4">
+      <c r="J37" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="K37" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="L37" s="1">
         <v>18</v>
       </c>
-      <c r="M37" s="4">
+      <c r="M37" s="1">
         <v>2</v>
       </c>
-      <c r="N37" s="4">
+      <c r="N37" s="1">
         <v>20</v>
       </c>
-      <c r="O37" s="4">
+      <c r="O37" s="1">
         <v>8</v>
       </c>
       <c r="P37" s="1"/>
       <c r="Q37" s="1"/>
       <c r="R37" s="1"/>
-      <c r="S37" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="T37" s="4" t="s">
-        <v>93</v>
+      <c r="S37" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="T37" s="1" t="s">
+        <v>95</v>
       </c>
       <c r="U37" s="1"/>
       <c r="V37" s="1"/>
-      <c r="W37" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="X37" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="Y37" s="18" t="s">
-        <v>137</v>
-      </c>
-      <c r="Z37" s="18" t="s">
-        <v>53</v>
-      </c>
+      <c r="W37" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="X37" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="Y37" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="Z37" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="AA37" s="1"/>
       <c r="AB37" s="1"/>
       <c r="AC37" s="1"/>
       <c r="AD37" s="1"/>
@@ -3187,59 +3222,65 @@
       <c r="A38" s="1">
         <v>33</v>
       </c>
-      <c r="B38" s="16" t="s">
+      <c r="B38" s="15" t="s">
         <v>12</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D38" s="1"/>
-      <c r="E38" s="20" t="s">
-        <v>161</v>
-      </c>
-      <c r="F38" s="1"/>
-      <c r="G38" s="1"/>
-      <c r="H38" s="1"/>
+      <c r="E38" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="F38" s="1">
+        <v>0</v>
+      </c>
+      <c r="G38" s="1">
+        <v>1</v>
+      </c>
+      <c r="H38" s="1">
+        <v>123</v>
+      </c>
       <c r="I38" s="1"/>
-      <c r="J38" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="K38" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="L38" s="4">
+      <c r="J38" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="K38" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="L38" s="1">
         <v>18</v>
       </c>
-      <c r="M38" s="4">
+      <c r="M38" s="1">
         <v>2</v>
       </c>
-      <c r="N38" s="4">
+      <c r="N38" s="1">
         <v>20</v>
       </c>
-      <c r="O38" s="4">
+      <c r="O38" s="1">
         <v>8</v>
       </c>
       <c r="P38" s="1"/>
       <c r="Q38" s="1"/>
       <c r="R38" s="1"/>
-      <c r="S38" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="T38" s="4" t="s">
-        <v>94</v>
+      <c r="S38" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="T38" s="1" t="s">
+        <v>96</v>
       </c>
       <c r="U38" s="1"/>
       <c r="V38" s="1"/>
       <c r="W38" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X38" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="Y38" s="18" t="s">
-        <v>137</v>
-      </c>
-      <c r="Z38" s="18" t="s">
+      <c r="X38" s="23" t="s">
+        <v>154</v>
+      </c>
+      <c r="Y38" s="23" t="s">
+        <v>154</v>
+      </c>
+      <c r="Z38" s="16" t="s">
         <v>53</v>
       </c>
       <c r="AB38" s="1"/>
@@ -3251,48 +3292,52 @@
       <c r="A39" s="1">
         <v>34</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="B39" s="14" t="s">
         <v>13</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D39" s="1"/>
-      <c r="E39" s="20">
+      <c r="E39" s="19">
         <v>1120233</v>
       </c>
-      <c r="F39" s="1"/>
-      <c r="G39" s="1"/>
+      <c r="F39" s="1">
+        <v>0</v>
+      </c>
+      <c r="G39" s="1">
+        <v>1</v>
+      </c>
       <c r="H39" s="1"/>
-      <c r="I39" s="8">
-        <v>121</v>
-      </c>
-      <c r="J39" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="K39" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="L39" s="4">
+      <c r="I39" s="1">
+        <v>132</v>
+      </c>
+      <c r="J39" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="K39" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="L39" s="1">
         <v>18</v>
       </c>
-      <c r="M39" s="4">
+      <c r="M39" s="1">
         <v>2</v>
       </c>
-      <c r="N39" s="4">
+      <c r="N39" s="1">
         <v>20</v>
       </c>
-      <c r="O39" s="4">
+      <c r="O39" s="1">
         <v>8</v>
       </c>
       <c r="P39" s="1"/>
       <c r="Q39" s="1"/>
       <c r="R39" s="1"/>
-      <c r="S39" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="T39" s="4" t="s">
-        <v>92</v>
+      <c r="S39" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="T39" s="1" t="s">
+        <v>94</v>
       </c>
       <c r="U39" s="1">
         <v>14</v>
@@ -3303,13 +3348,13 @@
       <c r="W39" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="X39" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="Y39" s="18" t="s">
-        <v>137</v>
-      </c>
-      <c r="Z39" s="18" t="s">
+      <c r="X39" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="Y39" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="Z39" s="16" t="s">
         <v>53</v>
       </c>
       <c r="AB39" s="1"/>
@@ -3328,7 +3373,9 @@
         <v>54</v>
       </c>
       <c r="D40" s="1"/>
-      <c r="E40" s="1"/>
+      <c r="E40" s="1" t="s">
+        <v>143</v>
+      </c>
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
       <c r="H40" s="1"/>
@@ -3337,7 +3384,7 @@
         <v>72</v>
       </c>
       <c r="K40" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L40" s="4">
         <v>24</v>
@@ -3358,24 +3405,24 @@
         <v>66</v>
       </c>
       <c r="T40" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U40" s="4" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="V40" s="4" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="W40" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X40" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="Y40" s="18" t="s">
-        <v>137</v>
-      </c>
-      <c r="Z40" s="18" t="s">
+      <c r="X40" s="23" t="s">
+        <v>154</v>
+      </c>
+      <c r="Y40" s="23" t="s">
+        <v>154</v>
+      </c>
+      <c r="Z40" s="16" t="s">
         <v>53</v>
       </c>
       <c r="AB40" s="1"/>
@@ -3394,7 +3441,9 @@
         <v>19</v>
       </c>
       <c r="D41" s="1"/>
-      <c r="E41" s="1"/>
+      <c r="E41" s="19">
+        <v>293</v>
+      </c>
       <c r="F41" s="1"/>
       <c r="G41" s="1"/>
       <c r="H41" s="1"/>
@@ -3403,7 +3452,7 @@
         <v>72</v>
       </c>
       <c r="K41" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L41" s="4">
         <v>24</v>
@@ -3424,24 +3473,24 @@
         <v>66</v>
       </c>
       <c r="T41" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U41" s="4" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="V41" s="4" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="W41" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X41" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="Y41" s="18" t="s">
-        <v>137</v>
-      </c>
-      <c r="Z41" s="18" t="s">
+      <c r="X41" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="Y41" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="Z41" s="16" t="s">
         <v>53</v>
       </c>
       <c r="AB41" s="1"/>
@@ -3453,23 +3502,29 @@
       <c r="A42" s="1">
         <v>37</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="B42" s="12" t="s">
         <v>5</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D42" s="1"/>
-      <c r="E42" s="1"/>
+      <c r="E42" s="19">
+        <v>628293</v>
+      </c>
       <c r="F42" s="1"/>
-      <c r="G42" s="1"/>
+      <c r="G42" s="1">
+        <v>0</v>
+      </c>
       <c r="H42" s="1"/>
-      <c r="I42" s="1"/>
+      <c r="I42" s="1">
+        <v>144</v>
+      </c>
       <c r="J42" s="4" t="s">
         <v>72</v>
       </c>
       <c r="K42" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L42" s="4">
         <v>24</v>
@@ -3490,24 +3545,24 @@
         <v>65</v>
       </c>
       <c r="T42" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U42" s="4" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="V42" s="4" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="W42" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="X42" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="Y42" s="18" t="s">
-        <v>137</v>
-      </c>
-      <c r="Z42" s="18" t="s">
+      <c r="X42" s="23" t="s">
+        <v>154</v>
+      </c>
+      <c r="Y42" s="23" t="s">
+        <v>154</v>
+      </c>
+      <c r="Z42" s="16" t="s">
         <v>53</v>
       </c>
       <c r="AB42" s="1"/>
@@ -3526,7 +3581,9 @@
         <v>22</v>
       </c>
       <c r="D43" s="1"/>
-      <c r="E43" s="1"/>
+      <c r="E43" s="19" t="s">
+        <v>144</v>
+      </c>
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
       <c r="H43" s="1"/>
@@ -3535,7 +3592,7 @@
         <v>72</v>
       </c>
       <c r="K43" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L43" s="4">
         <v>24</v>
@@ -3556,24 +3613,24 @@
         <v>65</v>
       </c>
       <c r="T43" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U43" s="4" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="V43" s="4" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="W43" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X43" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="Y43" s="18" t="s">
-        <v>137</v>
-      </c>
-      <c r="Z43" s="18" t="s">
+      <c r="X43" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="Y43" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="Z43" s="16" t="s">
         <v>53</v>
       </c>
       <c r="AB43" s="1"/>
@@ -3585,14 +3642,16 @@
       <c r="A44" s="1">
         <v>39</v>
       </c>
-      <c r="B44" s="1" t="s">
+      <c r="B44" s="9" t="s">
         <v>8</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D44" s="1"/>
-      <c r="E44" s="1"/>
+      <c r="E44" s="19">
+        <v>70463</v>
+      </c>
       <c r="F44" s="1"/>
       <c r="G44" s="1"/>
       <c r="H44" s="1"/>
@@ -3601,7 +3660,7 @@
         <v>72</v>
       </c>
       <c r="K44" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L44" s="4">
         <v>24</v>
@@ -3622,24 +3681,24 @@
         <v>66</v>
       </c>
       <c r="T44" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U44" s="4" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="V44" s="4" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="W44" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X44" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="Y44" s="18" t="s">
-        <v>137</v>
-      </c>
-      <c r="Z44" s="18" t="s">
+      <c r="X44" s="23" t="s">
+        <v>154</v>
+      </c>
+      <c r="Y44" s="23" t="s">
+        <v>154</v>
+      </c>
+      <c r="Z44" s="16" t="s">
         <v>53</v>
       </c>
       <c r="AB44" s="1"/>
@@ -3658,7 +3717,9 @@
         <v>23</v>
       </c>
       <c r="D45" s="1"/>
-      <c r="E45" s="1"/>
+      <c r="E45" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="F45" s="1"/>
       <c r="G45" s="1"/>
       <c r="H45" s="1"/>
@@ -3667,7 +3728,7 @@
         <v>72</v>
       </c>
       <c r="K45" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L45" s="4">
         <v>24</v>
@@ -3688,24 +3749,24 @@
         <v>66</v>
       </c>
       <c r="T45" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U45" s="4" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="V45" s="4" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="W45" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X45" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="Y45" s="18" t="s">
-        <v>137</v>
-      </c>
-      <c r="Z45" s="18" t="s">
+      <c r="X45" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="Y45" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="Z45" s="16" t="s">
         <v>53</v>
       </c>
       <c r="AB45" s="1"/>
@@ -3717,14 +3778,16 @@
       <c r="A46" s="1">
         <v>41</v>
       </c>
-      <c r="B46" s="1" t="s">
+      <c r="B46" s="10" t="s">
         <v>10</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D46" s="1"/>
-      <c r="E46" s="1"/>
+      <c r="E46" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="F46" s="1"/>
       <c r="G46" s="1"/>
       <c r="H46" s="1"/>
@@ -3733,7 +3796,7 @@
         <v>72</v>
       </c>
       <c r="K46" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L46" s="4">
         <v>24</v>
@@ -3754,22 +3817,22 @@
         <v>66</v>
       </c>
       <c r="T46" s="4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="U46" s="4" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="V46" s="4" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="W46" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X46" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="Y46" s="18" t="s">
-        <v>138</v>
+      <c r="X46" s="21" t="s">
+        <v>154</v>
+      </c>
+      <c r="Y46" s="21" t="s">
+        <v>155</v>
       </c>
       <c r="Z46" s="18" t="s">
         <v>136</v>
@@ -3790,7 +3853,9 @@
         <v>28</v>
       </c>
       <c r="D47" s="1"/>
-      <c r="E47" s="1"/>
+      <c r="E47" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="F47" s="1"/>
       <c r="G47" s="1"/>
       <c r="H47" s="1"/>
@@ -3799,7 +3864,7 @@
         <v>72</v>
       </c>
       <c r="K47" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L47" s="4">
         <v>24</v>
@@ -3820,22 +3885,22 @@
         <v>66</v>
       </c>
       <c r="T47" s="4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="U47" s="4" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="V47" s="4" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="W47" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X47" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="Y47" s="18" t="s">
-        <v>138</v>
+      <c r="X47" s="20" t="s">
+        <v>155</v>
+      </c>
+      <c r="Y47" s="20" t="s">
+        <v>155</v>
       </c>
       <c r="Z47" s="18" t="s">
         <v>53</v>
@@ -3856,7 +3921,9 @@
         <v>29</v>
       </c>
       <c r="D48" s="1"/>
-      <c r="E48" s="1"/>
+      <c r="E48" s="1" t="s">
+        <v>29</v>
+      </c>
       <c r="F48" s="1"/>
       <c r="G48" s="1"/>
       <c r="H48" s="1"/>
@@ -3865,7 +3932,7 @@
         <v>72</v>
       </c>
       <c r="K48" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L48" s="4">
         <v>24</v>
@@ -3886,22 +3953,22 @@
         <v>66</v>
       </c>
       <c r="T48" s="4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="U48" s="4" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="V48" s="4" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="W48" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X48" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="Y48" s="18" t="s">
-        <v>138</v>
+      <c r="X48" s="21" t="s">
+        <v>155</v>
+      </c>
+      <c r="Y48" s="21" t="s">
+        <v>155</v>
       </c>
       <c r="Z48" s="18" t="s">
         <v>53</v>
@@ -3922,7 +3989,9 @@
         <v>27</v>
       </c>
       <c r="D49" s="1"/>
-      <c r="E49" s="1"/>
+      <c r="E49" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="F49" s="1"/>
       <c r="G49" s="1"/>
       <c r="H49" s="1"/>
@@ -3931,7 +4000,7 @@
         <v>72</v>
       </c>
       <c r="K49" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L49" s="4">
         <v>24</v>
@@ -3952,22 +4021,22 @@
         <v>66</v>
       </c>
       <c r="T49" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U49" s="4" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="V49" s="4" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="W49" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="X49" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="Y49" s="18" t="s">
-        <v>138</v>
+      <c r="X49" s="20" t="s">
+        <v>155</v>
+      </c>
+      <c r="Y49" s="20" t="s">
+        <v>155</v>
       </c>
       <c r="Z49" s="18" t="s">
         <v>53</v>
@@ -3988,7 +4057,9 @@
         <v>54</v>
       </c>
       <c r="D50" s="1"/>
-      <c r="E50" s="1"/>
+      <c r="E50" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="F50" s="1"/>
       <c r="G50" s="1"/>
       <c r="H50" s="1"/>
@@ -3997,7 +4068,7 @@
         <v>72</v>
       </c>
       <c r="K50" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L50" s="4">
         <v>30</v>
@@ -4018,22 +4089,22 @@
         <v>66</v>
       </c>
       <c r="T50" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U50" s="4" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="V50" s="4" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="W50" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X50" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="Y50" s="18" t="s">
-        <v>138</v>
+      <c r="X50" s="21" t="s">
+        <v>155</v>
+      </c>
+      <c r="Y50" s="21" t="s">
+        <v>155</v>
       </c>
       <c r="Z50" s="18" t="s">
         <v>53</v>
@@ -4054,7 +4125,9 @@
         <v>19</v>
       </c>
       <c r="D51" s="1"/>
-      <c r="E51" s="1"/>
+      <c r="E51" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="F51" s="1"/>
       <c r="G51" s="1"/>
       <c r="H51" s="1"/>
@@ -4063,7 +4136,7 @@
         <v>72</v>
       </c>
       <c r="K51" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L51" s="4">
         <v>30</v>
@@ -4084,22 +4157,22 @@
         <v>66</v>
       </c>
       <c r="T51" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U51" s="4" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="V51" s="4" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="W51" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X51" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="Y51" s="18" t="s">
-        <v>138</v>
+      <c r="X51" s="20" t="s">
+        <v>155</v>
+      </c>
+      <c r="Y51" s="20" t="s">
+        <v>155</v>
       </c>
       <c r="Z51" s="18" t="s">
         <v>53</v>
@@ -4113,14 +4186,16 @@
       <c r="A52" s="1">
         <v>47</v>
       </c>
-      <c r="B52" s="1" t="s">
+      <c r="B52" s="12" t="s">
         <v>5</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D52" s="1"/>
-      <c r="E52" s="1"/>
+      <c r="E52" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="F52" s="1"/>
       <c r="G52" s="1"/>
       <c r="H52" s="1"/>
@@ -4129,7 +4204,7 @@
         <v>72</v>
       </c>
       <c r="K52" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L52" s="4">
         <v>30</v>
@@ -4150,22 +4225,22 @@
         <v>66</v>
       </c>
       <c r="T52" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U52" s="4" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="V52" s="4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="W52" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="X52" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="Y52" s="18" t="s">
-        <v>138</v>
+      <c r="X52" s="21" t="s">
+        <v>155</v>
+      </c>
+      <c r="Y52" s="21" t="s">
+        <v>155</v>
       </c>
       <c r="Z52" s="18" t="s">
         <v>53</v>
@@ -4186,7 +4261,9 @@
         <v>21</v>
       </c>
       <c r="D53" s="1"/>
-      <c r="E53" s="1"/>
+      <c r="E53" s="1" t="s">
+        <v>21</v>
+      </c>
       <c r="F53" s="1"/>
       <c r="G53" s="1"/>
       <c r="H53" s="1"/>
@@ -4195,7 +4272,7 @@
         <v>72</v>
       </c>
       <c r="K53" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L53" s="4">
         <v>30</v>
@@ -4216,22 +4293,22 @@
         <v>66</v>
       </c>
       <c r="T53" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U53" s="4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="V53" s="4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="W53" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X53" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="Y53" s="18" t="s">
-        <v>138</v>
+      <c r="X53" s="20" t="s">
+        <v>155</v>
+      </c>
+      <c r="Y53" s="20" t="s">
+        <v>155</v>
       </c>
       <c r="Z53" s="18" t="s">
         <v>53</v>
@@ -4252,7 +4329,9 @@
         <v>22</v>
       </c>
       <c r="D54" s="1"/>
-      <c r="E54" s="1"/>
+      <c r="E54" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="F54" s="1"/>
       <c r="G54" s="1"/>
       <c r="H54" s="1"/>
@@ -4261,7 +4340,7 @@
         <v>72</v>
       </c>
       <c r="K54" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L54" s="4">
         <v>30</v>
@@ -4282,22 +4361,22 @@
         <v>66</v>
       </c>
       <c r="T54" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U54" s="4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="V54" s="4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="W54" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X54" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="Y54" s="18" t="s">
-        <v>138</v>
+      <c r="X54" s="21" t="s">
+        <v>155</v>
+      </c>
+      <c r="Y54" s="21" t="s">
+        <v>155</v>
       </c>
       <c r="Z54" s="18" t="s">
         <v>53</v>
@@ -4311,14 +4390,16 @@
       <c r="A55" s="1">
         <v>50</v>
       </c>
-      <c r="B55" s="1" t="s">
+      <c r="B55" s="9" t="s">
         <v>8</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D55" s="1"/>
-      <c r="E55" s="1"/>
+      <c r="E55" s="1" t="s">
+        <v>30</v>
+      </c>
       <c r="F55" s="1"/>
       <c r="G55" s="1"/>
       <c r="H55" s="1"/>
@@ -4327,7 +4408,7 @@
         <v>72</v>
       </c>
       <c r="K55" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L55" s="4">
         <v>30</v>
@@ -4348,22 +4429,22 @@
         <v>66</v>
       </c>
       <c r="T55" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U55" s="4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="V55" s="4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="W55" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X55" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="Y55" s="18" t="s">
-        <v>138</v>
+      <c r="X55" s="20" t="s">
+        <v>155</v>
+      </c>
+      <c r="Y55" s="20" t="s">
+        <v>155</v>
       </c>
       <c r="Z55" s="18" t="s">
         <v>53</v>
@@ -4384,7 +4465,9 @@
         <v>23</v>
       </c>
       <c r="D56" s="1"/>
-      <c r="E56" s="1"/>
+      <c r="E56" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="F56" s="1"/>
       <c r="G56" s="1"/>
       <c r="H56" s="1"/>
@@ -4393,7 +4476,7 @@
         <v>72</v>
       </c>
       <c r="K56" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L56" s="4">
         <v>30</v>
@@ -4414,22 +4497,22 @@
         <v>66</v>
       </c>
       <c r="T56" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U56" s="4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="V56" s="4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="W56" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X56" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="Y56" s="18" t="s">
-        <v>138</v>
+      <c r="X56" s="21" t="s">
+        <v>155</v>
+      </c>
+      <c r="Y56" s="21" t="s">
+        <v>155</v>
       </c>
       <c r="Z56" s="18" t="s">
         <v>53</v>
@@ -4443,14 +4526,16 @@
       <c r="A57" s="1">
         <v>52</v>
       </c>
-      <c r="B57" s="1" t="s">
+      <c r="B57" s="10" t="s">
         <v>10</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D57" s="1"/>
-      <c r="E57" s="1"/>
+      <c r="E57" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="F57" s="1"/>
       <c r="G57" s="1"/>
       <c r="H57" s="1"/>
@@ -4459,7 +4544,7 @@
         <v>72</v>
       </c>
       <c r="K57" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L57" s="4">
         <v>30</v>
@@ -4480,22 +4565,22 @@
         <v>66</v>
       </c>
       <c r="T57" s="4" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="U57" s="4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="V57" s="4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="W57" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X57" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="Y57" s="18" t="s">
-        <v>139</v>
+      <c r="X57" s="20" t="s">
+        <v>155</v>
+      </c>
+      <c r="Y57" s="20" t="s">
+        <v>156</v>
       </c>
       <c r="Z57" s="18" t="s">
         <v>89</v>
@@ -4516,7 +4601,9 @@
         <v>25</v>
       </c>
       <c r="D58" s="1"/>
-      <c r="E58" s="1"/>
+      <c r="E58" s="1" t="s">
+        <v>25</v>
+      </c>
       <c r="F58" s="1"/>
       <c r="G58" s="1"/>
       <c r="H58" s="1"/>
@@ -4525,7 +4612,7 @@
         <v>72</v>
       </c>
       <c r="K58" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L58" s="4">
         <v>30</v>
@@ -4546,22 +4633,22 @@
         <v>66</v>
       </c>
       <c r="T58" s="4" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="U58" s="4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="V58" s="4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="W58" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X58" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="Y58" s="18" t="s">
-        <v>139</v>
+      <c r="X58" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y58" s="21" t="s">
+        <v>156</v>
       </c>
       <c r="Z58" s="18" t="s">
         <v>53</v>
@@ -4575,14 +4662,16 @@
       <c r="A59" s="1">
         <v>54</v>
       </c>
-      <c r="B59" s="1" t="s">
+      <c r="B59" s="15" t="s">
         <v>12</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D59" s="1"/>
-      <c r="E59" s="1"/>
+      <c r="E59" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="F59" s="1"/>
       <c r="G59" s="1"/>
       <c r="H59" s="1"/>
@@ -4591,7 +4680,7 @@
         <v>72</v>
       </c>
       <c r="K59" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L59" s="4">
         <v>30</v>
@@ -4612,22 +4701,22 @@
         <v>66</v>
       </c>
       <c r="T59" s="4" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="U59" s="4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="V59" s="4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="W59" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X59" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="Y59" s="18" t="s">
-        <v>139</v>
+      <c r="X59" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y59" s="20" t="s">
+        <v>156</v>
       </c>
       <c r="Z59" s="18" t="s">
         <v>53</v>
@@ -4641,14 +4730,16 @@
       <c r="A60" s="1">
         <v>55</v>
       </c>
-      <c r="B60" s="1" t="s">
+      <c r="B60" s="14" t="s">
         <v>13</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D60" s="1"/>
-      <c r="E60" s="1"/>
+      <c r="E60" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="F60" s="1"/>
       <c r="G60" s="1"/>
       <c r="H60" s="1"/>
@@ -4657,7 +4748,7 @@
         <v>72</v>
       </c>
       <c r="K60" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L60" s="4">
         <v>30</v>
@@ -4678,22 +4769,22 @@
         <v>66</v>
       </c>
       <c r="T60" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U60" s="4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="V60" s="4" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="W60" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="X60" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="Y60" s="18" t="s">
-        <v>139</v>
+      <c r="X60" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y60" s="21" t="s">
+        <v>156</v>
       </c>
       <c r="Z60" s="18" t="s">
         <v>53</v>
@@ -4714,7 +4805,9 @@
         <v>54</v>
       </c>
       <c r="D61" s="1"/>
-      <c r="E61" s="1"/>
+      <c r="E61" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="F61" s="1"/>
       <c r="G61" s="1"/>
       <c r="H61" s="1"/>
@@ -4723,7 +4816,7 @@
         <v>72</v>
       </c>
       <c r="K61" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L61" s="4">
         <v>36</v>
@@ -4744,22 +4837,22 @@
         <v>66</v>
       </c>
       <c r="T61" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U61" s="4" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="V61" s="4" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="W61" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X61" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="Y61" s="18" t="s">
-        <v>139</v>
+      <c r="X61" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y61" s="20" t="s">
+        <v>156</v>
       </c>
       <c r="Z61" s="18" t="s">
         <v>53</v>
@@ -4780,7 +4873,9 @@
         <v>19</v>
       </c>
       <c r="D62" s="1"/>
-      <c r="E62" s="1"/>
+      <c r="E62" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="F62" s="1"/>
       <c r="G62" s="1"/>
       <c r="H62" s="1"/>
@@ -4789,7 +4884,7 @@
         <v>72</v>
       </c>
       <c r="K62" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L62" s="4">
         <v>36</v>
@@ -4810,22 +4905,22 @@
         <v>66</v>
       </c>
       <c r="T62" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U62" s="4" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="V62" s="4" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="W62" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X62" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="Y62" s="18" t="s">
-        <v>139</v>
+      <c r="X62" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y62" s="21" t="s">
+        <v>156</v>
       </c>
       <c r="Z62" s="18" t="s">
         <v>53</v>
@@ -4839,14 +4934,16 @@
       <c r="A63" s="1">
         <v>58</v>
       </c>
-      <c r="B63" s="1" t="s">
+      <c r="B63" s="12" t="s">
         <v>5</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D63" s="1"/>
-      <c r="E63" s="1"/>
+      <c r="E63" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="F63" s="1"/>
       <c r="G63" s="1"/>
       <c r="H63" s="1"/>
@@ -4855,7 +4952,7 @@
         <v>72</v>
       </c>
       <c r="K63" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L63" s="4">
         <v>36</v>
@@ -4876,22 +4973,22 @@
         <v>65</v>
       </c>
       <c r="T63" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U63" s="4" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="V63" s="4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="W63" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="X63" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="Y63" s="18" t="s">
-        <v>139</v>
+      <c r="X63" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y63" s="20" t="s">
+        <v>156</v>
       </c>
       <c r="Z63" s="18" t="s">
         <v>53</v>
@@ -4912,7 +5009,9 @@
         <v>22</v>
       </c>
       <c r="D64" s="1"/>
-      <c r="E64" s="1"/>
+      <c r="E64" s="1" t="s">
+        <v>21</v>
+      </c>
       <c r="F64" s="1"/>
       <c r="G64" s="1"/>
       <c r="H64" s="1"/>
@@ -4921,7 +5020,7 @@
         <v>72</v>
       </c>
       <c r="K64" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L64" s="4">
         <v>36</v>
@@ -4942,22 +5041,22 @@
         <v>65</v>
       </c>
       <c r="T64" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U64" s="4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="V64" s="4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="W64" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X64" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="Y64" s="18" t="s">
-        <v>139</v>
+      <c r="X64" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y64" s="21" t="s">
+        <v>156</v>
       </c>
       <c r="Z64" s="18" t="s">
         <v>53</v>
@@ -4971,14 +5070,16 @@
       <c r="A65" s="1">
         <v>60</v>
       </c>
-      <c r="B65" s="1" t="s">
+      <c r="B65" s="9" t="s">
         <v>8</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D65" s="1"/>
-      <c r="E65" s="1"/>
+      <c r="E65" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="F65" s="1"/>
       <c r="G65" s="1"/>
       <c r="H65" s="1"/>
@@ -4987,7 +5088,7 @@
         <v>72</v>
       </c>
       <c r="K65" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L65" s="4">
         <v>36</v>
@@ -5008,22 +5109,22 @@
         <v>66</v>
       </c>
       <c r="T65" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U65" s="4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="V65" s="4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="W65" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X65" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="Y65" s="18" t="s">
-        <v>139</v>
+      <c r="X65" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y65" s="20" t="s">
+        <v>156</v>
       </c>
       <c r="Z65" s="18" t="s">
         <v>53</v>
@@ -5044,7 +5145,9 @@
         <v>23</v>
       </c>
       <c r="D66" s="1"/>
-      <c r="E66" s="1"/>
+      <c r="E66" s="1" t="s">
+        <v>30</v>
+      </c>
       <c r="F66" s="1"/>
       <c r="G66" s="1"/>
       <c r="H66" s="1"/>
@@ -5053,7 +5156,7 @@
         <v>72</v>
       </c>
       <c r="K66" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L66" s="4">
         <v>36</v>
@@ -5074,22 +5177,22 @@
         <v>66</v>
       </c>
       <c r="T66" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U66" s="4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="V66" s="4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="W66" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X66" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="Y66" s="18" t="s">
-        <v>139</v>
+      <c r="X66" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y66" s="21" t="s">
+        <v>156</v>
       </c>
       <c r="Z66" s="18" t="s">
         <v>53</v>
@@ -5119,7 +5222,7 @@
         <v>72</v>
       </c>
       <c r="K67" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L67" s="4">
         <v>36</v>
@@ -5140,22 +5243,22 @@
         <v>66</v>
       </c>
       <c r="T67" s="4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="U67" s="4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="V67" s="4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="W67" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X67" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="Y67" s="18" t="s">
-        <v>140</v>
+      <c r="X67" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y67" s="20" t="s">
+        <v>157</v>
       </c>
       <c r="Z67" s="18" t="s">
         <v>136</v>
@@ -5185,7 +5288,7 @@
         <v>72</v>
       </c>
       <c r="K68" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L68" s="4">
         <v>36</v>
@@ -5206,22 +5309,22 @@
         <v>66</v>
       </c>
       <c r="T68" s="4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="U68" s="4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="V68" s="4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="W68" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X68" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="Y68" s="18" t="s">
-        <v>140</v>
+      <c r="X68" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y68" s="21" t="s">
+        <v>157</v>
       </c>
       <c r="Z68" s="18" t="s">
         <v>53</v>
@@ -5251,7 +5354,7 @@
         <v>72</v>
       </c>
       <c r="K69" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L69" s="4">
         <v>36</v>
@@ -5272,22 +5375,22 @@
         <v>66</v>
       </c>
       <c r="T69" s="4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="U69" s="4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="V69" s="4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="W69" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X69" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="Y69" s="18" t="s">
-        <v>140</v>
+      <c r="X69" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y69" s="20" t="s">
+        <v>157</v>
       </c>
       <c r="Z69" s="18" t="s">
         <v>53</v>
@@ -5301,7 +5404,7 @@
       <c r="A70" s="1">
         <v>65</v>
       </c>
-      <c r="B70" s="1" t="s">
+      <c r="B70" s="14" t="s">
         <v>13</v>
       </c>
       <c r="C70" s="1" t="s">
@@ -5317,7 +5420,7 @@
         <v>72</v>
       </c>
       <c r="K70" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L70" s="4">
         <v>36</v>
@@ -5338,22 +5441,22 @@
         <v>66</v>
       </c>
       <c r="T70" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U70" s="4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="V70" s="4" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="W70" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="X70" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="Y70" s="18" t="s">
-        <v>140</v>
+      <c r="X70" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y70" s="21" t="s">
+        <v>157</v>
       </c>
       <c r="Z70" s="18" t="s">
         <v>53</v>
@@ -5383,7 +5486,7 @@
         <v>72</v>
       </c>
       <c r="K71" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L71" s="4">
         <v>42</v>
@@ -5404,22 +5507,22 @@
         <v>66</v>
       </c>
       <c r="T71" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U71" s="4" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="V71" s="4" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="W71" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X71" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="Y71" s="18" t="s">
-        <v>140</v>
+      <c r="X71" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y71" s="20" t="s">
+        <v>157</v>
       </c>
       <c r="Z71" s="18" t="s">
         <v>53</v>
@@ -5449,7 +5552,7 @@
         <v>72</v>
       </c>
       <c r="K72" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L72" s="4">
         <v>42</v>
@@ -5470,22 +5573,22 @@
         <v>66</v>
       </c>
       <c r="T72" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U72" s="4" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="V72" s="4" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="W72" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X72" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="Y72" s="18" t="s">
-        <v>140</v>
+      <c r="X72" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y72" s="21" t="s">
+        <v>157</v>
       </c>
       <c r="Z72" s="18" t="s">
         <v>53</v>
@@ -5515,7 +5618,7 @@
         <v>72</v>
       </c>
       <c r="K73" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L73" s="4">
         <v>42</v>
@@ -5536,22 +5639,22 @@
         <v>66</v>
       </c>
       <c r="T73" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U73" s="4" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="V73" s="4" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="W73" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="X73" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="Y73" s="18" t="s">
-        <v>140</v>
+      <c r="X73" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y73" s="20" t="s">
+        <v>157</v>
       </c>
       <c r="Z73" s="18" t="s">
         <v>53</v>
@@ -5581,7 +5684,7 @@
         <v>72</v>
       </c>
       <c r="K74" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L74" s="4">
         <v>42</v>
@@ -5602,22 +5705,22 @@
         <v>66</v>
       </c>
       <c r="T74" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U74" s="4" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="V74" s="4" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="W74" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X74" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="Y74" s="18" t="s">
-        <v>140</v>
+      <c r="X74" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y74" s="21" t="s">
+        <v>157</v>
       </c>
       <c r="Z74" s="18" t="s">
         <v>53</v>
@@ -5647,7 +5750,7 @@
         <v>72</v>
       </c>
       <c r="K75" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L75" s="4">
         <v>42</v>
@@ -5668,22 +5771,22 @@
         <v>66</v>
       </c>
       <c r="T75" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U75" s="4" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="V75" s="4" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="W75" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X75" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="Y75" s="18" t="s">
-        <v>140</v>
+      <c r="X75" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y75" s="20" t="s">
+        <v>157</v>
       </c>
       <c r="Z75" s="18" t="s">
         <v>53</v>
@@ -5713,7 +5816,7 @@
         <v>72</v>
       </c>
       <c r="K76" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L76" s="4">
         <v>42</v>
@@ -5734,22 +5837,22 @@
         <v>66</v>
       </c>
       <c r="T76" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U76" s="4" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="V76" s="4" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="W76" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X76" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="Y76" s="18" t="s">
-        <v>140</v>
+      <c r="X76" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y76" s="21" t="s">
+        <v>157</v>
       </c>
       <c r="Z76" s="18" t="s">
         <v>53</v>
@@ -5779,7 +5882,7 @@
         <v>72</v>
       </c>
       <c r="K77" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L77" s="4">
         <v>42</v>
@@ -5800,22 +5903,22 @@
         <v>66</v>
       </c>
       <c r="T77" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U77" s="4" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="V77" s="4" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="W77" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X77" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="Y77" s="18" t="s">
-        <v>140</v>
+      <c r="X77" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y77" s="20" t="s">
+        <v>157</v>
       </c>
       <c r="Z77" s="18" t="s">
         <v>53</v>
@@ -5845,7 +5948,7 @@
         <v>72</v>
       </c>
       <c r="K78" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L78" s="4">
         <v>42</v>
@@ -5866,22 +5969,22 @@
         <v>66</v>
       </c>
       <c r="T78" s="4" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="U78" s="4" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="V78" s="4" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="W78" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X78" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="Y78" s="18" t="s">
-        <v>141</v>
+      <c r="X78" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y78" s="21" t="s">
+        <v>156</v>
       </c>
       <c r="Z78" s="18" t="s">
         <v>89</v>
@@ -5911,7 +6014,7 @@
         <v>72</v>
       </c>
       <c r="K79" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L79" s="4">
         <v>42</v>
@@ -5932,22 +6035,22 @@
         <v>66</v>
       </c>
       <c r="T79" s="4" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="U79" s="4" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="V79" s="4" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="W79" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X79" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="Y79" s="18" t="s">
-        <v>141</v>
+      <c r="X79" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y79" s="20" t="s">
+        <v>156</v>
       </c>
       <c r="Z79" s="18" t="s">
         <v>53</v>
@@ -5977,7 +6080,7 @@
         <v>72</v>
       </c>
       <c r="K80" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L80" s="4">
         <v>42</v>
@@ -5998,22 +6101,22 @@
         <v>66</v>
       </c>
       <c r="T80" s="4" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="U80" s="4" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="V80" s="4" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="W80" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X80" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="Y80" s="18" t="s">
-        <v>141</v>
+      <c r="X80" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y80" s="21" t="s">
+        <v>156</v>
       </c>
       <c r="Z80" s="18" t="s">
         <v>53</v>
@@ -6043,7 +6146,7 @@
         <v>72</v>
       </c>
       <c r="K81" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L81" s="4">
         <v>42</v>
@@ -6064,22 +6167,22 @@
         <v>66</v>
       </c>
       <c r="T81" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U81" s="4" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="V81" s="4" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="W81" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="X81" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="Y81" s="18" t="s">
-        <v>141</v>
+      <c r="X81" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y81" s="20" t="s">
+        <v>156</v>
       </c>
       <c r="Z81" s="18" t="s">
         <v>53</v>
@@ -6109,7 +6212,7 @@
         <v>72</v>
       </c>
       <c r="K82" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L82" s="4">
         <v>48</v>
@@ -6130,22 +6233,22 @@
         <v>66</v>
       </c>
       <c r="T82" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U82" s="4" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="V82" s="4" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="W82" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X82" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="Y82" s="18" t="s">
-        <v>141</v>
+      <c r="X82" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y82" s="21" t="s">
+        <v>156</v>
       </c>
       <c r="Z82" s="18" t="s">
         <v>53</v>
@@ -6175,7 +6278,7 @@
         <v>72</v>
       </c>
       <c r="K83" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L83" s="4">
         <v>48</v>
@@ -6196,22 +6299,22 @@
         <v>66</v>
       </c>
       <c r="T83" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U83" s="4" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="V83" s="4" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="W83" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X83" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="Y83" s="18" t="s">
-        <v>141</v>
+      <c r="X83" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y83" s="20" t="s">
+        <v>156</v>
       </c>
       <c r="Z83" s="18" t="s">
         <v>53</v>
@@ -6241,7 +6344,7 @@
         <v>72</v>
       </c>
       <c r="K84" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L84" s="4">
         <v>48</v>
@@ -6262,22 +6365,22 @@
         <v>65</v>
       </c>
       <c r="T84" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U84" s="4" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="V84" s="4" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="W84" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="X84" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="Y84" s="18" t="s">
-        <v>141</v>
+      <c r="X84" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y84" s="21" t="s">
+        <v>156</v>
       </c>
       <c r="Z84" s="18" t="s">
         <v>53</v>
@@ -6307,7 +6410,7 @@
         <v>72</v>
       </c>
       <c r="K85" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L85" s="4">
         <v>48</v>
@@ -6328,22 +6431,22 @@
         <v>65</v>
       </c>
       <c r="T85" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U85" s="4" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="V85" s="4" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="W85" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X85" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="Y85" s="18" t="s">
-        <v>141</v>
+      <c r="X85" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y85" s="20" t="s">
+        <v>156</v>
       </c>
       <c r="Z85" s="18" t="s">
         <v>53</v>
@@ -6373,7 +6476,7 @@
         <v>72</v>
       </c>
       <c r="K86" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L86" s="4">
         <v>48</v>
@@ -6394,22 +6497,22 @@
         <v>66</v>
       </c>
       <c r="T86" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U86" s="4" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="V86" s="4" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="W86" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X86" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="Y86" s="18" t="s">
-        <v>141</v>
+      <c r="X86" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y86" s="21" t="s">
+        <v>156</v>
       </c>
       <c r="Z86" s="18" t="s">
         <v>53</v>
@@ -6439,7 +6542,7 @@
         <v>72</v>
       </c>
       <c r="K87" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L87" s="4">
         <v>48</v>
@@ -6460,22 +6563,22 @@
         <v>66</v>
       </c>
       <c r="T87" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U87" s="4" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="V87" s="4" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="W87" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X87" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="Y87" s="18" t="s">
-        <v>141</v>
+      <c r="X87" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y87" s="20" t="s">
+        <v>156</v>
       </c>
       <c r="Z87" s="18" t="s">
         <v>53</v>
@@ -6505,7 +6608,7 @@
         <v>72</v>
       </c>
       <c r="K88" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L88" s="4">
         <v>48</v>
@@ -6526,22 +6629,22 @@
         <v>66</v>
       </c>
       <c r="T88" s="4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="U88" s="4" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="V88" s="4" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="W88" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X88" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="Y88" s="18" t="s">
-        <v>142</v>
+      <c r="X88" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y88" s="21" t="s">
+        <v>157</v>
       </c>
       <c r="Z88" s="18" t="s">
         <v>136</v>
@@ -6571,7 +6674,7 @@
         <v>72</v>
       </c>
       <c r="K89" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L89" s="4">
         <v>48</v>
@@ -6592,22 +6695,22 @@
         <v>66</v>
       </c>
       <c r="T89" s="4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="U89" s="4" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="V89" s="4" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="W89" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X89" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="Y89" s="18" t="s">
-        <v>142</v>
+      <c r="X89" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y89" s="20" t="s">
+        <v>157</v>
       </c>
       <c r="Z89" s="18" t="s">
         <v>53</v>
@@ -6637,7 +6740,7 @@
         <v>72</v>
       </c>
       <c r="K90" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L90" s="4">
         <v>48</v>
@@ -6658,22 +6761,22 @@
         <v>66</v>
       </c>
       <c r="T90" s="4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="U90" s="4" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="V90" s="4" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="W90" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X90" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="Y90" s="18" t="s">
-        <v>142</v>
+      <c r="X90" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y90" s="21" t="s">
+        <v>157</v>
       </c>
       <c r="Z90" s="18" t="s">
         <v>53</v>
@@ -6703,7 +6806,7 @@
         <v>72</v>
       </c>
       <c r="K91" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L91" s="4">
         <v>48</v>
@@ -6724,22 +6827,22 @@
         <v>66</v>
       </c>
       <c r="T91" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U91" s="4" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="V91" s="4" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="W91" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="X91" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="Y91" s="18" t="s">
-        <v>142</v>
+      <c r="X91" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y91" s="20" t="s">
+        <v>157</v>
       </c>
       <c r="Z91" s="18" t="s">
         <v>53</v>
@@ -6769,7 +6872,7 @@
         <v>72</v>
       </c>
       <c r="K92" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L92" s="4">
         <v>54</v>
@@ -6790,22 +6893,22 @@
         <v>66</v>
       </c>
       <c r="T92" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U92" s="4" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="V92" s="4" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="W92" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X92" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="Y92" s="18" t="s">
-        <v>142</v>
+      <c r="X92" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y92" s="21" t="s">
+        <v>157</v>
       </c>
       <c r="Z92" s="18" t="s">
         <v>53</v>
@@ -6835,7 +6938,7 @@
         <v>72</v>
       </c>
       <c r="K93" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L93" s="4">
         <v>54</v>
@@ -6856,22 +6959,22 @@
         <v>66</v>
       </c>
       <c r="T93" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U93" s="4" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="V93" s="4" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="W93" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X93" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="Y93" s="18" t="s">
-        <v>142</v>
+      <c r="X93" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y93" s="20" t="s">
+        <v>157</v>
       </c>
       <c r="Z93" s="18" t="s">
         <v>53</v>
@@ -6901,7 +7004,7 @@
         <v>72</v>
       </c>
       <c r="K94" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L94" s="4">
         <v>54</v>
@@ -6922,22 +7025,22 @@
         <v>66</v>
       </c>
       <c r="T94" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U94" s="4" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="V94" s="4" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="W94" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="X94" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="Y94" s="18" t="s">
-        <v>142</v>
+      <c r="X94" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y94" s="21" t="s">
+        <v>157</v>
       </c>
       <c r="Z94" s="18" t="s">
         <v>53</v>
@@ -6961,7 +7064,7 @@
         <v>72</v>
       </c>
       <c r="K95" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L95" s="4">
         <v>54</v>
@@ -6979,22 +7082,22 @@
         <v>66</v>
       </c>
       <c r="T95" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U95" s="4" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="V95" s="4" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="W95" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X95" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="Y95" s="18" t="s">
-        <v>142</v>
+      <c r="X95" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y95" s="20" t="s">
+        <v>157</v>
       </c>
       <c r="Z95" s="18" t="s">
         <v>53</v>
@@ -7014,7 +7117,7 @@
         <v>72</v>
       </c>
       <c r="K96" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L96" s="4">
         <v>54</v>
@@ -7032,22 +7135,22 @@
         <v>66</v>
       </c>
       <c r="T96" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U96" s="4" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="V96" s="4" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="W96" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X96" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="Y96" s="18" t="s">
-        <v>142</v>
+      <c r="X96" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y96" s="21" t="s">
+        <v>157</v>
       </c>
       <c r="Z96" s="18" t="s">
         <v>53</v>
@@ -7067,7 +7170,7 @@
         <v>72</v>
       </c>
       <c r="K97" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L97" s="4">
         <v>54</v>
@@ -7085,22 +7188,22 @@
         <v>66</v>
       </c>
       <c r="T97" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U97" s="4" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="V97" s="4" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="W97" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X97" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="Y97" s="18" t="s">
-        <v>142</v>
+      <c r="X97" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y97" s="20" t="s">
+        <v>157</v>
       </c>
       <c r="Z97" s="18" t="s">
         <v>53</v>
@@ -7120,7 +7223,7 @@
         <v>72</v>
       </c>
       <c r="K98" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L98" s="4">
         <v>54</v>
@@ -7138,22 +7241,22 @@
         <v>66</v>
       </c>
       <c r="T98" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U98" s="4" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="V98" s="4" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="W98" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X98" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="Y98" s="18" t="s">
-        <v>142</v>
+      <c r="X98" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y98" s="21" t="s">
+        <v>157</v>
       </c>
       <c r="Z98" s="18" t="s">
         <v>53</v>
@@ -7173,7 +7276,7 @@
         <v>72</v>
       </c>
       <c r="K99" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L99" s="4">
         <v>54</v>
@@ -7191,22 +7294,22 @@
         <v>66</v>
       </c>
       <c r="T99" s="4" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="U99" s="4" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="V99" s="4" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="W99" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X99" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="Y99" s="18" t="s">
-        <v>143</v>
+      <c r="X99" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y99" s="20" t="s">
+        <v>156</v>
       </c>
       <c r="Z99" s="18" t="s">
         <v>89</v>
@@ -7226,7 +7329,7 @@
         <v>72</v>
       </c>
       <c r="K100" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L100" s="4">
         <v>54</v>
@@ -7244,22 +7347,22 @@
         <v>66</v>
       </c>
       <c r="T100" s="4" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="U100" s="4" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="V100" s="4" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="W100" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X100" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="Y100" s="18" t="s">
-        <v>143</v>
+      <c r="X100" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y100" s="21" t="s">
+        <v>156</v>
       </c>
       <c r="Z100" s="18" t="s">
         <v>53</v>
@@ -7279,7 +7382,7 @@
         <v>72</v>
       </c>
       <c r="K101" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L101" s="4">
         <v>54</v>
@@ -7297,22 +7400,22 @@
         <v>66</v>
       </c>
       <c r="T101" s="4" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="U101" s="4" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="V101" s="4" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="W101" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X101" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="Y101" s="18" t="s">
-        <v>143</v>
+      <c r="X101" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y101" s="20" t="s">
+        <v>156</v>
       </c>
       <c r="Z101" s="18" t="s">
         <v>53</v>
@@ -7332,7 +7435,7 @@
         <v>72</v>
       </c>
       <c r="K102" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L102" s="4">
         <v>54</v>
@@ -7350,22 +7453,22 @@
         <v>66</v>
       </c>
       <c r="T102" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U102" s="4" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="V102" s="4" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="W102" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="X102" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="Y102" s="18" t="s">
-        <v>143</v>
+      <c r="X102" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y102" s="21" t="s">
+        <v>156</v>
       </c>
       <c r="Z102" s="18" t="s">
         <v>53</v>
@@ -7385,7 +7488,7 @@
         <v>72</v>
       </c>
       <c r="K103" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L103" s="4">
         <v>60</v>
@@ -7403,22 +7506,22 @@
         <v>66</v>
       </c>
       <c r="T103" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U103" s="4" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="V103" s="4" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="W103" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X103" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="Y103" s="18" t="s">
-        <v>143</v>
+      <c r="X103" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y103" s="20" t="s">
+        <v>156</v>
       </c>
       <c r="Z103" s="18" t="s">
         <v>53</v>
@@ -7438,7 +7541,7 @@
         <v>72</v>
       </c>
       <c r="K104" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L104" s="4">
         <v>60</v>
@@ -7456,22 +7559,22 @@
         <v>66</v>
       </c>
       <c r="T104" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U104" s="4" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="V104" s="4" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="W104" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X104" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="Y104" s="18" t="s">
-        <v>143</v>
+      <c r="X104" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y104" s="21" t="s">
+        <v>156</v>
       </c>
       <c r="Z104" s="18" t="s">
         <v>53</v>
@@ -7491,7 +7594,7 @@
         <v>72</v>
       </c>
       <c r="K105" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L105" s="4">
         <v>60</v>
@@ -7509,22 +7612,22 @@
         <v>65</v>
       </c>
       <c r="T105" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U105" s="4" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="V105" s="4" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="W105" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="X105" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="Y105" s="18" t="s">
-        <v>143</v>
+      <c r="X105" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y105" s="20" t="s">
+        <v>156</v>
       </c>
       <c r="Z105" s="18" t="s">
         <v>53</v>
@@ -7544,7 +7647,7 @@
         <v>72</v>
       </c>
       <c r="K106" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L106" s="4">
         <v>60</v>
@@ -7562,22 +7665,22 @@
         <v>65</v>
       </c>
       <c r="T106" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U106" s="4" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="V106" s="4" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="W106" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X106" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="Y106" s="18" t="s">
-        <v>143</v>
+      <c r="X106" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y106" s="21" t="s">
+        <v>156</v>
       </c>
       <c r="Z106" s="18" t="s">
         <v>53</v>
@@ -7597,7 +7700,7 @@
         <v>72</v>
       </c>
       <c r="K107" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L107" s="4">
         <v>60</v>
@@ -7615,22 +7718,22 @@
         <v>66</v>
       </c>
       <c r="T107" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U107" s="4" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="V107" s="4" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="W107" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X107" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="Y107" s="18" t="s">
-        <v>143</v>
+      <c r="X107" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y107" s="20" t="s">
+        <v>156</v>
       </c>
       <c r="Z107" s="18" t="s">
         <v>53</v>
@@ -7650,7 +7753,7 @@
         <v>72</v>
       </c>
       <c r="K108" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L108" s="4">
         <v>60</v>
@@ -7668,22 +7771,22 @@
         <v>66</v>
       </c>
       <c r="T108" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U108" s="4" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="V108" s="4" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="W108" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X108" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="Y108" s="18" t="s">
-        <v>143</v>
+      <c r="X108" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y108" s="21" t="s">
+        <v>156</v>
       </c>
       <c r="Z108" s="18" t="s">
         <v>53</v>
@@ -7703,7 +7806,7 @@
         <v>72</v>
       </c>
       <c r="K109" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L109" s="4">
         <v>60</v>
@@ -7721,22 +7824,22 @@
         <v>66</v>
       </c>
       <c r="T109" s="4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="U109" s="4" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="V109" s="4" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="W109" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X109" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="Y109" s="18" t="s">
-        <v>144</v>
+      <c r="X109" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y109" s="20" t="s">
+        <v>157</v>
       </c>
       <c r="Z109" s="18" t="s">
         <v>136</v>
@@ -7756,7 +7859,7 @@
         <v>72</v>
       </c>
       <c r="K110" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L110" s="4">
         <v>60</v>
@@ -7774,22 +7877,22 @@
         <v>66</v>
       </c>
       <c r="T110" s="4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="U110" s="4" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="V110" s="4" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="W110" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X110" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="Y110" s="18" t="s">
-        <v>144</v>
+      <c r="X110" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y110" s="21" t="s">
+        <v>157</v>
       </c>
       <c r="Z110" s="18" t="s">
         <v>53</v>
@@ -7809,7 +7912,7 @@
         <v>72</v>
       </c>
       <c r="K111" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L111" s="4">
         <v>60</v>
@@ -7827,22 +7930,22 @@
         <v>66</v>
       </c>
       <c r="T111" s="4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="U111" s="4" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="V111" s="4" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="W111" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X111" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="Y111" s="18" t="s">
-        <v>144</v>
+      <c r="X111" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y111" s="20" t="s">
+        <v>157</v>
       </c>
       <c r="Z111" s="18" t="s">
         <v>53</v>
@@ -7862,7 +7965,7 @@
         <v>72</v>
       </c>
       <c r="K112" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L112" s="4">
         <v>60</v>
@@ -7880,22 +7983,22 @@
         <v>66</v>
       </c>
       <c r="T112" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U112" s="4" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="V112" s="4" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="W112" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="X112" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="Y112" s="18" t="s">
-        <v>144</v>
+      <c r="X112" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y112" s="21" t="s">
+        <v>157</v>
       </c>
       <c r="Z112" s="18" t="s">
         <v>53</v>
@@ -7915,7 +8018,7 @@
         <v>72</v>
       </c>
       <c r="K113" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L113" s="4">
         <v>66</v>
@@ -7933,22 +8036,22 @@
         <v>66</v>
       </c>
       <c r="T113" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U113" s="4" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="V113" s="4" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="W113" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X113" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="Y113" s="18" t="s">
-        <v>144</v>
+      <c r="X113" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y113" s="20" t="s">
+        <v>157</v>
       </c>
       <c r="Z113" s="18" t="s">
         <v>53</v>
@@ -7968,7 +8071,7 @@
         <v>72</v>
       </c>
       <c r="K114" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L114" s="4">
         <v>66</v>
@@ -7986,22 +8089,22 @@
         <v>66</v>
       </c>
       <c r="T114" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U114" s="4" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="V114" s="4" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="W114" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X114" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="Y114" s="18" t="s">
-        <v>144</v>
+      <c r="X114" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y114" s="21" t="s">
+        <v>157</v>
       </c>
       <c r="Z114" s="18" t="s">
         <v>53</v>
@@ -8021,7 +8124,7 @@
         <v>72</v>
       </c>
       <c r="K115" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L115" s="4">
         <v>66</v>
@@ -8039,22 +8142,22 @@
         <v>66</v>
       </c>
       <c r="T115" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U115" s="4" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="V115" s="4" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="W115" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="X115" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="Y115" s="18" t="s">
-        <v>144</v>
+      <c r="X115" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y115" s="20" t="s">
+        <v>157</v>
       </c>
       <c r="Z115" s="18" t="s">
         <v>53</v>
@@ -8074,7 +8177,7 @@
         <v>72</v>
       </c>
       <c r="K116" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L116" s="4">
         <v>66</v>
@@ -8092,22 +8195,22 @@
         <v>66</v>
       </c>
       <c r="T116" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U116" s="4" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="V116" s="4" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="W116" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X116" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="Y116" s="18" t="s">
-        <v>144</v>
+      <c r="X116" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y116" s="21" t="s">
+        <v>157</v>
       </c>
       <c r="Z116" s="18" t="s">
         <v>53</v>
@@ -8127,7 +8230,7 @@
         <v>72</v>
       </c>
       <c r="K117" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L117" s="4">
         <v>66</v>
@@ -8145,22 +8248,22 @@
         <v>66</v>
       </c>
       <c r="T117" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U117" s="4" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="V117" s="4" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="W117" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X117" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="Y117" s="18" t="s">
-        <v>144</v>
+      <c r="X117" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y117" s="20" t="s">
+        <v>157</v>
       </c>
       <c r="Z117" s="18" t="s">
         <v>53</v>
@@ -8180,7 +8283,7 @@
         <v>72</v>
       </c>
       <c r="K118" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L118" s="4">
         <v>66</v>
@@ -8198,22 +8301,22 @@
         <v>66</v>
       </c>
       <c r="T118" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U118" s="4" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="V118" s="4" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="W118" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X118" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="Y118" s="18" t="s">
-        <v>144</v>
+      <c r="X118" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y118" s="21" t="s">
+        <v>157</v>
       </c>
       <c r="Z118" s="18" t="s">
         <v>53</v>
@@ -8233,7 +8336,7 @@
         <v>72</v>
       </c>
       <c r="K119" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L119" s="4">
         <v>66</v>
@@ -8251,22 +8354,22 @@
         <v>66</v>
       </c>
       <c r="T119" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U119" s="4" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="V119" s="4" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="W119" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X119" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="Y119" s="18" t="s">
-        <v>144</v>
+      <c r="X119" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y119" s="20" t="s">
+        <v>157</v>
       </c>
       <c r="Z119" s="18" t="s">
         <v>53</v>
@@ -8286,7 +8389,7 @@
         <v>72</v>
       </c>
       <c r="K120" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L120" s="4">
         <v>66</v>
@@ -8304,22 +8407,22 @@
         <v>66</v>
       </c>
       <c r="T120" s="4" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="U120" s="4" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="V120" s="4" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="W120" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X120" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="Y120" s="18" t="s">
-        <v>145</v>
+      <c r="X120" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y120" s="21" t="s">
+        <v>156</v>
       </c>
       <c r="Z120" s="18" t="s">
         <v>89</v>
@@ -8339,7 +8442,7 @@
         <v>72</v>
       </c>
       <c r="K121" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L121" s="4">
         <v>66</v>
@@ -8357,22 +8460,22 @@
         <v>66</v>
       </c>
       <c r="T121" s="4" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="U121" s="4" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="V121" s="4" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="W121" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X121" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="Y121" s="18" t="s">
-        <v>145</v>
+      <c r="X121" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y121" s="20" t="s">
+        <v>156</v>
       </c>
       <c r="Z121" s="18" t="s">
         <v>53</v>
@@ -8392,7 +8495,7 @@
         <v>72</v>
       </c>
       <c r="K122" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L122" s="4">
         <v>66</v>
@@ -8410,22 +8513,22 @@
         <v>66</v>
       </c>
       <c r="T122" s="4" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="U122" s="4" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="V122" s="4" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="W122" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X122" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="Y122" s="18" t="s">
-        <v>145</v>
+      <c r="X122" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y122" s="21" t="s">
+        <v>156</v>
       </c>
       <c r="Z122" s="18" t="s">
         <v>53</v>
@@ -8445,7 +8548,7 @@
         <v>72</v>
       </c>
       <c r="K123" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L123" s="4">
         <v>66</v>
@@ -8463,22 +8566,22 @@
         <v>66</v>
       </c>
       <c r="T123" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U123" s="4" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="V123" s="4" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="W123" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="X123" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="Y123" s="18" t="s">
-        <v>145</v>
+      <c r="X123" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y123" s="20" t="s">
+        <v>156</v>
       </c>
       <c r="Z123" s="18" t="s">
         <v>53</v>
@@ -8498,7 +8601,7 @@
         <v>72</v>
       </c>
       <c r="K124" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L124" s="4">
         <v>72</v>
@@ -8516,22 +8619,22 @@
         <v>66</v>
       </c>
       <c r="T124" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U124" s="4" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="V124" s="4" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="W124" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X124" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="Y124" s="18" t="s">
-        <v>145</v>
+      <c r="X124" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y124" s="21" t="s">
+        <v>156</v>
       </c>
       <c r="Z124" s="18" t="s">
         <v>53</v>
@@ -8551,7 +8654,7 @@
         <v>72</v>
       </c>
       <c r="K125" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L125" s="4">
         <v>72</v>
@@ -8569,22 +8672,22 @@
         <v>66</v>
       </c>
       <c r="T125" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U125" s="4" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="V125" s="4" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="W125" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X125" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="Y125" s="18" t="s">
-        <v>145</v>
+      <c r="X125" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y125" s="20" t="s">
+        <v>156</v>
       </c>
       <c r="Z125" s="18" t="s">
         <v>53</v>
@@ -8604,7 +8707,7 @@
         <v>72</v>
       </c>
       <c r="K126" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L126" s="4">
         <v>72</v>
@@ -8622,22 +8725,22 @@
         <v>65</v>
       </c>
       <c r="T126" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U126" s="4" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="V126" s="4" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="W126" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="X126" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="Y126" s="18" t="s">
-        <v>145</v>
+      <c r="X126" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y126" s="21" t="s">
+        <v>156</v>
       </c>
       <c r="Z126" s="18" t="s">
         <v>53</v>
@@ -8657,7 +8760,7 @@
         <v>72</v>
       </c>
       <c r="K127" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L127" s="4">
         <v>72</v>
@@ -8675,22 +8778,22 @@
         <v>65</v>
       </c>
       <c r="T127" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U127" s="4" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="V127" s="4" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="W127" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X127" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="Y127" s="18" t="s">
-        <v>145</v>
+      <c r="X127" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y127" s="20" t="s">
+        <v>156</v>
       </c>
       <c r="Z127" s="18" t="s">
         <v>53</v>
@@ -8710,7 +8813,7 @@
         <v>72</v>
       </c>
       <c r="K128" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L128" s="4">
         <v>72</v>
@@ -8728,22 +8831,22 @@
         <v>66</v>
       </c>
       <c r="T128" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U128" s="4" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="V128" s="4" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="W128" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X128" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="Y128" s="18" t="s">
-        <v>145</v>
+      <c r="X128" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y128" s="21" t="s">
+        <v>156</v>
       </c>
       <c r="Z128" s="18" t="s">
         <v>53</v>
@@ -8763,7 +8866,7 @@
         <v>72</v>
       </c>
       <c r="K129" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L129" s="4">
         <v>72</v>
@@ -8781,22 +8884,22 @@
         <v>66</v>
       </c>
       <c r="T129" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U129" s="4" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="V129" s="4" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="W129" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X129" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="Y129" s="18" t="s">
-        <v>145</v>
+      <c r="X129" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y129" s="20" t="s">
+        <v>156</v>
       </c>
       <c r="Z129" s="18" t="s">
         <v>53</v>
@@ -8816,7 +8919,7 @@
         <v>72</v>
       </c>
       <c r="K130" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L130" s="4">
         <v>72</v>
@@ -8834,22 +8937,22 @@
         <v>66</v>
       </c>
       <c r="T130" s="4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="U130" s="4" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="V130" s="4" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="W130" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X130" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="Y130" s="18" t="s">
-        <v>146</v>
+      <c r="X130" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y130" s="21" t="s">
+        <v>157</v>
       </c>
       <c r="Z130" s="18" t="s">
         <v>136</v>
@@ -8869,7 +8972,7 @@
         <v>72</v>
       </c>
       <c r="K131" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L131" s="4">
         <v>72</v>
@@ -8887,22 +8990,22 @@
         <v>66</v>
       </c>
       <c r="T131" s="4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="U131" s="4" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="V131" s="4" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="W131" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X131" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="Y131" s="18" t="s">
-        <v>146</v>
+      <c r="X131" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y131" s="20" t="s">
+        <v>157</v>
       </c>
       <c r="Z131" s="18" t="s">
         <v>53</v>
@@ -8922,7 +9025,7 @@
         <v>72</v>
       </c>
       <c r="K132" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L132" s="4">
         <v>72</v>
@@ -8940,22 +9043,22 @@
         <v>66</v>
       </c>
       <c r="T132" s="4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="U132" s="4" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="V132" s="4" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="W132" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X132" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="Y132" s="18" t="s">
-        <v>146</v>
+      <c r="X132" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y132" s="21" t="s">
+        <v>157</v>
       </c>
       <c r="Z132" s="18" t="s">
         <v>53</v>
@@ -8975,7 +9078,7 @@
         <v>72</v>
       </c>
       <c r="K133" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L133" s="4">
         <v>72</v>
@@ -8993,22 +9096,22 @@
         <v>66</v>
       </c>
       <c r="T133" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U133" s="4" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="V133" s="4" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="W133" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="X133" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="Y133" s="18" t="s">
-        <v>146</v>
+      <c r="X133" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y133" s="20" t="s">
+        <v>157</v>
       </c>
       <c r="Z133" s="18" t="s">
         <v>53</v>
@@ -9028,7 +9131,7 @@
         <v>72</v>
       </c>
       <c r="K134" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L134" s="4">
         <v>78</v>
@@ -9046,22 +9149,22 @@
         <v>66</v>
       </c>
       <c r="T134" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U134" s="4" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="V134" s="4" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="W134" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X134" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="Y134" s="18" t="s">
-        <v>146</v>
+      <c r="X134" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y134" s="21" t="s">
+        <v>157</v>
       </c>
       <c r="Z134" s="18" t="s">
         <v>53</v>
@@ -9081,7 +9184,7 @@
         <v>72</v>
       </c>
       <c r="K135" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L135" s="4">
         <v>78</v>
@@ -9099,22 +9202,22 @@
         <v>66</v>
       </c>
       <c r="T135" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U135" s="4" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="V135" s="4" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="W135" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X135" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="Y135" s="18" t="s">
-        <v>146</v>
+      <c r="X135" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y135" s="20" t="s">
+        <v>157</v>
       </c>
       <c r="Z135" s="18" t="s">
         <v>53</v>
@@ -9134,7 +9237,7 @@
         <v>72</v>
       </c>
       <c r="K136" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L136" s="4">
         <v>78</v>
@@ -9152,22 +9255,22 @@
         <v>66</v>
       </c>
       <c r="T136" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U136" s="4" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="V136" s="4" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="W136" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="X136" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="Y136" s="18" t="s">
-        <v>146</v>
+      <c r="X136" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y136" s="21" t="s">
+        <v>157</v>
       </c>
       <c r="Z136" s="18" t="s">
         <v>53</v>
@@ -9187,7 +9290,7 @@
         <v>72</v>
       </c>
       <c r="K137" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L137" s="4">
         <v>78</v>
@@ -9205,22 +9308,22 @@
         <v>66</v>
       </c>
       <c r="T137" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U137" s="4" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="V137" s="4" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="W137" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X137" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="Y137" s="18" t="s">
-        <v>146</v>
+      <c r="X137" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y137" s="20" t="s">
+        <v>157</v>
       </c>
       <c r="Z137" s="18" t="s">
         <v>53</v>
@@ -9240,7 +9343,7 @@
         <v>72</v>
       </c>
       <c r="K138" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L138" s="4">
         <v>78</v>
@@ -9258,22 +9361,22 @@
         <v>66</v>
       </c>
       <c r="T138" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U138" s="4" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="V138" s="4" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="W138" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X138" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="Y138" s="18" t="s">
-        <v>146</v>
+      <c r="X138" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y138" s="21" t="s">
+        <v>157</v>
       </c>
       <c r="Z138" s="18" t="s">
         <v>53</v>
@@ -9293,7 +9396,7 @@
         <v>72</v>
       </c>
       <c r="K139" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L139" s="4">
         <v>78</v>
@@ -9311,22 +9414,22 @@
         <v>66</v>
       </c>
       <c r="T139" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U139" s="4" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="V139" s="4" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="W139" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X139" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="Y139" s="18" t="s">
-        <v>146</v>
+      <c r="X139" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y139" s="20" t="s">
+        <v>157</v>
       </c>
       <c r="Z139" s="18" t="s">
         <v>53</v>
@@ -9346,7 +9449,7 @@
         <v>72</v>
       </c>
       <c r="K140" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L140" s="4">
         <v>78</v>
@@ -9364,22 +9467,22 @@
         <v>66</v>
       </c>
       <c r="T140" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U140" s="4" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="V140" s="4" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="W140" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X140" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="Y140" s="18" t="s">
-        <v>146</v>
+      <c r="X140" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y140" s="21" t="s">
+        <v>157</v>
       </c>
       <c r="Z140" s="18" t="s">
         <v>53</v>
@@ -9399,7 +9502,7 @@
         <v>72</v>
       </c>
       <c r="K141" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L141" s="4">
         <v>78</v>
@@ -9417,22 +9520,22 @@
         <v>66</v>
       </c>
       <c r="T141" s="4" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="U141" s="4" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="V141" s="4" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="W141" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X141" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="Y141" s="18" t="s">
-        <v>147</v>
+      <c r="X141" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y141" s="20" t="s">
+        <v>156</v>
       </c>
       <c r="Z141" s="18" t="s">
         <v>89</v>
@@ -9452,7 +9555,7 @@
         <v>72</v>
       </c>
       <c r="K142" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L142" s="4">
         <v>78</v>
@@ -9470,22 +9573,22 @@
         <v>66</v>
       </c>
       <c r="T142" s="4" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="U142" s="4" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="V142" s="4" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="W142" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X142" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="Y142" s="18" t="s">
-        <v>147</v>
+      <c r="X142" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y142" s="21" t="s">
+        <v>156</v>
       </c>
       <c r="Z142" s="18" t="s">
         <v>53</v>
@@ -9505,7 +9608,7 @@
         <v>72</v>
       </c>
       <c r="K143" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L143" s="4">
         <v>78</v>
@@ -9523,22 +9626,22 @@
         <v>66</v>
       </c>
       <c r="T143" s="4" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="U143" s="4" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="V143" s="4" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="W143" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X143" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="Y143" s="18" t="s">
-        <v>147</v>
+      <c r="X143" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y143" s="20" t="s">
+        <v>156</v>
       </c>
       <c r="Z143" s="18" t="s">
         <v>53</v>
@@ -9558,7 +9661,7 @@
         <v>72</v>
       </c>
       <c r="K144" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L144" s="4">
         <v>78</v>
@@ -9576,22 +9679,22 @@
         <v>66</v>
       </c>
       <c r="T144" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U144" s="4" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="V144" s="4" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="W144" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="X144" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="Y144" s="18" t="s">
-        <v>147</v>
+      <c r="X144" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y144" s="21" t="s">
+        <v>156</v>
       </c>
       <c r="Z144" s="18" t="s">
         <v>53</v>
@@ -9611,7 +9714,7 @@
         <v>72</v>
       </c>
       <c r="K145" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L145" s="4">
         <v>84</v>
@@ -9629,22 +9732,22 @@
         <v>66</v>
       </c>
       <c r="T145" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U145" s="4" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="V145" s="4" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="W145" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X145" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="Y145" s="18" t="s">
-        <v>147</v>
+      <c r="X145" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y145" s="20" t="s">
+        <v>156</v>
       </c>
       <c r="Z145" s="18" t="s">
         <v>53</v>
@@ -9664,7 +9767,7 @@
         <v>72</v>
       </c>
       <c r="K146" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L146" s="4">
         <v>84</v>
@@ -9682,22 +9785,22 @@
         <v>66</v>
       </c>
       <c r="T146" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U146" s="4" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="V146" s="4" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="W146" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X146" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="Y146" s="18" t="s">
-        <v>147</v>
+      <c r="X146" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y146" s="21" t="s">
+        <v>156</v>
       </c>
       <c r="Z146" s="18" t="s">
         <v>53</v>
@@ -9717,7 +9820,7 @@
         <v>72</v>
       </c>
       <c r="K147" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L147" s="4">
         <v>84</v>
@@ -9735,22 +9838,22 @@
         <v>65</v>
       </c>
       <c r="T147" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U147" s="4" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="V147" s="4" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="W147" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="X147" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="Y147" s="18" t="s">
-        <v>147</v>
+      <c r="X147" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y147" s="20" t="s">
+        <v>156</v>
       </c>
       <c r="Z147" s="18" t="s">
         <v>53</v>
@@ -9770,7 +9873,7 @@
         <v>72</v>
       </c>
       <c r="K148" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L148" s="4">
         <v>84</v>
@@ -9788,22 +9891,22 @@
         <v>65</v>
       </c>
       <c r="T148" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U148" s="4" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="V148" s="4" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="W148" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X148" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="Y148" s="18" t="s">
-        <v>147</v>
+      <c r="X148" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y148" s="21" t="s">
+        <v>156</v>
       </c>
       <c r="Z148" s="18" t="s">
         <v>53</v>
@@ -9823,7 +9926,7 @@
         <v>72</v>
       </c>
       <c r="K149" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L149" s="4">
         <v>84</v>
@@ -9841,22 +9944,22 @@
         <v>66</v>
       </c>
       <c r="T149" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U149" s="4" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="V149" s="4" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="W149" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X149" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="Y149" s="18" t="s">
-        <v>147</v>
+      <c r="X149" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y149" s="20" t="s">
+        <v>156</v>
       </c>
       <c r="Z149" s="18" t="s">
         <v>53</v>
@@ -9876,7 +9979,7 @@
         <v>72</v>
       </c>
       <c r="K150" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L150" s="4">
         <v>84</v>
@@ -9894,22 +9997,22 @@
         <v>66</v>
       </c>
       <c r="T150" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U150" s="4" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="V150" s="4" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="W150" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X150" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="Y150" s="18" t="s">
-        <v>147</v>
+      <c r="X150" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y150" s="21" t="s">
+        <v>156</v>
       </c>
       <c r="Z150" s="18" t="s">
         <v>53</v>
@@ -9929,7 +10032,7 @@
         <v>72</v>
       </c>
       <c r="K151" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L151" s="4">
         <v>84</v>
@@ -9947,22 +10050,22 @@
         <v>66</v>
       </c>
       <c r="T151" s="4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="U151" s="4" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="V151" s="4" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="W151" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X151" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="Y151" s="18" t="s">
-        <v>148</v>
+      <c r="X151" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y151" s="20" t="s">
+        <v>157</v>
       </c>
       <c r="Z151" s="18" t="s">
         <v>136</v>
@@ -9982,7 +10085,7 @@
         <v>72</v>
       </c>
       <c r="K152" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L152" s="4">
         <v>84</v>
@@ -10000,22 +10103,22 @@
         <v>66</v>
       </c>
       <c r="T152" s="4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="U152" s="4" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="V152" s="4" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="W152" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X152" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="Y152" s="18" t="s">
-        <v>148</v>
+      <c r="X152" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y152" s="21" t="s">
+        <v>157</v>
       </c>
       <c r="Z152" s="18" t="s">
         <v>53</v>
@@ -10035,7 +10138,7 @@
         <v>72</v>
       </c>
       <c r="K153" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L153" s="4">
         <v>84</v>
@@ -10053,22 +10156,22 @@
         <v>66</v>
       </c>
       <c r="T153" s="4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="U153" s="4" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="V153" s="4" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="W153" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X153" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="Y153" s="18" t="s">
-        <v>148</v>
+      <c r="X153" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y153" s="20" t="s">
+        <v>157</v>
       </c>
       <c r="Z153" s="18" t="s">
         <v>53</v>
@@ -10088,7 +10191,7 @@
         <v>72</v>
       </c>
       <c r="K154" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L154" s="4">
         <v>84</v>
@@ -10106,22 +10209,22 @@
         <v>66</v>
       </c>
       <c r="T154" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U154" s="4" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="V154" s="4" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="W154" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="X154" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="Y154" s="18" t="s">
-        <v>148</v>
+      <c r="X154" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y154" s="21" t="s">
+        <v>157</v>
       </c>
       <c r="Z154" s="18" t="s">
         <v>53</v>
@@ -10141,7 +10244,7 @@
         <v>72</v>
       </c>
       <c r="K155" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L155" s="4">
         <v>90</v>
@@ -10159,22 +10262,22 @@
         <v>66</v>
       </c>
       <c r="T155" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U155" s="4" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="V155" s="4" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="W155" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X155" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="Y155" s="18" t="s">
-        <v>148</v>
+      <c r="X155" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y155" s="20" t="s">
+        <v>157</v>
       </c>
       <c r="Z155" s="18" t="s">
         <v>53</v>
@@ -10194,7 +10297,7 @@
         <v>72</v>
       </c>
       <c r="K156" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L156" s="4">
         <v>90</v>
@@ -10212,22 +10315,22 @@
         <v>66</v>
       </c>
       <c r="T156" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U156" s="4" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="V156" s="4" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="W156" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X156" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="Y156" s="18" t="s">
-        <v>148</v>
+      <c r="X156" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y156" s="21" t="s">
+        <v>157</v>
       </c>
       <c r="Z156" s="18" t="s">
         <v>53</v>
@@ -10247,7 +10350,7 @@
         <v>72</v>
       </c>
       <c r="K157" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L157" s="4">
         <v>90</v>
@@ -10265,22 +10368,22 @@
         <v>66</v>
       </c>
       <c r="T157" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U157" s="4" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="V157" s="4" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="W157" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="X157" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="Y157" s="18" t="s">
-        <v>148</v>
+      <c r="X157" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y157" s="20" t="s">
+        <v>157</v>
       </c>
       <c r="Z157" s="18" t="s">
         <v>53</v>
@@ -10300,7 +10403,7 @@
         <v>72</v>
       </c>
       <c r="K158" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L158" s="4">
         <v>90</v>
@@ -10318,22 +10421,22 @@
         <v>66</v>
       </c>
       <c r="T158" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U158" s="4" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="V158" s="4" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="W158" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X158" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="Y158" s="18" t="s">
-        <v>148</v>
+      <c r="X158" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y158" s="21" t="s">
+        <v>157</v>
       </c>
       <c r="Z158" s="18" t="s">
         <v>53</v>
@@ -10353,7 +10456,7 @@
         <v>72</v>
       </c>
       <c r="K159" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L159" s="4">
         <v>90</v>
@@ -10371,22 +10474,22 @@
         <v>66</v>
       </c>
       <c r="T159" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U159" s="4" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="V159" s="4" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="W159" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X159" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="Y159" s="18" t="s">
-        <v>148</v>
+      <c r="X159" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y159" s="20" t="s">
+        <v>157</v>
       </c>
       <c r="Z159" s="18" t="s">
         <v>53</v>
@@ -10406,7 +10509,7 @@
         <v>72</v>
       </c>
       <c r="K160" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L160" s="4">
         <v>90</v>
@@ -10424,22 +10527,22 @@
         <v>66</v>
       </c>
       <c r="T160" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U160" s="4" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="V160" s="4" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="W160" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X160" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="Y160" s="18" t="s">
-        <v>148</v>
+      <c r="X160" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y160" s="21" t="s">
+        <v>157</v>
       </c>
       <c r="Z160" s="18" t="s">
         <v>53</v>
@@ -10459,7 +10562,7 @@
         <v>72</v>
       </c>
       <c r="K161" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L161" s="4">
         <v>90</v>
@@ -10477,22 +10580,22 @@
         <v>66</v>
       </c>
       <c r="T161" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U161" s="4" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="V161" s="4" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="W161" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X161" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="Y161" s="18" t="s">
-        <v>148</v>
+      <c r="X161" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y161" s="20" t="s">
+        <v>157</v>
       </c>
       <c r="Z161" s="18" t="s">
         <v>53</v>
@@ -10512,7 +10615,7 @@
         <v>72</v>
       </c>
       <c r="K162" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L162" s="4">
         <v>90</v>
@@ -10530,22 +10633,22 @@
         <v>66</v>
       </c>
       <c r="T162" s="4" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="U162" s="4" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="V162" s="4" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="W162" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X162" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="Y162" s="18" t="s">
-        <v>149</v>
+      <c r="X162" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y162" s="21" t="s">
+        <v>156</v>
       </c>
       <c r="Z162" s="18" t="s">
         <v>89</v>
@@ -10565,7 +10668,7 @@
         <v>72</v>
       </c>
       <c r="K163" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L163" s="4">
         <v>90</v>
@@ -10583,22 +10686,22 @@
         <v>66</v>
       </c>
       <c r="T163" s="4" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="U163" s="4" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="V163" s="4" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="W163" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X163" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="Y163" s="18" t="s">
-        <v>149</v>
+      <c r="X163" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y163" s="20" t="s">
+        <v>156</v>
       </c>
       <c r="Z163" s="18" t="s">
         <v>53</v>
@@ -10618,7 +10721,7 @@
         <v>72</v>
       </c>
       <c r="K164" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L164" s="4">
         <v>90</v>
@@ -10636,22 +10739,22 @@
         <v>66</v>
       </c>
       <c r="T164" s="4" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="U164" s="4" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="V164" s="4" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="W164" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X164" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="Y164" s="18" t="s">
-        <v>149</v>
+      <c r="X164" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y164" s="21" t="s">
+        <v>156</v>
       </c>
       <c r="Z164" s="18" t="s">
         <v>53</v>
@@ -10671,7 +10774,7 @@
         <v>72</v>
       </c>
       <c r="K165" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L165" s="4">
         <v>90</v>
@@ -10689,22 +10792,22 @@
         <v>66</v>
       </c>
       <c r="T165" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U165" s="4" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="V165" s="4" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="W165" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="X165" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="Y165" s="18" t="s">
-        <v>149</v>
+      <c r="X165" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y165" s="20" t="s">
+        <v>156</v>
       </c>
       <c r="Z165" s="18" t="s">
         <v>53</v>
@@ -10724,7 +10827,7 @@
         <v>72</v>
       </c>
       <c r="K166" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L166" s="4">
         <v>96</v>
@@ -10742,22 +10845,22 @@
         <v>66</v>
       </c>
       <c r="T166" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U166" s="4" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="V166" s="4" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="W166" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X166" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="Y166" s="18" t="s">
-        <v>149</v>
+      <c r="X166" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y166" s="21" t="s">
+        <v>156</v>
       </c>
       <c r="Z166" s="18" t="s">
         <v>53</v>
@@ -10777,7 +10880,7 @@
         <v>72</v>
       </c>
       <c r="K167" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L167" s="4">
         <v>96</v>
@@ -10795,22 +10898,22 @@
         <v>66</v>
       </c>
       <c r="T167" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U167" s="4" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="V167" s="4" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="W167" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X167" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="Y167" s="18" t="s">
-        <v>149</v>
+      <c r="X167" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y167" s="20" t="s">
+        <v>156</v>
       </c>
       <c r="Z167" s="18" t="s">
         <v>53</v>
@@ -10830,7 +10933,7 @@
         <v>72</v>
       </c>
       <c r="K168" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L168" s="4">
         <v>96</v>
@@ -10848,22 +10951,22 @@
         <v>65</v>
       </c>
       <c r="T168" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U168" s="4" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="V168" s="4" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="W168" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="X168" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="Y168" s="18" t="s">
-        <v>149</v>
+      <c r="X168" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y168" s="21" t="s">
+        <v>156</v>
       </c>
       <c r="Z168" s="18" t="s">
         <v>53</v>
@@ -10883,7 +10986,7 @@
         <v>72</v>
       </c>
       <c r="K169" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L169" s="4">
         <v>96</v>
@@ -10901,22 +11004,22 @@
         <v>65</v>
       </c>
       <c r="T169" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U169" s="4" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="V169" s="4" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="W169" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X169" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="Y169" s="18" t="s">
-        <v>149</v>
+      <c r="X169" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y169" s="20" t="s">
+        <v>156</v>
       </c>
       <c r="Z169" s="18" t="s">
         <v>53</v>
@@ -10936,7 +11039,7 @@
         <v>72</v>
       </c>
       <c r="K170" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L170" s="4">
         <v>96</v>
@@ -10954,22 +11057,22 @@
         <v>66</v>
       </c>
       <c r="T170" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U170" s="4" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="V170" s="4" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="W170" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X170" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="Y170" s="18" t="s">
-        <v>149</v>
+      <c r="X170" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y170" s="21" t="s">
+        <v>156</v>
       </c>
       <c r="Z170" s="18" t="s">
         <v>53</v>
@@ -10989,7 +11092,7 @@
         <v>72</v>
       </c>
       <c r="K171" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L171" s="4">
         <v>96</v>
@@ -11007,22 +11110,22 @@
         <v>66</v>
       </c>
       <c r="T171" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U171" s="4" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="V171" s="4" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="W171" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X171" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="Y171" s="18" t="s">
-        <v>149</v>
+      <c r="X171" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y171" s="20" t="s">
+        <v>156</v>
       </c>
       <c r="Z171" s="18" t="s">
         <v>53</v>
@@ -11042,7 +11145,7 @@
         <v>72</v>
       </c>
       <c r="K172" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L172" s="4">
         <v>96</v>
@@ -11060,22 +11163,22 @@
         <v>66</v>
       </c>
       <c r="T172" s="4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="U172" s="4" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="V172" s="4" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="W172" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X172" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="Y172" s="18" t="s">
-        <v>150</v>
+      <c r="X172" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y172" s="21" t="s">
+        <v>157</v>
       </c>
       <c r="Z172" s="18" t="s">
         <v>136</v>
@@ -11095,7 +11198,7 @@
         <v>72</v>
       </c>
       <c r="K173" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L173" s="4">
         <v>96</v>
@@ -11113,22 +11216,22 @@
         <v>66</v>
       </c>
       <c r="T173" s="4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="U173" s="4" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="V173" s="4" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="W173" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X173" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="Y173" s="18" t="s">
-        <v>150</v>
+      <c r="X173" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y173" s="20" t="s">
+        <v>157</v>
       </c>
       <c r="Z173" s="18" t="s">
         <v>53</v>
@@ -11148,7 +11251,7 @@
         <v>72</v>
       </c>
       <c r="K174" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L174" s="4">
         <v>96</v>
@@ -11166,22 +11269,22 @@
         <v>66</v>
       </c>
       <c r="T174" s="4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="U174" s="4" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="V174" s="4" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="W174" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X174" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="Y174" s="18" t="s">
-        <v>150</v>
+      <c r="X174" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y174" s="21" t="s">
+        <v>157</v>
       </c>
       <c r="Z174" s="18" t="s">
         <v>53</v>
@@ -11201,7 +11304,7 @@
         <v>72</v>
       </c>
       <c r="K175" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L175" s="4">
         <v>96</v>
@@ -11219,22 +11322,22 @@
         <v>66</v>
       </c>
       <c r="T175" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U175" s="4" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="V175" s="4" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="W175" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="X175" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="Y175" s="18" t="s">
-        <v>150</v>
+      <c r="X175" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y175" s="20" t="s">
+        <v>157</v>
       </c>
       <c r="Z175" s="18" t="s">
         <v>53</v>
@@ -11254,7 +11357,7 @@
         <v>72</v>
       </c>
       <c r="K176" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L176" s="4">
         <v>102</v>
@@ -11272,22 +11375,22 @@
         <v>66</v>
       </c>
       <c r="T176" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U176" s="4" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="V176" s="4" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="W176" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X176" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="Y176" s="18" t="s">
-        <v>150</v>
+      <c r="X176" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y176" s="21" t="s">
+        <v>157</v>
       </c>
       <c r="Z176" s="18" t="s">
         <v>53</v>
@@ -11307,7 +11410,7 @@
         <v>72</v>
       </c>
       <c r="K177" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L177" s="4">
         <v>102</v>
@@ -11325,22 +11428,22 @@
         <v>66</v>
       </c>
       <c r="T177" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U177" s="4" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="V177" s="4" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="W177" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X177" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="Y177" s="18" t="s">
-        <v>150</v>
+      <c r="X177" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y177" s="20" t="s">
+        <v>157</v>
       </c>
       <c r="Z177" s="18" t="s">
         <v>53</v>
@@ -11360,7 +11463,7 @@
         <v>72</v>
       </c>
       <c r="K178" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L178" s="4">
         <v>102</v>
@@ -11378,22 +11481,22 @@
         <v>66</v>
       </c>
       <c r="T178" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U178" s="4" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="V178" s="4" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="W178" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="X178" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="Y178" s="18" t="s">
-        <v>150</v>
+      <c r="X178" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y178" s="21" t="s">
+        <v>157</v>
       </c>
       <c r="Z178" s="18" t="s">
         <v>53</v>
@@ -11413,7 +11516,7 @@
         <v>72</v>
       </c>
       <c r="K179" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L179" s="4">
         <v>102</v>
@@ -11431,22 +11534,22 @@
         <v>66</v>
       </c>
       <c r="T179" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U179" s="4" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="V179" s="4" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="W179" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X179" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="Y179" s="18" t="s">
-        <v>150</v>
+      <c r="X179" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y179" s="20" t="s">
+        <v>157</v>
       </c>
       <c r="Z179" s="18" t="s">
         <v>53</v>
@@ -11466,7 +11569,7 @@
         <v>72</v>
       </c>
       <c r="K180" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L180" s="4">
         <v>102</v>
@@ -11484,22 +11587,22 @@
         <v>66</v>
       </c>
       <c r="T180" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U180" s="4" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="V180" s="4" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="W180" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X180" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="Y180" s="18" t="s">
-        <v>150</v>
+      <c r="X180" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y180" s="21" t="s">
+        <v>157</v>
       </c>
       <c r="Z180" s="18" t="s">
         <v>53</v>
@@ -11519,7 +11622,7 @@
         <v>72</v>
       </c>
       <c r="K181" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L181" s="4">
         <v>102</v>
@@ -11537,22 +11640,22 @@
         <v>66</v>
       </c>
       <c r="T181" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U181" s="4" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="V181" s="4" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="W181" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X181" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="Y181" s="18" t="s">
-        <v>150</v>
+      <c r="X181" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y181" s="20" t="s">
+        <v>157</v>
       </c>
       <c r="Z181" s="18" t="s">
         <v>53</v>
@@ -11572,7 +11675,7 @@
         <v>72</v>
       </c>
       <c r="K182" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L182" s="4">
         <v>102</v>
@@ -11590,22 +11693,22 @@
         <v>66</v>
       </c>
       <c r="T182" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U182" s="4" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="V182" s="4" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="W182" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X182" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="Y182" s="18" t="s">
-        <v>150</v>
+      <c r="X182" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y182" s="21" t="s">
+        <v>157</v>
       </c>
       <c r="Z182" s="18" t="s">
         <v>53</v>
@@ -11625,7 +11728,7 @@
         <v>72</v>
       </c>
       <c r="K183" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L183" s="4">
         <v>102</v>
@@ -11643,22 +11746,22 @@
         <v>66</v>
       </c>
       <c r="T183" s="4" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="U183" s="4" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="V183" s="4" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="W183" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X183" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="Y183" s="18" t="s">
-        <v>149</v>
+      <c r="X183" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y183" s="20" t="s">
+        <v>156</v>
       </c>
       <c r="Z183" s="18" t="s">
         <v>89</v>
@@ -11678,7 +11781,7 @@
         <v>72</v>
       </c>
       <c r="K184" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L184" s="4">
         <v>102</v>
@@ -11696,22 +11799,22 @@
         <v>66</v>
       </c>
       <c r="T184" s="4" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="U184" s="4" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="V184" s="4" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="W184" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X184" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="Y184" s="18" t="s">
-        <v>149</v>
+      <c r="X184" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y184" s="21" t="s">
+        <v>156</v>
       </c>
       <c r="Z184" s="18" t="s">
         <v>53</v>
@@ -11731,7 +11834,7 @@
         <v>72</v>
       </c>
       <c r="K185" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L185" s="4">
         <v>102</v>
@@ -11749,22 +11852,22 @@
         <v>66</v>
       </c>
       <c r="T185" s="4" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="U185" s="4" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="V185" s="4" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="W185" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X185" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="Y185" s="18" t="s">
-        <v>149</v>
+      <c r="X185" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y185" s="20" t="s">
+        <v>156</v>
       </c>
       <c r="Z185" s="18" t="s">
         <v>53</v>
@@ -11784,7 +11887,7 @@
         <v>72</v>
       </c>
       <c r="K186" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L186" s="4">
         <v>102</v>
@@ -11802,22 +11905,22 @@
         <v>66</v>
       </c>
       <c r="T186" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U186" s="4" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="V186" s="4" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="W186" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="X186" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="Y186" s="18" t="s">
-        <v>149</v>
+      <c r="X186" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y186" s="21" t="s">
+        <v>156</v>
       </c>
       <c r="Z186" s="18" t="s">
         <v>53</v>
@@ -11837,7 +11940,7 @@
         <v>72</v>
       </c>
       <c r="K187" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L187" s="4">
         <v>108</v>
@@ -11855,22 +11958,22 @@
         <v>66</v>
       </c>
       <c r="T187" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U187" s="4" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="V187" s="4" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="W187" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X187" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="Y187" s="18" t="s">
-        <v>149</v>
+      <c r="X187" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y187" s="20" t="s">
+        <v>156</v>
       </c>
       <c r="Z187" s="18" t="s">
         <v>53</v>
@@ -11890,7 +11993,7 @@
         <v>72</v>
       </c>
       <c r="K188" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L188" s="4">
         <v>108</v>
@@ -11908,22 +12011,22 @@
         <v>66</v>
       </c>
       <c r="T188" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U188" s="4" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="V188" s="4" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="W188" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X188" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="Y188" s="18" t="s">
-        <v>149</v>
+      <c r="X188" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y188" s="21" t="s">
+        <v>156</v>
       </c>
       <c r="Z188" s="18" t="s">
         <v>53</v>
@@ -11943,7 +12046,7 @@
         <v>72</v>
       </c>
       <c r="K189" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L189" s="4">
         <v>108</v>
@@ -11961,22 +12064,22 @@
         <v>65</v>
       </c>
       <c r="T189" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U189" s="4" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="V189" s="4" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="W189" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="X189" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="Y189" s="18" t="s">
-        <v>149</v>
+      <c r="X189" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y189" s="20" t="s">
+        <v>156</v>
       </c>
       <c r="Z189" s="18" t="s">
         <v>53</v>
@@ -11996,7 +12099,7 @@
         <v>72</v>
       </c>
       <c r="K190" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L190" s="4">
         <v>108</v>
@@ -12014,22 +12117,22 @@
         <v>65</v>
       </c>
       <c r="T190" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U190" s="4" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="V190" s="4" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="W190" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X190" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="Y190" s="18" t="s">
-        <v>149</v>
+      <c r="X190" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y190" s="21" t="s">
+        <v>156</v>
       </c>
       <c r="Z190" s="18" t="s">
         <v>53</v>
@@ -12049,7 +12152,7 @@
         <v>72</v>
       </c>
       <c r="K191" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L191" s="4">
         <v>108</v>
@@ -12067,22 +12170,22 @@
         <v>66</v>
       </c>
       <c r="T191" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U191" s="4" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="V191" s="4" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="W191" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X191" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="Y191" s="18" t="s">
-        <v>149</v>
+      <c r="X191" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y191" s="20" t="s">
+        <v>156</v>
       </c>
       <c r="Z191" s="18" t="s">
         <v>53</v>
@@ -12102,7 +12205,7 @@
         <v>72</v>
       </c>
       <c r="K192" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L192" s="4">
         <v>108</v>
@@ -12120,22 +12223,22 @@
         <v>66</v>
       </c>
       <c r="T192" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U192" s="4" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="V192" s="4" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="W192" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X192" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="Y192" s="18" t="s">
-        <v>149</v>
+      <c r="X192" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y192" s="21" t="s">
+        <v>156</v>
       </c>
       <c r="Z192" s="18" t="s">
         <v>53</v>
@@ -12155,7 +12258,7 @@
         <v>72</v>
       </c>
       <c r="K193" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L193" s="4">
         <v>108</v>
@@ -12173,22 +12276,22 @@
         <v>66</v>
       </c>
       <c r="T193" s="4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="U193" s="4" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="V193" s="4" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="W193" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X193" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="Y193" s="18" t="s">
-        <v>150</v>
+      <c r="X193" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y193" s="20" t="s">
+        <v>157</v>
       </c>
       <c r="Z193" s="18" t="s">
         <v>136</v>
@@ -12208,7 +12311,7 @@
         <v>72</v>
       </c>
       <c r="K194" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L194" s="4">
         <v>108</v>
@@ -12226,22 +12329,22 @@
         <v>66</v>
       </c>
       <c r="T194" s="4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="U194" s="4" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="V194" s="4" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="W194" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X194" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="Y194" s="18" t="s">
-        <v>150</v>
+      <c r="X194" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y194" s="21" t="s">
+        <v>157</v>
       </c>
       <c r="Z194" s="18" t="s">
         <v>53</v>
@@ -12261,7 +12364,7 @@
         <v>72</v>
       </c>
       <c r="K195" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L195" s="4">
         <v>108</v>
@@ -12279,22 +12382,22 @@
         <v>66</v>
       </c>
       <c r="T195" s="4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="U195" s="4" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="V195" s="4" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="W195" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X195" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="Y195" s="18" t="s">
-        <v>150</v>
+      <c r="X195" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y195" s="20" t="s">
+        <v>157</v>
       </c>
       <c r="Z195" s="18" t="s">
         <v>53</v>
@@ -12314,7 +12417,7 @@
         <v>72</v>
       </c>
       <c r="K196" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L196" s="4">
         <v>108</v>
@@ -12332,22 +12435,22 @@
         <v>66</v>
       </c>
       <c r="T196" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U196" s="4" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="V196" s="4" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="W196" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="X196" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="Y196" s="18" t="s">
-        <v>150</v>
+      <c r="X196" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y196" s="21" t="s">
+        <v>157</v>
       </c>
       <c r="Z196" s="18" t="s">
         <v>53</v>
@@ -12367,7 +12470,7 @@
         <v>72</v>
       </c>
       <c r="K197" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L197" s="4">
         <v>114</v>
@@ -12385,22 +12488,22 @@
         <v>66</v>
       </c>
       <c r="T197" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U197" s="4" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="V197" s="4" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="W197" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X197" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="Y197" s="18" t="s">
-        <v>150</v>
+      <c r="X197" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y197" s="20" t="s">
+        <v>157</v>
       </c>
       <c r="Z197" s="18" t="s">
         <v>53</v>
@@ -12420,7 +12523,7 @@
         <v>72</v>
       </c>
       <c r="K198" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L198" s="4">
         <v>114</v>
@@ -12438,22 +12541,22 @@
         <v>66</v>
       </c>
       <c r="T198" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U198" s="4" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="V198" s="4" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="W198" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X198" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="Y198" s="18" t="s">
-        <v>150</v>
+      <c r="X198" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y198" s="21" t="s">
+        <v>157</v>
       </c>
       <c r="Z198" s="18" t="s">
         <v>53</v>
@@ -12473,7 +12576,7 @@
         <v>72</v>
       </c>
       <c r="K199" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L199" s="4">
         <v>114</v>
@@ -12491,22 +12594,22 @@
         <v>66</v>
       </c>
       <c r="T199" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U199" s="4" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="V199" s="4" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="W199" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="X199" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="Y199" s="18" t="s">
-        <v>150</v>
+      <c r="X199" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y199" s="20" t="s">
+        <v>157</v>
       </c>
       <c r="Z199" s="18" t="s">
         <v>53</v>
@@ -12526,7 +12629,7 @@
         <v>72</v>
       </c>
       <c r="K200" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L200" s="4">
         <v>114</v>
@@ -12544,16 +12647,16 @@
         <v>66</v>
       </c>
       <c r="T200" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="W200" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X200" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="Y200" s="18" t="s">
-        <v>150</v>
+      <c r="X200" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y200" s="21" t="s">
+        <v>157</v>
       </c>
       <c r="Z200" s="18" t="s">
         <v>53</v>
@@ -12573,7 +12676,7 @@
         <v>72</v>
       </c>
       <c r="K201" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L201" s="4">
         <v>114</v>
@@ -12591,16 +12694,16 @@
         <v>66</v>
       </c>
       <c r="T201" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="W201" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X201" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="Y201" s="18" t="s">
-        <v>150</v>
+      <c r="X201" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y201" s="20" t="s">
+        <v>157</v>
       </c>
       <c r="Z201" s="18" t="s">
         <v>53</v>
@@ -12620,7 +12723,7 @@
         <v>72</v>
       </c>
       <c r="K202" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L202" s="4">
         <v>114</v>
@@ -12638,16 +12741,16 @@
         <v>66</v>
       </c>
       <c r="T202" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="W202" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X202" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="Y202" s="18" t="s">
-        <v>150</v>
+      <c r="X202" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y202" s="21" t="s">
+        <v>157</v>
       </c>
       <c r="Z202" s="18" t="s">
         <v>53</v>
@@ -12667,7 +12770,7 @@
         <v>72</v>
       </c>
       <c r="K203" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L203" s="4">
         <v>114</v>
@@ -12685,16 +12788,16 @@
         <v>66</v>
       </c>
       <c r="T203" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="W203" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X203" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="Y203" s="18" t="s">
-        <v>150</v>
+      <c r="X203" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y203" s="20" t="s">
+        <v>157</v>
       </c>
       <c r="Z203" s="18" t="s">
         <v>53</v>
@@ -12714,7 +12817,7 @@
         <v>72</v>
       </c>
       <c r="K204" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L204" s="4">
         <v>114</v>
@@ -12732,16 +12835,16 @@
         <v>66</v>
       </c>
       <c r="T204" s="4" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="W204" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X204" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="Y204" s="18" t="s">
-        <v>149</v>
+      <c r="X204" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y204" s="21" t="s">
+        <v>156</v>
       </c>
       <c r="Z204" s="18" t="s">
         <v>89</v>
@@ -12761,7 +12864,7 @@
         <v>72</v>
       </c>
       <c r="K205" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L205" s="4">
         <v>114</v>
@@ -12779,16 +12882,16 @@
         <v>66</v>
       </c>
       <c r="T205" s="4" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="W205" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X205" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="Y205" s="18" t="s">
-        <v>149</v>
+      <c r="X205" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y205" s="20" t="s">
+        <v>156</v>
       </c>
       <c r="Z205" s="18" t="s">
         <v>53</v>
@@ -12798,6 +12901,28 @@
       <c r="A206" s="1"/>
       <c r="B206" s="1"/>
       <c r="C206" s="1"/>
+      <c r="X206" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="Y206" s="18" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="207" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="X207" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="Y207" s="18" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="208" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="X208" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="Y208" s="18" t="s">
+        <v>137</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>

--- a/programs/assembly/tage_test_trace.xlsx
+++ b/programs/assembly/tage_test_trace.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\emerald\zaqal\programs\assembly\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE488C8C-7C69-499B-ABF6-52FE5CFF3E9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{528FAB25-E15A-45DE-A437-ADD1964C1774}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30855" yWindow="780" windowWidth="12360" windowHeight="15150" xr2:uid="{E346031A-6FE0-420F-941A-72680D802F2C}"/>
+    <workbookView xWindow="10725" yWindow="0" windowWidth="14520" windowHeight="15150" xr2:uid="{E346031A-6FE0-420F-941A-72680D802F2C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2335" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2313" uniqueCount="161">
   <si>
     <t>order</t>
   </si>
@@ -514,13 +514,19 @@
   </si>
   <si>
     <t xml:space="preserve"> (T0[7], Tag=x7,US=0, CTR=3) </t>
+  </si>
+  <si>
+    <t>A20A</t>
+  </si>
+  <si>
+    <t>143 (check TOP.Core.backend.exec.regFile.io_wdata_0[63:0] and TOP.Core.backend.exec.regFile.io_waddr_0[7:0]  at cycle 143)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -643,6 +649,13 @@
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="6" tint="-0.249977111117893"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -718,7 +731,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -753,6 +766,7 @@
     <xf numFmtId="0" fontId="17" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1083,10 +1097,14 @@
     <col min="12" max="12" width="4.42578125" style="4" customWidth="1"/>
     <col min="13" max="15" width="3.5703125" style="4" customWidth="1"/>
     <col min="16" max="17" width="2.42578125" style="4" customWidth="1"/>
-    <col min="18" max="18" width="5.5703125" style="4" customWidth="1"/>
-    <col min="19" max="20" width="9.140625" style="4"/>
+    <col min="18" max="18" width="3.140625" style="4" customWidth="1"/>
+    <col min="19" max="19" width="4.5703125" style="4" customWidth="1"/>
+    <col min="20" max="20" width="5.42578125" style="4" customWidth="1"/>
     <col min="21" max="22" width="5.140625" style="4" customWidth="1"/>
-    <col min="23" max="27" width="9.140625" style="4"/>
+    <col min="23" max="23" width="9.140625" style="4"/>
+    <col min="24" max="24" width="4.140625" style="4" customWidth="1"/>
+    <col min="25" max="25" width="7.42578125" style="4" customWidth="1"/>
+    <col min="26" max="27" width="9.140625" style="4"/>
     <col min="28" max="28" width="3.7109375" style="4" customWidth="1"/>
     <col min="29" max="29" width="4" style="4" customWidth="1"/>
     <col min="30" max="16384" width="9.140625" style="4"/>
@@ -3369,7 +3387,7 @@
       <c r="B40" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="C40" s="24" t="s">
         <v>54</v>
       </c>
       <c r="D40" s="1"/>
@@ -3378,42 +3396,44 @@
       </c>
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
-      <c r="H40" s="1"/>
+      <c r="H40" s="24" t="s">
+        <v>160</v>
+      </c>
       <c r="I40" s="1"/>
-      <c r="J40" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="K40" s="4" t="s">
+      <c r="J40" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="K40" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="L40" s="4">
+      <c r="L40" s="1">
         <v>24</v>
       </c>
-      <c r="M40" s="4">
+      <c r="M40" s="1">
         <v>2</v>
       </c>
-      <c r="N40" s="4">
+      <c r="N40" s="1">
         <v>20</v>
       </c>
-      <c r="O40" s="4">
+      <c r="O40" s="1">
         <v>8</v>
       </c>
       <c r="P40" s="1"/>
       <c r="Q40" s="1"/>
       <c r="R40" s="1"/>
-      <c r="S40" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="T40" s="4" t="s">
+      <c r="S40" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="T40" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="U40" s="4" t="s">
+      <c r="U40" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="V40" s="4" t="s">
+      <c r="V40" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="W40" s="4" t="s">
+      <c r="W40" s="1" t="s">
         <v>53</v>
       </c>
       <c r="X40" s="23" t="s">
@@ -3448,40 +3468,40 @@
       <c r="G41" s="1"/>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
-      <c r="J41" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="K41" s="4" t="s">
+      <c r="J41" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="K41" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="L41" s="4">
+      <c r="L41" s="1">
         <v>24</v>
       </c>
-      <c r="M41" s="4">
-        <v>0</v>
-      </c>
-      <c r="N41" s="4">
+      <c r="M41" s="1">
+        <v>0</v>
+      </c>
+      <c r="N41" s="1">
         <v>20</v>
       </c>
-      <c r="O41" s="4">
+      <c r="O41" s="1">
         <v>8</v>
       </c>
       <c r="P41" s="1"/>
       <c r="Q41" s="1"/>
       <c r="R41" s="1"/>
-      <c r="S41" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="T41" s="4" t="s">
+      <c r="S41" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="T41" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="U41" s="4" t="s">
+      <c r="U41" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="V41" s="4" t="s">
+      <c r="V41" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="W41" s="4" t="s">
+      <c r="W41" s="1" t="s">
         <v>53</v>
       </c>
       <c r="X41" s="22" t="s">
@@ -3512,48 +3532,50 @@
       <c r="E42" s="19">
         <v>628293</v>
       </c>
-      <c r="F42" s="1"/>
+      <c r="F42" s="1">
+        <v>0</v>
+      </c>
       <c r="G42" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H42" s="1"/>
       <c r="I42" s="1">
         <v>144</v>
       </c>
-      <c r="J42" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="K42" s="4" t="s">
+      <c r="J42" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="K42" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="L42" s="4">
+      <c r="L42" s="1">
         <v>24</v>
       </c>
-      <c r="M42" s="4">
-        <v>0</v>
-      </c>
-      <c r="N42" s="4">
+      <c r="M42" s="1">
+        <v>0</v>
+      </c>
+      <c r="N42" s="1">
         <v>20</v>
       </c>
-      <c r="O42" s="4">
+      <c r="O42" s="1">
         <v>8</v>
       </c>
       <c r="P42" s="1"/>
       <c r="Q42" s="1"/>
       <c r="R42" s="1"/>
-      <c r="S42" s="4" t="s">
+      <c r="S42" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="T42" s="4" t="s">
+      <c r="T42" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="U42" s="4" t="s">
+      <c r="U42" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="V42" s="4" t="s">
+      <c r="V42" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="W42" s="4" t="s">
+      <c r="W42" s="1" t="s">
         <v>78</v>
       </c>
       <c r="X42" s="23" t="s">
@@ -3588,40 +3610,40 @@
       <c r="G43" s="1"/>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
-      <c r="J43" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="K43" s="4" t="s">
+      <c r="J43" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="K43" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="L43" s="4">
+      <c r="L43" s="1">
         <v>24</v>
       </c>
-      <c r="M43" s="4">
-        <v>0</v>
-      </c>
-      <c r="N43" s="4">
+      <c r="M43" s="1">
+        <v>0</v>
+      </c>
+      <c r="N43" s="1">
         <v>20</v>
       </c>
-      <c r="O43" s="4">
+      <c r="O43" s="1">
         <v>0</v>
       </c>
       <c r="P43" s="1"/>
       <c r="Q43" s="1"/>
       <c r="R43" s="1"/>
-      <c r="S43" s="4" t="s">
+      <c r="S43" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="T43" s="4" t="s">
+      <c r="T43" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="U43" s="4" t="s">
+      <c r="U43" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="V43" s="4" t="s">
+      <c r="V43" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="W43" s="4" t="s">
+      <c r="W43" s="1" t="s">
         <v>53</v>
       </c>
       <c r="X43" s="22" t="s">
@@ -3652,44 +3674,50 @@
       <c r="E44" s="19">
         <v>70463</v>
       </c>
-      <c r="F44" s="1"/>
-      <c r="G44" s="1"/>
+      <c r="F44" s="1">
+        <v>0</v>
+      </c>
+      <c r="G44" s="1">
+        <v>1</v>
+      </c>
       <c r="H44" s="1"/>
-      <c r="I44" s="1"/>
-      <c r="J44" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="K44" s="4" t="s">
+      <c r="I44" s="1">
+        <v>154</v>
+      </c>
+      <c r="J44" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="K44" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="L44" s="4">
+      <c r="L44" s="1">
         <v>24</v>
       </c>
-      <c r="M44" s="4">
-        <v>0</v>
-      </c>
-      <c r="N44" s="4">
+      <c r="M44" s="1">
+        <v>0</v>
+      </c>
+      <c r="N44" s="1">
         <v>20</v>
       </c>
-      <c r="O44" s="4">
+      <c r="O44" s="1">
         <v>0</v>
       </c>
       <c r="P44" s="1"/>
       <c r="Q44" s="1"/>
       <c r="R44" s="1"/>
-      <c r="S44" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="T44" s="4" t="s">
+      <c r="S44" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="T44" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="U44" s="4" t="s">
+      <c r="U44" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="V44" s="4" t="s">
+      <c r="V44" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="W44" s="4" t="s">
+      <c r="W44" s="1" t="s">
         <v>53</v>
       </c>
       <c r="X44" s="23" t="s">
@@ -3717,47 +3745,47 @@
         <v>23</v>
       </c>
       <c r="D45" s="1"/>
-      <c r="E45" s="1" t="s">
-        <v>23</v>
+      <c r="E45" s="19">
+        <v>1120233</v>
       </c>
       <c r="F45" s="1"/>
       <c r="G45" s="1"/>
       <c r="H45" s="1"/>
       <c r="I45" s="1"/>
-      <c r="J45" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="K45" s="4" t="s">
+      <c r="J45" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="K45" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="L45" s="4">
+      <c r="L45" s="1">
         <v>24</v>
       </c>
-      <c r="M45" s="4">
-        <v>0</v>
-      </c>
-      <c r="N45" s="4">
+      <c r="M45" s="1">
+        <v>0</v>
+      </c>
+      <c r="N45" s="1">
         <v>20</v>
       </c>
-      <c r="O45" s="4">
+      <c r="O45" s="1">
         <v>0</v>
       </c>
       <c r="P45" s="1"/>
       <c r="Q45" s="1"/>
       <c r="R45" s="1"/>
-      <c r="S45" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="T45" s="4" t="s">
+      <c r="S45" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="T45" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="U45" s="4" t="s">
+      <c r="U45" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="V45" s="4" t="s">
+      <c r="V45" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="W45" s="4" t="s">
+      <c r="W45" s="1" t="s">
         <v>53</v>
       </c>
       <c r="X45" s="22" t="s">
@@ -3785,57 +3813,59 @@
         <v>24</v>
       </c>
       <c r="D46" s="1"/>
-      <c r="E46" s="1" t="s">
-        <v>24</v>
+      <c r="E46" s="19" t="s">
+        <v>147</v>
       </c>
       <c r="F46" s="1"/>
       <c r="G46" s="1"/>
       <c r="H46" s="1"/>
-      <c r="I46" s="1"/>
-      <c r="J46" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="K46" s="4" t="s">
+      <c r="I46" s="1">
+        <v>165</v>
+      </c>
+      <c r="J46" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="K46" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="L46" s="4">
+      <c r="L46" s="1">
         <v>24</v>
       </c>
-      <c r="M46" s="4">
-        <v>0</v>
-      </c>
-      <c r="N46" s="4">
+      <c r="M46" s="1">
+        <v>0</v>
+      </c>
+      <c r="N46" s="1">
         <v>20</v>
       </c>
-      <c r="O46" s="4">
+      <c r="O46" s="1">
         <v>0</v>
       </c>
       <c r="P46" s="1"/>
       <c r="Q46" s="1"/>
       <c r="R46" s="1"/>
-      <c r="S46" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="T46" s="4" t="s">
+      <c r="S46" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="T46" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="U46" s="4" t="s">
+      <c r="U46" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="V46" s="4" t="s">
+      <c r="V46" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="W46" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="X46" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="Y46" s="21" t="s">
-        <v>155</v>
-      </c>
-      <c r="Z46" s="18" t="s">
-        <v>136</v>
+      <c r="W46" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="X46" s="23" t="s">
+        <v>159</v>
+      </c>
+      <c r="Y46" s="23">
+        <v>288288</v>
+      </c>
+      <c r="Z46" s="16" t="s">
+        <v>90</v>
       </c>
       <c r="AB46" s="1"/>
       <c r="AC46" s="1"/>
@@ -3853,8 +3883,8 @@
         <v>28</v>
       </c>
       <c r="D47" s="1"/>
-      <c r="E47" s="1" t="s">
-        <v>28</v>
+      <c r="E47" s="19" t="s">
+        <v>150</v>
       </c>
       <c r="F47" s="1"/>
       <c r="G47" s="1"/>
@@ -3896,11 +3926,11 @@
       <c r="W47" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X47" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="Y47" s="20" t="s">
-        <v>155</v>
+      <c r="X47" s="23" t="s">
+        <v>159</v>
+      </c>
+      <c r="Y47" s="23">
+        <v>288288</v>
       </c>
       <c r="Z47" s="18" t="s">
         <v>53</v>
@@ -3921,8 +3951,8 @@
         <v>29</v>
       </c>
       <c r="D48" s="1"/>
-      <c r="E48" s="1" t="s">
-        <v>29</v>
+      <c r="E48" s="19">
+        <v>1400793</v>
       </c>
       <c r="F48" s="1"/>
       <c r="G48" s="1"/>
@@ -3964,11 +3994,11 @@
       <c r="W48" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X48" s="21" t="s">
-        <v>155</v>
-      </c>
-      <c r="Y48" s="21" t="s">
-        <v>155</v>
+      <c r="X48" s="23" t="s">
+        <v>159</v>
+      </c>
+      <c r="Y48" s="23">
+        <v>288288</v>
       </c>
       <c r="Z48" s="18" t="s">
         <v>53</v>
@@ -3989,8 +4019,8 @@
         <v>27</v>
       </c>
       <c r="D49" s="1"/>
-      <c r="E49" s="1" t="s">
-        <v>27</v>
+      <c r="E49" s="19" t="s">
+        <v>149</v>
       </c>
       <c r="F49" s="1"/>
       <c r="G49" s="1"/>
@@ -4032,11 +4062,11 @@
       <c r="W49" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="X49" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="Y49" s="20" t="s">
-        <v>155</v>
+      <c r="X49" s="23" t="s">
+        <v>159</v>
+      </c>
+      <c r="Y49" s="23">
+        <v>288288</v>
       </c>
       <c r="Z49" s="18" t="s">
         <v>53</v>
@@ -4057,8 +4087,8 @@
         <v>54</v>
       </c>
       <c r="D50" s="1"/>
-      <c r="E50" s="1" t="s">
-        <v>18</v>
+      <c r="E50" s="19">
+        <v>628293</v>
       </c>
       <c r="F50" s="1"/>
       <c r="G50" s="1"/>
@@ -4100,11 +4130,11 @@
       <c r="W50" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X50" s="21" t="s">
-        <v>155</v>
-      </c>
-      <c r="Y50" s="21" t="s">
-        <v>155</v>
+      <c r="X50" s="23" t="s">
+        <v>159</v>
+      </c>
+      <c r="Y50" s="23">
+        <v>288288</v>
       </c>
       <c r="Z50" s="18" t="s">
         <v>53</v>
@@ -4125,8 +4155,8 @@
         <v>19</v>
       </c>
       <c r="D51" s="1"/>
-      <c r="E51" s="1" t="s">
-        <v>19</v>
+      <c r="E51" s="19" t="s">
+        <v>144</v>
       </c>
       <c r="F51" s="1"/>
       <c r="G51" s="1"/>
@@ -4168,11 +4198,11 @@
       <c r="W51" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X51" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="Y51" s="20" t="s">
-        <v>155</v>
+      <c r="X51" s="23" t="s">
+        <v>159</v>
+      </c>
+      <c r="Y51" s="23">
+        <v>288288</v>
       </c>
       <c r="Z51" s="18" t="s">
         <v>53</v>
@@ -4193,8 +4223,8 @@
         <v>20</v>
       </c>
       <c r="D52" s="1"/>
-      <c r="E52" s="1" t="s">
-        <v>20</v>
+      <c r="E52" s="19">
+        <v>70463</v>
       </c>
       <c r="F52" s="1"/>
       <c r="G52" s="1"/>
@@ -4236,11 +4266,11 @@
       <c r="W52" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="X52" s="21" t="s">
-        <v>155</v>
-      </c>
-      <c r="Y52" s="21" t="s">
-        <v>155</v>
+      <c r="X52" s="23" t="s">
+        <v>159</v>
+      </c>
+      <c r="Y52" s="23">
+        <v>288288</v>
       </c>
       <c r="Z52" s="18" t="s">
         <v>53</v>
@@ -4261,8 +4291,8 @@
         <v>21</v>
       </c>
       <c r="D53" s="1"/>
-      <c r="E53" s="1" t="s">
-        <v>21</v>
+      <c r="E53" s="19">
+        <v>100793</v>
       </c>
       <c r="F53" s="1"/>
       <c r="G53" s="1"/>
@@ -4304,11 +4334,11 @@
       <c r="W53" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X53" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="Y53" s="20" t="s">
-        <v>155</v>
+      <c r="X53" s="23" t="s">
+        <v>159</v>
+      </c>
+      <c r="Y53" s="23">
+        <v>288288</v>
       </c>
       <c r="Z53" s="18" t="s">
         <v>53</v>
@@ -4329,8 +4359,8 @@
         <v>22</v>
       </c>
       <c r="D54" s="1"/>
-      <c r="E54" s="1" t="s">
-        <v>22</v>
+      <c r="E54" s="19">
+        <v>271893</v>
       </c>
       <c r="F54" s="1"/>
       <c r="G54" s="1"/>
@@ -4372,11 +4402,11 @@
       <c r="W54" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X54" s="21" t="s">
-        <v>155</v>
-      </c>
-      <c r="Y54" s="21" t="s">
-        <v>155</v>
+      <c r="X54" s="23" t="s">
+        <v>159</v>
+      </c>
+      <c r="Y54" s="23">
+        <v>288288</v>
       </c>
       <c r="Z54" s="18" t="s">
         <v>53</v>
@@ -4397,8 +4427,8 @@
         <v>30</v>
       </c>
       <c r="D55" s="1"/>
-      <c r="E55" s="1" t="s">
-        <v>30</v>
+      <c r="E55" s="19" t="s">
+        <v>145</v>
       </c>
       <c r="F55" s="1"/>
       <c r="G55" s="1"/>
@@ -4440,11 +4470,11 @@
       <c r="W55" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X55" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="Y55" s="20" t="s">
-        <v>155</v>
+      <c r="X55" s="23" t="s">
+        <v>159</v>
+      </c>
+      <c r="Y55" s="23">
+        <v>288288</v>
       </c>
       <c r="Z55" s="18" t="s">
         <v>53</v>
@@ -4465,8 +4495,8 @@
         <v>23</v>
       </c>
       <c r="D56" s="1"/>
-      <c r="E56" s="1" t="s">
-        <v>23</v>
+      <c r="E56" s="19">
+        <v>1120233</v>
       </c>
       <c r="F56" s="1"/>
       <c r="G56" s="1"/>
@@ -4508,11 +4538,11 @@
       <c r="W56" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="X56" s="21" t="s">
-        <v>155</v>
-      </c>
-      <c r="Y56" s="21" t="s">
-        <v>155</v>
+      <c r="X56" s="23" t="s">
+        <v>159</v>
+      </c>
+      <c r="Y56" s="23">
+        <v>288288</v>
       </c>
       <c r="Z56" s="18" t="s">
         <v>53</v>
@@ -4533,8 +4563,8 @@
         <v>24</v>
       </c>
       <c r="D57" s="1"/>
-      <c r="E57" s="1" t="s">
-        <v>24</v>
+      <c r="E57" s="19" t="s">
+        <v>147</v>
       </c>
       <c r="F57" s="1"/>
       <c r="G57" s="1"/>
@@ -4601,8 +4631,8 @@
         <v>25</v>
       </c>
       <c r="D58" s="1"/>
-      <c r="E58" s="1" t="s">
-        <v>25</v>
+      <c r="E58" s="19">
+        <v>1400793</v>
       </c>
       <c r="F58" s="1"/>
       <c r="G58" s="1"/>
@@ -4669,8 +4699,8 @@
         <v>26</v>
       </c>
       <c r="D59" s="1"/>
-      <c r="E59" s="1" t="s">
-        <v>26</v>
+      <c r="E59" s="19" t="s">
+        <v>148</v>
       </c>
       <c r="F59" s="1"/>
       <c r="G59" s="1"/>
@@ -4737,8 +4767,8 @@
         <v>27</v>
       </c>
       <c r="D60" s="1"/>
-      <c r="E60" s="1" t="s">
-        <v>27</v>
+      <c r="E60" s="19" t="s">
+        <v>149</v>
       </c>
       <c r="F60" s="1"/>
       <c r="G60" s="1"/>
@@ -4805,8 +4835,8 @@
         <v>54</v>
       </c>
       <c r="D61" s="1"/>
-      <c r="E61" s="1" t="s">
-        <v>18</v>
+      <c r="E61" s="19">
+        <v>628293</v>
       </c>
       <c r="F61" s="1"/>
       <c r="G61" s="1"/>
@@ -4873,8 +4903,8 @@
         <v>19</v>
       </c>
       <c r="D62" s="1"/>
-      <c r="E62" s="1" t="s">
-        <v>19</v>
+      <c r="E62" s="19" t="s">
+        <v>144</v>
       </c>
       <c r="F62" s="1"/>
       <c r="G62" s="1"/>
@@ -4941,8 +4971,8 @@
         <v>20</v>
       </c>
       <c r="D63" s="1"/>
-      <c r="E63" s="1" t="s">
-        <v>20</v>
+      <c r="E63" s="19">
+        <v>70463</v>
       </c>
       <c r="F63" s="1"/>
       <c r="G63" s="1"/>
@@ -5009,8 +5039,8 @@
         <v>22</v>
       </c>
       <c r="D64" s="1"/>
-      <c r="E64" s="1" t="s">
-        <v>21</v>
+      <c r="E64" s="19">
+        <v>100793</v>
       </c>
       <c r="F64" s="1"/>
       <c r="G64" s="1"/>
@@ -5077,8 +5107,8 @@
         <v>30</v>
       </c>
       <c r="D65" s="1"/>
-      <c r="E65" s="1" t="s">
-        <v>22</v>
+      <c r="E65" s="19">
+        <v>271893</v>
       </c>
       <c r="F65" s="1"/>
       <c r="G65" s="1"/>
@@ -5145,8 +5175,8 @@
         <v>23</v>
       </c>
       <c r="D66" s="1"/>
-      <c r="E66" s="1" t="s">
-        <v>30</v>
+      <c r="E66" s="19" t="s">
+        <v>145</v>
       </c>
       <c r="F66" s="1"/>
       <c r="G66" s="1"/>
